--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="411" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E110889-FAD8-44BF-A484-BCE96DAD1330}"/>
+  <xr:revisionPtr revIDLastSave="420" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0921D60-E89A-4F5E-B883-DEDBA3F12087}"/>
   <bookViews>
-    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" firstSheet="4" activeTab="4" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
+    <workbookView xWindow="1013" yWindow="1995" windowWidth="16200" windowHeight="9308" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Aria (tubo aperto)" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="30">
   <si>
     <t>n</t>
   </si>
@@ -57,16 +57,10 @@
     <t>Incertezza</t>
   </si>
   <si>
-    <t>0,5 hz</t>
-  </si>
-  <si>
     <t>3,5 cm</t>
   </si>
   <si>
     <t>0,5cm</t>
-  </si>
-  <si>
-    <t>1 hz</t>
   </si>
   <si>
     <t>n=4</t>
@@ -145,7 +139,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -215,7 +209,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -548,15 +542,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06F22C44-05D5-4272-A0FE-86D34BE429B9}">
   <dimension ref="A2:F18"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" customWidth="1"/>
+    <col min="1" max="1" width="22.3984375" customWidth="1"/>
+    <col min="2" max="2" width="21.59765625" customWidth="1"/>
     <col min="3" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" customWidth="1"/>
+    <col min="6" max="6" width="16.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -573,87 +567,87 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>1</v>
       </c>
       <c r="B3">
         <v>190.1</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3">
+        <v>3.5</v>
+      </c>
+      <c r="E3" t="s">
         <v>5</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>2</v>
       </c>
       <c r="B4">
         <v>381</v>
       </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>3</v>
       </c>
       <c r="B5">
         <v>561</v>
       </c>
-      <c r="C5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="C5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>4</v>
       </c>
       <c r="B6">
         <v>760.2</v>
       </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="C6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
         <v>5</v>
       </c>
       <c r="B7">
         <v>935.6</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>13</v>
       </c>
       <c r="C10" s="3">
         <v>34.5</v>
@@ -662,7 +656,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B11" s="5"/>
       <c r="C11" s="3">
         <v>56</v>
@@ -671,7 +665,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B12" s="6"/>
       <c r="C12" s="3">
         <v>78.8</v>
@@ -680,9 +674,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B13" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C13" s="3">
         <v>23</v>
@@ -691,7 +685,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B14" s="5"/>
       <c r="C14" s="3">
         <v>45</v>
@@ -700,7 +694,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B15" s="5"/>
       <c r="C15" s="3">
         <v>67.5</v>
@@ -709,22 +703,22 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C16">
         <f>(2*90)/4</f>
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="3:3">
+    <row r="17" spans="3:3" x14ac:dyDescent="0.45">
       <c r="C17" s="3">
         <f>C12-C10</f>
         <v>44.3</v>
       </c>
     </row>
-    <row r="18" spans="3:3">
+    <row r="18" spans="3:3" x14ac:dyDescent="0.45">
       <c r="C18" s="3">
         <f>C15-C13</f>
         <v>44.5</v>
@@ -742,31 +736,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AB8339D-D738-4E2D-B0E2-FC9074DD0D10}">
   <dimension ref="B1:H7"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" customWidth="1"/>
+    <col min="3" max="3" width="13.59765625" customWidth="1"/>
+    <col min="5" max="5" width="15.86328125" customWidth="1"/>
+    <col min="6" max="6" width="13.59765625" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8">
+    <row r="1" spans="2:8" x14ac:dyDescent="0.45">
       <c r="C1" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D1" s="5"/>
       <c r="E1" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F1" s="5"/>
       <c r="G1" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H1" s="5"/>
     </row>
-    <row r="2" spans="2:8">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -789,7 +783,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:8">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B3" s="2">
         <v>1</v>
       </c>
@@ -812,7 +806,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B4" s="2">
         <v>2</v>
       </c>
@@ -835,7 +829,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B5" s="2">
         <v>3</v>
       </c>
@@ -858,7 +852,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="2:8">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B6" s="2">
         <v>4</v>
       </c>
@@ -881,7 +875,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="2:8">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B7" s="2">
         <v>5</v>
       </c>
@@ -917,15 +911,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{358E4CEC-525A-4BCF-91E4-363DE62CA86F}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" customWidth="1"/>
-    <col min="8" max="8" width="12.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.86328125" customWidth="1"/>
+    <col min="7" max="7" width="14.3984375" customWidth="1"/>
+    <col min="8" max="8" width="12.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -936,10 +930,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>0</v>
@@ -951,16 +945,16 @@
         <v>2</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -983,7 +977,7 @@
         <v>83.8</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1003,7 +997,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1023,7 +1017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1043,7 +1037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1071,29 +1065,29 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF3685B9-F09A-4019-850A-B546C03596ED}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>24</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>25</v>
       </c>
-      <c r="E1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1.57</v>
       </c>
@@ -1104,7 +1098,7 @@
         <v>4.4999999999999997E-3</v>
       </c>
       <c r="D2">
-        <f>A2/B2</f>
+        <f t="shared" ref="D2:D8" si="0">A2/B2</f>
         <v>348.88888888888891</v>
       </c>
       <c r="E2">
@@ -1112,10 +1106,10 @@
         <v>348.88888888888891</v>
       </c>
       <c r="F2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>1.37</v>
       </c>
@@ -1126,15 +1120,15 @@
         <v>3.9199999999999999E-3</v>
       </c>
       <c r="D3">
-        <f>A3/B3</f>
+        <f t="shared" si="0"/>
         <v>349.48979591836741</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E8" si="0">A3/C3</f>
+        <f t="shared" ref="E3:E8" si="1">A3/C3</f>
         <v>349.48979591836741</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>1.17</v>
       </c>
@@ -1145,15 +1139,15 @@
         <v>3.3500000000000001E-3</v>
       </c>
       <c r="D4">
-        <f>A4/B4</f>
+        <f t="shared" si="0"/>
         <v>348.21428571428567</v>
       </c>
       <c r="E4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>349.25373134328356</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>0.97</v>
       </c>
@@ -1164,15 +1158,15 @@
         <v>2.7699999999999999E-3</v>
       </c>
       <c r="D5">
-        <f>A5/B5</f>
+        <f t="shared" si="0"/>
         <v>347.67025089605733</v>
       </c>
       <c r="E5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>350.18050541516249</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>0.77</v>
       </c>
@@ -1183,15 +1177,15 @@
         <v>2.2000000000000001E-3</v>
       </c>
       <c r="D6">
-        <f>A6/B6</f>
-        <v>350</v>
-      </c>
-      <c r="E6">
         <f t="shared" si="0"/>
         <v>350</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="E6">
+        <f t="shared" si="1"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>0.56999999999999995</v>
       </c>
@@ -1202,15 +1196,15 @@
         <v>1.6199999999999999E-3</v>
       </c>
       <c r="D7">
-        <f>A7/B7</f>
-        <v>351.85185185185185</v>
-      </c>
-      <c r="E7">
         <f t="shared" si="0"/>
         <v>351.85185185185185</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="E7">
+        <f t="shared" si="1"/>
+        <v>351.85185185185185</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>0.37</v>
       </c>
@@ -1221,11 +1215,11 @@
         <v>1.0399999999999999E-3</v>
       </c>
       <c r="D8">
-        <f>A8/B8</f>
+        <f t="shared" si="0"/>
         <v>352.38095238095241</v>
       </c>
       <c r="E8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>355.76923076923077</v>
       </c>
     </row>
@@ -1237,24 +1231,24 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA895F12-453C-425C-ABA4-7F1645AB6AC5}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="15.140625" customWidth="1"/>
+    <col min="1" max="1" width="15.1328125" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>490</v>
       </c>
@@ -1262,7 +1256,7 @@
         <v>-710</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>500</v>
       </c>
@@ -1273,7 +1267,7 @@
         <v>-620</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>510</v>
       </c>
@@ -1288,7 +1282,7 @@
         <v>2.247495384378138</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>520</v>
       </c>
@@ -1299,7 +1293,7 @@
         <v>-80</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>534.29999999999995</v>
       </c>
@@ -1310,7 +1304,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>540</v>
       </c>
@@ -1321,7 +1315,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>550</v>
       </c>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="420" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0921D60-E89A-4F5E-B883-DEDBA3F12087}"/>
+  <xr:revisionPtr revIDLastSave="459" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4107681A-6FF2-4830-A7E6-6A484EFDD51E}"/>
   <bookViews>
-    <workbookView xWindow="1013" yWindow="1995" windowWidth="16200" windowHeight="9308" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Aria (tubo aperto)" sheetId="1" r:id="rId1"/>
-    <sheet name="Aria (tubo chiuso)" sheetId="2" r:id="rId2"/>
-    <sheet name="Argon e Kripton" sheetId="3" r:id="rId3"/>
-    <sheet name="Onde quadre-riflessione" sheetId="4" r:id="rId4"/>
-    <sheet name="Punto 5" sheetId="5" r:id="rId5"/>
+    <sheet name="Foglio1" sheetId="6" r:id="rId2"/>
+    <sheet name="Aria (tubo chiuso)" sheetId="2" r:id="rId3"/>
+    <sheet name="Argon e Kripton" sheetId="3" r:id="rId4"/>
+    <sheet name="Onde quadre-riflessione" sheetId="4" r:id="rId5"/>
+    <sheet name="Punto 5" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
   <si>
     <t>n</t>
   </si>
@@ -57,21 +58,12 @@
     <t>Incertezza</t>
   </si>
   <si>
-    <t>3,5 cm</t>
-  </si>
-  <si>
-    <t>0,5cm</t>
-  </si>
-  <si>
     <t>n=4</t>
   </si>
   <si>
     <t>Distanza (cm)</t>
   </si>
   <si>
-    <t>v suono teorica</t>
-  </si>
-  <si>
     <t>frequenza=760,2 hz</t>
   </si>
   <si>
@@ -130,6 +122,12 @@
   </si>
   <si>
     <t>Dt micro s</t>
+  </si>
+  <si>
+    <t>Incertezza (m)</t>
+  </si>
+  <si>
+    <t>Lunghezza tubo (m)</t>
   </si>
 </sst>
 </file>
@@ -174,7 +172,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -191,11 +189,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -207,6 +242,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -541,7 +580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06F22C44-05D5-4272-A0FE-86D34BE429B9}">
-  <dimension ref="A2:F18"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="22.3984375" customWidth="1"/>
@@ -550,190 +589,217 @@
     <col min="6" max="6" width="16.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" s="1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>190.1</v>
+      </c>
+      <c r="C2">
+        <v>3.5</v>
+      </c>
+      <c r="D2" s="8">
+        <v>3.5000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>190.1</v>
+        <v>381</v>
       </c>
       <c r="C3">
         <v>3.5</v>
       </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="D3" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>381</v>
+        <v>561</v>
       </c>
       <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+        <v>4</v>
+      </c>
+      <c r="D4" s="8">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5">
-        <v>561</v>
+        <v>760.2</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="D5" s="9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>760.2</v>
+        <v>935.6</v>
       </c>
       <c r="C6">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A7" s="2">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>935.6</v>
-      </c>
-      <c r="C7">
+      <c r="D6" s="8">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="D7" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D8" s="10">
+        <v>0.01</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B0617E3-9B4E-4B1F-B0F5-FBC89FE8E318}">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="16.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.53125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.1328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A10" s="4" t="s">
+      <c r="E1" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="3">
-        <v>34.5</v>
-      </c>
-      <c r="D10">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B11" s="5"/>
-      <c r="C11" s="3">
-        <v>56</v>
-      </c>
-      <c r="D11">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B12" s="6"/>
-      <c r="C12" s="3">
-        <v>78.8</v>
-      </c>
-      <c r="D12">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B13" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="3">
-        <v>23</v>
-      </c>
-      <c r="D13">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B14" s="5"/>
-      <c r="C14" s="3">
-        <v>45</v>
-      </c>
-      <c r="D14">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B15" s="5"/>
-      <c r="C15" s="3">
-        <v>67.5</v>
-      </c>
-      <c r="D15">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16">
+      <c r="F1">
         <f>(2*90)/4</f>
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.45">
-      <c r="C17" s="3">
-        <f>C12-C10</f>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3">
+        <v>34.5</v>
+      </c>
+      <c r="D2">
+        <v>0.5</v>
+      </c>
+      <c r="F2" s="3">
+        <f>C4-C2</f>
         <v>44.3</v>
       </c>
     </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.45">
-      <c r="C18" s="3">
-        <f>C15-C13</f>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="3">
+        <v>56</v>
+      </c>
+      <c r="D3">
+        <v>0.5</v>
+      </c>
+      <c r="F3" s="3">
+        <f>C7-C5</f>
         <v>44.5</v>
       </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B4" s="6"/>
+      <c r="C4" s="3">
+        <v>78.8</v>
+      </c>
+      <c r="D4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="3">
+        <v>23</v>
+      </c>
+      <c r="D5">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B6" s="5"/>
+      <c r="C6" s="3">
+        <v>45</v>
+      </c>
+      <c r="D6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B7" s="5"/>
+      <c r="C7" s="3">
+        <v>67.5</v>
+      </c>
+      <c r="D7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C11" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B5:B7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AB8339D-D738-4E2D-B0E2-FC9074DD0D10}">
   <dimension ref="B1:H7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -748,15 +814,15 @@
   <sheetData>
     <row r="1" spans="2:8" x14ac:dyDescent="0.45">
       <c r="C1" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D1" s="5"/>
       <c r="E1" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F1" s="5"/>
       <c r="G1" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H1" s="5"/>
     </row>
@@ -908,7 +974,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{358E4CEC-525A-4BCF-91E4-363DE62CA86F}">
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -930,10 +996,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>0</v>
@@ -945,13 +1011,13 @@
         <v>2</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
@@ -1062,29 +1128,29 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF3685B9-F09A-4019-850A-B546C03596ED}">
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>22</v>
-      </c>
-      <c r="D1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
@@ -1106,7 +1172,7 @@
         <v>348.88888888888891</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
@@ -1228,7 +1294,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA895F12-453C-425C-ABA4-7F1645AB6AC5}">
   <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1239,13 +1305,13 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="459" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4107681A-6FF2-4830-A7E6-6A484EFDD51E}"/>
+  <xr:revisionPtr revIDLastSave="469" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5ADEA415-4D2B-44E8-B541-C541D1B62199}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="33">
   <si>
     <t>n</t>
   </si>
@@ -128,6 +128,18 @@
   </si>
   <si>
     <t>Lunghezza tubo (m)</t>
+  </si>
+  <si>
+    <t>Temperatura stanza (k)</t>
+  </si>
+  <si>
+    <t>Massa molare aria (g/mol)</t>
+  </si>
+  <si>
+    <t>Incertezza (g/mol)</t>
+  </si>
+  <si>
+    <t>γ</t>
   </si>
 </sst>
 </file>
@@ -230,7 +242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -246,6 +258,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -580,7 +594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06F22C44-05D5-4272-A0FE-86D34BE429B9}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="22.3984375" customWidth="1"/>
@@ -589,7 +603,7 @@
     <col min="6" max="6" width="16.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -602,8 +616,11 @@
       <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E1" s="11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -616,8 +633,11 @@
       <c r="D2" s="8">
         <v>3.5000000000000003E-2</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E2" s="12">
+        <v>296.14999999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -630,8 +650,11 @@
       <c r="D3" s="9" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E3" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -644,8 +667,11 @@
       <c r="D4" s="8">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E4">
+        <v>28.97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -658,8 +684,11 @@
       <c r="D5" s="9" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E5" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -672,15 +701,24 @@
       <c r="D6" s="8">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E6" s="12">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="D7" s="9" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="E7" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="D8" s="10">
         <v>0.01</v>
+      </c>
+      <c r="E8">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="469" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5ADEA415-4D2B-44E8-B541-C541D1B62199}"/>
+  <xr:revisionPtr revIDLastSave="503" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F071D7E4-096F-4143-B4B9-7A81C539BC19}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="34">
   <si>
     <t>n</t>
   </si>
@@ -140,17 +140,29 @@
   </si>
   <si>
     <t>γ</t>
+  </si>
+  <si>
+    <t>R gas ideale</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="176" formatCode="#,##0.000000000"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -242,7 +254,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -260,6 +272,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -594,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06F22C44-05D5-4272-A0FE-86D34BE429B9}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="22.3984375" customWidth="1"/>
@@ -668,7 +682,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="E4">
-        <v>28.97</v>
+        <v>2.8964699999999999E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
@@ -719,6 +733,16 @@
       </c>
       <c r="E8">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E9" s="13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E10" s="14">
+        <v>8.3144626180000003</v>
       </c>
     </row>
   </sheetData>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="503" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F071D7E4-096F-4143-B4B9-7A81C539BC19}"/>
+  <xr:revisionPtr revIDLastSave="504" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CB086D1-E9E2-4DC5-BF3C-66305C000E6B}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
@@ -716,7 +716,7 @@
         <v>0.9</v>
       </c>
       <c r="E6" s="12">
-        <v>0.05</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="504" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CB086D1-E9E2-4DC5-BF3C-66305C000E6B}"/>
+  <xr:revisionPtr revIDLastSave="508" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F909E5B2-B345-42F4-91DA-D1639678F471}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="35">
   <si>
     <t>n</t>
   </si>
@@ -143,6 +143,9 @@
   </si>
   <si>
     <t>R gas ideale</t>
+  </si>
+  <si>
+    <t>Incertezza temperatura (k)</t>
   </si>
 </sst>
 </file>
@@ -608,7 +611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06F22C44-05D5-4272-A0FE-86D34BE429B9}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="22.3984375" customWidth="1"/>
@@ -664,8 +667,8 @@
       <c r="D3" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>30</v>
+      <c r="E3" s="11" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
@@ -681,8 +684,8 @@
       <c r="D4" s="8">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="E4">
-        <v>2.8964699999999999E-2</v>
+      <c r="E4" s="12">
+        <v>0.5</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
@@ -699,7 +702,7 @@
         <v>28</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
@@ -715,8 +718,8 @@
       <c r="D6" s="8">
         <v>0.9</v>
       </c>
-      <c r="E6" s="12">
-        <v>5.0000000000000001E-4</v>
+      <c r="E6">
+        <v>2.8964699999999999E-2</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
@@ -724,24 +727,34 @@
         <v>27</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="D8" s="10">
         <v>0.01</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="12">
+        <v>5.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E9" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E10">
         <v>1.4</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="E9" s="13" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E11" s="13" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="E10" s="14">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E12" s="14">
         <v>8.3144626180000003</v>
       </c>
     </row>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="508" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F909E5B2-B345-42F4-91DA-D1639678F471}"/>
+  <xr:revisionPtr revIDLastSave="513" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F12C74B-3A3D-451C-B7E5-10C54351C0E8}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Aria (tubo aperto)" sheetId="1" r:id="rId1"/>
@@ -876,7 +876,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AB8339D-D738-4E2D-B0E2-FC9074DD0D10}">
-  <dimension ref="B1:H7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -887,163 +887,163 @@
     <col min="8" max="8" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="C1" s="5" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="B1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5" t="s">
+      <c r="C1" s="5"/>
+      <c r="D1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5" t="s">
+      <c r="E1" s="5"/>
+      <c r="F1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="5"/>
-    </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="G1" s="5"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B2" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="E2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="G2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B3" s="2">
-        <v>1</v>
+      <c r="B3">
+        <v>319.2</v>
       </c>
       <c r="C3">
-        <v>319.2</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>760</v>
       </c>
       <c r="E3">
-        <v>760</v>
+        <v>3</v>
       </c>
       <c r="F3">
+        <v>377</v>
+      </c>
+      <c r="G3">
         <v>3</v>
       </c>
-      <c r="G3">
-        <v>377</v>
-      </c>
-      <c r="H3">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>534.29999999999995</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>1068</v>
+      </c>
+      <c r="E4">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B4" s="2">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>534.29999999999995</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>1068</v>
-      </c>
       <c r="F4">
+        <v>632</v>
+      </c>
+      <c r="G4">
         <v>3</v>
       </c>
-      <c r="G4">
-        <v>632</v>
-      </c>
-      <c r="H4">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B5" s="2">
+      <c r="B5">
+        <v>741.2</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>1688</v>
+      </c>
+      <c r="E5">
         <v>3</v>
       </c>
-      <c r="C5">
-        <v>741.2</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>1688</v>
-      </c>
       <c r="F5">
+        <v>884</v>
+      </c>
+      <c r="G5">
         <v>3</v>
       </c>
-      <c r="G5">
-        <v>884</v>
-      </c>
-      <c r="H5">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>954.1</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>1990</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>1146</v>
+      </c>
+      <c r="G6">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B6" s="2">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>954.1</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>1990</v>
-      </c>
-      <c r="F6">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A7" s="2">
         <v>5</v>
       </c>
-      <c r="G6">
-        <v>1146</v>
-      </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B7" s="2">
+      <c r="B7">
+        <v>1155.0999999999999</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>2290</v>
+      </c>
+      <c r="E7">
         <v>5</v>
       </c>
-      <c r="C7">
-        <v>1155.0999999999999</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>2290</v>
-      </c>
       <c r="F7">
-        <v>5</v>
+        <v>1404.5</v>
       </c>
       <c r="G7">
-        <v>1404.5</v>
-      </c>
-      <c r="H7">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="513" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F12C74B-3A3D-451C-B7E5-10C54351C0E8}"/>
+  <xr:revisionPtr revIDLastSave="515" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC15F71D-7ED9-4855-9D3A-0BB8C26E848D}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
@@ -932,7 +932,7 @@
         <v>319.2</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3">
         <v>760</v>
@@ -955,7 +955,7 @@
         <v>534.29999999999995</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4">
         <v>1068</v>
@@ -978,7 +978,7 @@
         <v>741.2</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5">
         <v>1688</v>
@@ -1001,7 +1001,7 @@
         <v>954.1</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6">
         <v>1990</v>
@@ -1024,7 +1024,7 @@
         <v>1155.0999999999999</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7">
         <v>2290</v>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="515" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC15F71D-7ED9-4855-9D3A-0BB8C26E848D}"/>
+  <xr:revisionPtr revIDLastSave="519" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A43244E-2F16-4B4B-BDBB-F636687BA727}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
+    <workbookView xWindow="1013" yWindow="1995" windowWidth="16200" windowHeight="9308" activeTab="2" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Aria (tubo aperto)" sheetId="1" r:id="rId1"/>
@@ -154,7 +154,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="176" formatCode="#,##0.000000000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -257,26 +257,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -630,10 +628,10 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="11" t="s">
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>29</v>
       </c>
     </row>
@@ -647,10 +645,10 @@
       <c r="C2">
         <v>3.5</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="6">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2">
         <v>296.14999999999998</v>
       </c>
     </row>
@@ -664,10 +662,10 @@
       <c r="C3">
         <v>3.5</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="1" t="s">
         <v>34</v>
       </c>
     </row>
@@ -681,10 +679,10 @@
       <c r="C4">
         <v>4</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="6">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4">
         <v>0.5</v>
       </c>
     </row>
@@ -698,7 +696,7 @@
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="7" t="s">
         <v>28</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -715,7 +713,7 @@
       <c r="C6">
         <v>4</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="6">
         <v>0.9</v>
       </c>
       <c r="E6">
@@ -723,7 +721,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="7" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -731,10 +729,10 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D8" s="10">
+      <c r="D8" s="8">
         <v>0.01</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8">
         <v>5.0000000000000001E-4</v>
       </c>
     </row>
@@ -749,12 +747,12 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="9" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="E12" s="14">
+      <c r="E12" s="10">
         <v>8.3144626180000003</v>
       </c>
     </row>
@@ -794,7 +792,7 @@
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="3">
@@ -812,7 +810,7 @@
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="5"/>
+      <c r="B3" s="11"/>
       <c r="C3" s="3">
         <v>56</v>
       </c>
@@ -825,7 +823,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B4" s="6"/>
+      <c r="B4" s="12"/>
       <c r="C4" s="3">
         <v>78.8</v>
       </c>
@@ -834,7 +832,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="3">
@@ -845,7 +843,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B6" s="5"/>
+      <c r="B6" s="11"/>
       <c r="C6" s="3">
         <v>45</v>
       </c>
@@ -854,7 +852,7 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B7" s="5"/>
+      <c r="B7" s="11"/>
       <c r="C7" s="3">
         <v>67.5</v>
       </c>
@@ -888,18 +886,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5" t="s">
+      <c r="C1" s="11"/>
+      <c r="D1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5" t="s">
+      <c r="E1" s="11"/>
+      <c r="F1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="5"/>
+      <c r="G1" s="11"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
@@ -949,7 +947,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4">
         <v>534.29999999999995</v>
@@ -972,7 +970,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B5">
         <v>741.2</v>
@@ -995,7 +993,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B6">
         <v>954.1</v>
@@ -1018,7 +1016,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B7">
         <v>1155.0999999999999</v>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="519" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A43244E-2F16-4B4B-BDBB-F636687BA727}"/>
+  <xr:revisionPtr revIDLastSave="645" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A886EA8F-E192-4FDF-BEFE-B1191BEFAD53}"/>
   <bookViews>
-    <workbookView xWindow="1013" yWindow="1995" windowWidth="16200" windowHeight="9308" activeTab="2" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="4" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Aria (tubo aperto)" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="38">
   <si>
     <t>n</t>
   </si>
@@ -55,18 +55,9 @@
     <t>D diametro del tubo aperto</t>
   </si>
   <si>
-    <t>Incertezza</t>
-  </si>
-  <si>
     <t>n=4</t>
   </si>
   <si>
-    <t>Distanza (cm)</t>
-  </si>
-  <si>
-    <t>frequenza=760,2 hz</t>
-  </si>
-  <si>
     <t>Ventri</t>
   </si>
   <si>
@@ -146,17 +137,38 @@
   </si>
   <si>
     <t>Incertezza temperatura (k)</t>
+  </si>
+  <si>
+    <t>λ_n/2 osservata</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>λ_n sperimentale</t>
+  </si>
+  <si>
+    <t>V suono (m/s)</t>
+  </si>
+  <si>
+    <t>Posizione teorica (m)</t>
+  </si>
+  <si>
+    <t>Distanza (m)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.000000000"/>
+    <numFmt numFmtId="173" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="178" formatCode="0.000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -171,6 +183,18 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="5">
@@ -199,7 +223,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -208,15 +232,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -253,30 +268,141 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="173" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="12" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="12" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="12" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Migliaia" xfId="1" builtinId="3"/>
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -610,7 +736,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06F22C44-05D5-4272-A0FE-86D34BE429B9}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="22.3984375" customWidth="1"/>
     <col min="2" max="2" width="21.59765625" customWidth="1"/>
@@ -618,7 +744,7 @@
     <col min="6" max="6" width="16.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -632,10 +758,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -652,7 +778,7 @@
         <v>296.14999999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -663,13 +789,13 @@
         <v>3.5</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -686,7 +812,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -697,13 +823,13 @@
         <v>4</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -720,15 +846,15 @@
         <v>2.8964699999999999E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5">
       <c r="D7" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="14.65" thickBot="1">
       <c r="D8" s="8">
         <v>0.01</v>
       </c>
@@ -736,22 +862,22 @@
         <v>5.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5">
       <c r="E9" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="E10">
         <v>1.4</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5">
       <c r="E11" s="9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="E12" s="10">
         <v>8.3144626180000003</v>
       </c>
@@ -763,104 +889,194 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B0617E3-9B4E-4B1F-B0F5-FBC89FE8E318}">
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="16.19921875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.53125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.86328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="C1" s="2" t="s">
+    <row r="1" spans="1:9" ht="14.65" thickBot="1">
+      <c r="A1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="B2" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="28">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="D2" s="29">
+        <v>0.05</v>
+      </c>
+      <c r="E2" s="18">
+        <f>G2/G4</f>
+        <v>0.45381056300973421</v>
+      </c>
+      <c r="F2" s="19">
+        <f>C4-C3</f>
+        <v>0.22799999999999998</v>
+      </c>
+      <c r="G2" s="30">
+        <v>344.98678999999998</v>
+      </c>
+      <c r="H2" s="18">
+        <v>1</v>
+      </c>
+      <c r="I2" s="22">
+        <f>G2/(2*G4)</f>
+        <v>0.22690528150486711</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="B3" s="25"/>
+      <c r="C3" s="23">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="D3" s="22">
+        <v>0.05</v>
+      </c>
+      <c r="E3" s="18"/>
+      <c r="F3" s="19">
+        <f>C7-C6</f>
+        <v>0.22500000000000003</v>
+      </c>
+      <c r="G3" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="33">
+        <v>1.5</v>
+      </c>
+      <c r="I3" s="22">
+        <f>3*G2/(4*G4)</f>
+        <v>0.34035792225730072</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="14.65" thickBot="1">
+      <c r="B4" s="26"/>
+      <c r="C4" s="24">
+        <v>0.78800000000000003</v>
+      </c>
+      <c r="D4" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="E4" s="18"/>
+      <c r="F4" s="19">
+        <f>C6-C5</f>
+        <v>0.22</v>
+      </c>
+      <c r="G4" s="32">
+        <v>760.2</v>
+      </c>
+      <c r="H4" s="18">
+        <v>2</v>
+      </c>
+      <c r="I4" s="22">
+        <f>G2/G4</f>
+        <v>0.45381056300973421</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="14.65" thickBot="1">
+      <c r="B5" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1">
-        <f>(2*90)/4</f>
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="3">
-        <v>34.5</v>
-      </c>
-      <c r="D2">
-        <v>0.5</v>
-      </c>
-      <c r="F2" s="3">
-        <f>C4-C2</f>
-        <v>44.3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="3">
-        <v>56</v>
-      </c>
-      <c r="D3">
-        <v>0.5</v>
-      </c>
-      <c r="F3" s="3">
-        <f>C7-C5</f>
-        <v>44.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B4" s="12"/>
-      <c r="C4" s="3">
-        <v>78.8</v>
-      </c>
-      <c r="D4">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B5" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="3">
-        <v>23</v>
-      </c>
-      <c r="D5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B6" s="11"/>
-      <c r="C6" s="3">
-        <v>45</v>
-      </c>
-      <c r="D6">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B7" s="11"/>
-      <c r="C7" s="3">
-        <v>67.5</v>
-      </c>
-      <c r="D7">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C5" s="28">
+        <v>0.23</v>
+      </c>
+      <c r="D5" s="29">
+        <v>0.05</v>
+      </c>
+      <c r="E5" s="18"/>
+      <c r="F5" s="19">
+        <f>C3-C2</f>
+        <v>0.21500000000000008</v>
+      </c>
+      <c r="H5" s="34">
+        <v>2.5</v>
+      </c>
+      <c r="I5" s="22">
+        <f>(5*G2)/(4*G4)</f>
+        <v>0.56726320376216777</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="B6" s="25"/>
+      <c r="C6" s="23">
+        <v>0.45</v>
+      </c>
+      <c r="D6" s="22">
+        <v>0.05</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="13">
+        <f>AVERAGE(F2:F5)</f>
+        <v>0.22200000000000003</v>
+      </c>
+      <c r="H6" s="33">
+        <v>3</v>
+      </c>
+      <c r="I6" s="22">
+        <f>3*G2/(2*G4)</f>
+        <v>0.68071584451460143</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="14.65" thickBot="1">
+      <c r="B7" s="26"/>
+      <c r="C7" s="24">
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="D7" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="15">
+        <f>2*F6</f>
+        <v>0.44400000000000006</v>
+      </c>
+      <c r="H7" s="35">
+        <v>3.5</v>
+      </c>
+      <c r="I7" s="15">
+        <f>(G2*7)/(4*G4)</f>
+        <v>0.79416848526703487</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="C11" s="3"/>
     </row>
   </sheetData>
@@ -875,7 +1091,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AB8339D-D738-4E2D-B0E2-FC9074DD0D10}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="13.59765625" customWidth="1"/>
@@ -885,21 +1101,21 @@
     <col min="8" max="8" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7">
       <c r="B1" s="11" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C1" s="11"/>
       <c r="D1" s="11" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E1" s="11"/>
       <c r="F1" s="11" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G1" s="11"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -922,7 +1138,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -945,7 +1161,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -968,7 +1184,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7">
       <c r="A5" s="2">
         <v>5</v>
       </c>
@@ -991,7 +1207,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7">
       <c r="A6" s="2">
         <v>7</v>
       </c>
@@ -1014,7 +1230,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7">
       <c r="A7" s="2">
         <v>9</v>
       </c>
@@ -1050,7 +1266,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{358E4CEC-525A-4BCF-91E4-363DE62CA86F}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="14.86328125" customWidth="1"/>
@@ -1058,7 +1274,7 @@
     <col min="8" max="8" width="12.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1069,10 +1285,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>0</v>
@@ -1084,16 +1300,16 @@
         <v>2</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1116,7 +1332,7 @@
         <v>83.8</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1136,7 +1352,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1156,7 +1372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1176,7 +1392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1204,29 +1420,29 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF3685B9-F09A-4019-850A-B546C03596ED}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
         <v>18</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1.57</v>
       </c>
@@ -1245,10 +1461,10 @@
         <v>348.88888888888891</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>1.37</v>
       </c>
@@ -1267,7 +1483,7 @@
         <v>349.48979591836741</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>1.17</v>
       </c>
@@ -1286,7 +1502,7 @@
         <v>349.25373134328356</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>0.97</v>
       </c>
@@ -1305,7 +1521,7 @@
         <v>350.18050541516249</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>0.77</v>
       </c>
@@ -1324,7 +1540,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>0.56999999999999995</v>
       </c>
@@ -1343,7 +1559,7 @@
         <v>351.85185185185185</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>0.37</v>
       </c>
@@ -1370,24 +1586,24 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA895F12-453C-425C-ABA4-7F1645AB6AC5}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.1328125" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>490</v>
       </c>
@@ -1395,7 +1611,7 @@
         <v>-710</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>500</v>
       </c>
@@ -1406,7 +1622,7 @@
         <v>-620</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>510</v>
       </c>
@@ -1421,7 +1637,7 @@
         <v>2.247495384378138</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>520</v>
       </c>
@@ -1432,7 +1648,7 @@
         <v>-80</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>534.29999999999995</v>
       </c>
@@ -1443,7 +1659,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>540</v>
       </c>
@@ -1454,7 +1670,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>550</v>
       </c>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="645" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A886EA8F-E192-4FDF-BEFE-B1191BEFAD53}"/>
+  <xr:revisionPtr revIDLastSave="657" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E085B141-CC54-4BAC-89C1-4EC8ED80B8F8}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="4" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
+    <workbookView xWindow="675" yWindow="1657" windowWidth="16200" windowHeight="9308" firstSheet="1" activeTab="2" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Aria (tubo aperto)" sheetId="1" r:id="rId1"/>
-    <sheet name="Foglio1" sheetId="6" r:id="rId2"/>
+    <sheet name="Ventri e nodi" sheetId="6" r:id="rId2"/>
     <sheet name="Aria (tubo chiuso)" sheetId="2" r:id="rId3"/>
     <sheet name="Argon e Kripton" sheetId="3" r:id="rId4"/>
     <sheet name="Onde quadre-riflessione" sheetId="4" r:id="rId5"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="38">
   <si>
     <t>n</t>
   </si>
@@ -165,8 +165,8 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.000000000"/>
-    <numFmt numFmtId="173" formatCode="#,##0.00000"/>
-    <numFmt numFmtId="178" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -365,9 +365,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
@@ -379,20 +376,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
@@ -400,6 +388,18 @@
     <xf numFmtId="12" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="12" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="12" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Migliaia" xfId="1" builtinId="3"/>
@@ -907,171 +907,171 @@
       <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="21" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="16" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="28">
+      <c r="C2" s="24">
         <v>0.34499999999999997</v>
       </c>
-      <c r="D2" s="29">
+      <c r="D2" s="25">
         <v>0.05</v>
       </c>
-      <c r="E2" s="18">
+      <c r="E2" s="17">
         <f>G2/G4</f>
         <v>0.45381056300973421</v>
       </c>
-      <c r="F2" s="19">
+      <c r="F2" s="18">
         <f>C4-C3</f>
         <v>0.22799999999999998</v>
       </c>
-      <c r="G2" s="30">
+      <c r="G2" s="26">
         <v>344.98678999999998</v>
       </c>
-      <c r="H2" s="18">
+      <c r="H2" s="17">
         <v>1</v>
       </c>
-      <c r="I2" s="22">
+      <c r="I2" s="21">
         <f>G2/(2*G4)</f>
         <v>0.22690528150486711</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="B3" s="25"/>
-      <c r="C3" s="23">
+      <c r="B3" s="33"/>
+      <c r="C3" s="22">
         <v>0.56000000000000005</v>
       </c>
-      <c r="D3" s="22">
+      <c r="D3" s="21">
         <v>0.05</v>
       </c>
-      <c r="E3" s="18"/>
-      <c r="F3" s="19">
+      <c r="E3" s="17"/>
+      <c r="F3" s="18">
         <f>C7-C6</f>
         <v>0.22500000000000003</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="G3" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="33">
+      <c r="H3" s="29">
         <v>1.5</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="21">
         <f>3*G2/(4*G4)</f>
         <v>0.34035792225730072</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="14.65" thickBot="1">
-      <c r="B4" s="26"/>
-      <c r="C4" s="24">
+      <c r="B4" s="34"/>
+      <c r="C4" s="23">
         <v>0.78800000000000003</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="14">
         <v>0.05</v>
       </c>
-      <c r="E4" s="18"/>
-      <c r="F4" s="19">
+      <c r="E4" s="17"/>
+      <c r="F4" s="18">
         <f>C6-C5</f>
         <v>0.22</v>
       </c>
-      <c r="G4" s="32">
+      <c r="G4" s="28">
         <v>760.2</v>
       </c>
-      <c r="H4" s="18">
+      <c r="H4" s="17">
         <v>2</v>
       </c>
-      <c r="I4" s="22">
+      <c r="I4" s="21">
         <f>G2/G4</f>
         <v>0.45381056300973421</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="14.65" thickBot="1">
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="24">
         <v>0.23</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="25">
         <v>0.05</v>
       </c>
-      <c r="E5" s="18"/>
-      <c r="F5" s="19">
+      <c r="E5" s="17"/>
+      <c r="F5" s="18">
         <f>C3-C2</f>
         <v>0.21500000000000008</v>
       </c>
-      <c r="H5" s="34">
+      <c r="H5" s="30">
         <v>2.5</v>
       </c>
-      <c r="I5" s="22">
+      <c r="I5" s="21">
         <f>(5*G2)/(4*G4)</f>
         <v>0.56726320376216777</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="B6" s="25"/>
-      <c r="C6" s="23">
+      <c r="B6" s="33"/>
+      <c r="C6" s="22">
         <v>0.45</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="21">
         <v>0.05</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="12">
         <f>AVERAGE(F2:F5)</f>
         <v>0.22200000000000003</v>
       </c>
-      <c r="H6" s="33">
-        <v>3</v>
-      </c>
-      <c r="I6" s="22">
+      <c r="H6" s="29">
+        <v>3</v>
+      </c>
+      <c r="I6" s="21">
         <f>3*G2/(2*G4)</f>
         <v>0.68071584451460143</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="14.65" thickBot="1">
-      <c r="B7" s="26"/>
-      <c r="C7" s="24">
+      <c r="B7" s="34"/>
+      <c r="C7" s="23">
         <v>0.67500000000000004</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="14">
         <v>0.05</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="14">
         <f>2*F6</f>
         <v>0.44400000000000006</v>
       </c>
-      <c r="H7" s="35">
+      <c r="H7" s="31">
         <v>3.5</v>
       </c>
-      <c r="I7" s="15">
+      <c r="I7" s="14">
         <f>(G2*7)/(4*G4)</f>
         <v>0.79416848526703487</v>
       </c>
@@ -1090,7 +1090,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AB8339D-D738-4E2D-B0E2-FC9074DD0D10}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -1101,21 +1101,21 @@
     <col min="8" max="8" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="B1" s="11" t="s">
+    <row r="1" spans="1:8">
+      <c r="B1" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11" t="s">
+      <c r="C1" s="35"/>
+      <c r="D1" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="35"/>
+      <c r="G1" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="11"/>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="35"/>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1132,13 +1132,16 @@
         <v>2</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -1149,19 +1152,22 @@
         <v>3</v>
       </c>
       <c r="D3">
+        <v>377</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+      <c r="G3">
         <v>760</v>
       </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>377</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="H3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1172,19 +1178,22 @@
         <v>3</v>
       </c>
       <c r="D4">
+        <v>632</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4" s="2">
+        <v>3</v>
+      </c>
+      <c r="G4">
         <v>1068</v>
       </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>632</v>
-      </c>
-      <c r="G4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="H4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="2">
         <v>5</v>
       </c>
@@ -1195,19 +1204,22 @@
         <v>3</v>
       </c>
       <c r="D5">
+        <v>884</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5" s="2">
+        <v>7</v>
+      </c>
+      <c r="G5">
         <v>1688</v>
       </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>884</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="H5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="2">
         <v>7</v>
       </c>
@@ -1218,19 +1230,22 @@
         <v>3</v>
       </c>
       <c r="D6">
+        <v>1146</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6" s="2">
+        <v>9</v>
+      </c>
+      <c r="G6">
         <v>1990</v>
       </c>
-      <c r="E6">
+      <c r="H6">
         <v>5</v>
       </c>
-      <c r="F6">
-        <v>1146</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="2">
         <v>9</v>
       </c>
@@ -1241,23 +1256,26 @@
         <v>3</v>
       </c>
       <c r="D7">
+        <v>1404.5</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7" s="2">
+        <v>11</v>
+      </c>
+      <c r="G7">
         <v>2290</v>
       </c>
-      <c r="E7">
+      <c r="H7">
         <v>5</v>
-      </c>
-      <c r="F7">
-        <v>1404.5</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="G1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="657" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E085B141-CC54-4BAC-89C1-4EC8ED80B8F8}"/>
+  <xr:revisionPtr revIDLastSave="663" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84F3592A-EAFA-4997-BD1A-FA617A1730A0}"/>
   <bookViews>
     <workbookView xWindow="675" yWindow="1657" windowWidth="16200" windowHeight="9308" firstSheet="1" activeTab="2" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
@@ -388,6 +388,9 @@
     <xf numFmtId="12" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="12" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="12" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -396,9 +399,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -931,7 +931,7 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="33" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="24">
@@ -960,7 +960,7 @@
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="B3" s="33"/>
+      <c r="B3" s="34"/>
       <c r="C3" s="22">
         <v>0.56000000000000005</v>
       </c>
@@ -984,7 +984,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="14.65" thickBot="1">
-      <c r="B4" s="34"/>
+      <c r="B4" s="35"/>
       <c r="C4" s="23">
         <v>0.78800000000000003</v>
       </c>
@@ -1008,7 +1008,7 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="14.65" thickBot="1">
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="33" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="24">
@@ -1031,7 +1031,7 @@
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="B6" s="33"/>
+      <c r="B6" s="34"/>
       <c r="C6" s="22">
         <v>0.45</v>
       </c>
@@ -1054,7 +1054,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="14.65" thickBot="1">
-      <c r="B7" s="34"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="23">
         <v>0.67500000000000004</v>
       </c>
@@ -1102,18 +1102,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35" t="s">
+      <c r="C1" s="32"/>
+      <c r="D1" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="35"/>
-      <c r="G1" s="35" t="s">
+      <c r="E1" s="32"/>
+      <c r="G1" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="35"/>
+      <c r="H1" s="32"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
@@ -1149,13 +1149,13 @@
         <v>319.2</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D3">
         <v>377</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2">
         <v>1</v>
@@ -1164,7 +1164,7 @@
         <v>760</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1175,13 +1175,13 @@
         <v>534.29999999999995</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>632</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2">
         <v>3</v>
@@ -1190,7 +1190,7 @@
         <v>1068</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1201,13 +1201,13 @@
         <v>741.2</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>884</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F5" s="2">
         <v>7</v>
@@ -1216,7 +1216,7 @@
         <v>1688</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1227,13 +1227,13 @@
         <v>954.1</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>1146</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2">
         <v>9</v>
@@ -1253,13 +1253,13 @@
         <v>1155.0999999999999</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>1404.5</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F7" s="2">
         <v>11</v>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="663" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84F3592A-EAFA-4997-BD1A-FA617A1730A0}"/>
+  <xr:revisionPtr revIDLastSave="695" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BAE0BB1-B2B2-4F97-B1DD-19527129B037}"/>
   <bookViews>
-    <workbookView xWindow="675" yWindow="1657" windowWidth="16200" windowHeight="9308" firstSheet="1" activeTab="2" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="1" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Aria (tubo aperto)" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="38">
   <si>
     <t>n</t>
   </si>
@@ -353,7 +353,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -366,17 +366,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
@@ -400,6 +396,12 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="12" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Migliaia" xfId="1" builtinId="3"/>
@@ -889,11 +891,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B0617E3-9B4E-4B1F-B0F5-FBC89FE8E318}">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="16.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.59765625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
@@ -903,186 +905,158 @@
     <col min="9" max="9" width="17.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="14.65" thickBot="1">
+    <row r="1" spans="1:7" ht="14.65" thickBot="1">
       <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="20" t="s">
+      <c r="B1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="15" t="s">
         <v>32</v>
       </c>
       <c r="G1" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="H1" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="I1" s="16" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="B2" s="33" t="s">
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="24">
+      <c r="B2" s="37">
+        <v>0.5</v>
+      </c>
+      <c r="C2" s="20">
         <v>0.34499999999999997</v>
       </c>
-      <c r="D2" s="25">
+      <c r="D2" s="21">
         <v>0.05</v>
       </c>
-      <c r="E2" s="17">
+      <c r="E2" s="36">
         <f>G2/G4</f>
         <v>0.45381056300973421</v>
       </c>
-      <c r="F2" s="18">
+      <c r="F2" s="32">
         <f>C4-C3</f>
         <v>0.22799999999999998</v>
       </c>
-      <c r="G2" s="26">
+      <c r="G2" s="22">
         <v>344.98678999999998</v>
       </c>
-      <c r="H2" s="17">
-        <v>1</v>
-      </c>
-      <c r="I2" s="21">
-        <f>G2/(2*G4)</f>
-        <v>0.22690528150486711</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="B3" s="34"/>
-      <c r="C3" s="22">
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="30"/>
+      <c r="B3" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="C3" s="35">
         <v>0.56000000000000005</v>
       </c>
-      <c r="D3" s="21">
+      <c r="D3" s="18">
         <v>0.05</v>
       </c>
-      <c r="E3" s="17"/>
-      <c r="F3" s="18">
+      <c r="E3" s="36"/>
+      <c r="F3" s="32">
         <f>C7-C6</f>
         <v>0.22500000000000003</v>
       </c>
-      <c r="G3" s="27" t="s">
+      <c r="G3" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="29">
-        <v>1.5</v>
-      </c>
-      <c r="I3" s="21">
-        <f>3*G2/(4*G4)</f>
-        <v>0.34035792225730072</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="14.65" thickBot="1">
-      <c r="B4" s="35"/>
-      <c r="C4" s="23">
+    </row>
+    <row r="4" spans="1:7" ht="14.65" thickBot="1">
+      <c r="A4" s="31"/>
+      <c r="B4" s="27">
+        <v>2.5</v>
+      </c>
+      <c r="C4" s="19">
         <v>0.78800000000000003</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="13">
         <v>0.05</v>
       </c>
-      <c r="E4" s="17"/>
-      <c r="F4" s="18">
+      <c r="E4" s="36"/>
+      <c r="F4" s="32">
         <f>C6-C5</f>
         <v>0.22</v>
       </c>
-      <c r="G4" s="28">
+      <c r="G4" s="24">
         <v>760.2</v>
       </c>
-      <c r="H4" s="17">
-        <v>2</v>
-      </c>
-      <c r="I4" s="21">
-        <f>G2/G4</f>
-        <v>0.45381056300973421</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="14.65" thickBot="1">
-      <c r="B5" s="33" t="s">
+    </row>
+    <row r="5" spans="1:7" ht="14.65" thickBot="1">
+      <c r="A5" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="24">
+      <c r="B5" s="37">
+        <v>1</v>
+      </c>
+      <c r="C5" s="20">
         <v>0.23</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="21">
         <v>0.05</v>
       </c>
-      <c r="E5" s="17"/>
-      <c r="F5" s="18">
+      <c r="E5" s="16"/>
+      <c r="F5" s="32">
         <f>C3-C2</f>
         <v>0.21500000000000008</v>
       </c>
-      <c r="H5" s="30">
-        <v>2.5</v>
-      </c>
-      <c r="I5" s="21">
-        <f>(5*G2)/(4*G4)</f>
-        <v>0.56726320376216777</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="B6" s="34"/>
-      <c r="C6" s="22">
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="30"/>
+      <c r="B6" s="26">
+        <v>2</v>
+      </c>
+      <c r="C6" s="35">
         <v>0.45</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="18">
         <v>0.05</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="33">
         <f>AVERAGE(F2:F5)</f>
         <v>0.22200000000000003</v>
       </c>
-      <c r="H6" s="29">
+    </row>
+    <row r="7" spans="1:7" ht="14.65" thickBot="1">
+      <c r="A7" s="31"/>
+      <c r="B7" s="27">
         <v>3</v>
       </c>
-      <c r="I6" s="21">
-        <f>3*G2/(2*G4)</f>
-        <v>0.68071584451460143</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="14.65" thickBot="1">
-      <c r="B7" s="35"/>
-      <c r="C7" s="23">
+      <c r="C7" s="19">
         <v>0.67500000000000004</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="13">
         <v>0.05</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="34">
         <f>2*F6</f>
         <v>0.44400000000000006</v>
       </c>
-      <c r="H7" s="31">
-        <v>3.5</v>
-      </c>
-      <c r="I7" s="14">
-        <f>(G2*7)/(4*G4)</f>
-        <v>0.79416848526703487</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+    </row>
+    <row r="11" spans="1:7">
       <c r="C11" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A5:A7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1102,18 +1076,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32" t="s">
+      <c r="C1" s="28"/>
+      <c r="D1" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="32"/>
-      <c r="G1" s="32" t="s">
+      <c r="E1" s="28"/>
+      <c r="G1" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="32"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
@@ -1201,13 +1175,13 @@
         <v>741.2</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5">
         <v>884</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" s="2">
         <v>7</v>
@@ -1216,7 +1190,7 @@
         <v>1688</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1227,13 +1201,13 @@
         <v>954.1</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6">
         <v>1146</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" s="2">
         <v>9</v>
@@ -1242,7 +1216,7 @@
         <v>1990</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1253,13 +1227,13 @@
         <v>1155.0999999999999</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7">
         <v>1404.5</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" s="2">
         <v>11</v>
@@ -1268,7 +1242,7 @@
         <v>2290</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1603,7 +1577,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA895F12-453C-425C-ABA4-7F1645AB6AC5}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.1328125" customWidth="1"/>
@@ -1699,6 +1673,81 @@
         <v>180</v>
       </c>
     </row>
+    <row r="13" spans="1:7" ht="14.65" thickBot="1"/>
+    <row r="14" spans="1:7">
+      <c r="A14" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="22">
+        <v>344.98678999999998</v>
+      </c>
+      <c r="B15" s="16">
+        <v>1</v>
+      </c>
+      <c r="C15" s="18">
+        <f>A15/(2*A17)</f>
+        <v>0.22690528150486711</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="25">
+        <v>1.5</v>
+      </c>
+      <c r="C16" s="18">
+        <f>3*A15/(4*A17)</f>
+        <v>0.34035792225730072</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="14.65" thickBot="1">
+      <c r="A17" s="24">
+        <v>760.2</v>
+      </c>
+      <c r="B17" s="16">
+        <v>2</v>
+      </c>
+      <c r="C17" s="18">
+        <f>A15/A17</f>
+        <v>0.45381056300973421</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="B18" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="C18" s="18">
+        <f>(5*A15)/(4*A17)</f>
+        <v>0.56726320376216777</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="B19" s="25">
+        <v>3</v>
+      </c>
+      <c r="C19" s="18">
+        <f>3*A15/(2*A17)</f>
+        <v>0.68071584451460143</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="14.65" thickBot="1">
+      <c r="B20" s="27">
+        <v>3.5</v>
+      </c>
+      <c r="C20" s="13">
+        <f>(A15*7)/(4*A17)</f>
+        <v>0.79416848526703487</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="695" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BAE0BB1-B2B2-4F97-B1DD-19527129B037}"/>
+  <xr:revisionPtr revIDLastSave="699" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BC8596D-CE0E-486A-9D64-BEE0F58AB4F2}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="1" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
@@ -933,7 +933,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="37">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="C2" s="20">
         <v>0.34499999999999997</v>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="699" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BC8596D-CE0E-486A-9D64-BEE0F58AB4F2}"/>
+  <xr:revisionPtr revIDLastSave="706" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7575A064-28AD-4EA7-B54B-0B30E95C1FF9}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="1" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
@@ -933,7 +933,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="37">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="C2" s="20">
         <v>0.34499999999999997</v>
@@ -956,7 +956,7 @@
     <row r="3" spans="1:7">
       <c r="A3" s="30"/>
       <c r="B3" s="26">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="C3" s="35">
         <v>0.56000000000000005</v>
@@ -976,7 +976,7 @@
     <row r="4" spans="1:7" ht="14.65" thickBot="1">
       <c r="A4" s="31"/>
       <c r="B4" s="27">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="C4" s="19">
         <v>0.78800000000000003</v>
@@ -997,13 +997,13 @@
       <c r="A5" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="37">
+      <c r="B5" s="26">
         <v>1</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="35">
         <v>0.23</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="18">
         <v>0.05</v>
       </c>
       <c r="E5" s="16"/>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="706" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7575A064-28AD-4EA7-B54B-0B30E95C1FF9}"/>
+  <xr:revisionPtr revIDLastSave="770" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{070CFC06-9C8F-4F9D-95EF-55E3BD663ECA}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="1" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Aria (tubo aperto)" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="40">
   <si>
     <t>n</t>
   </si>
@@ -76,15 +76,6 @@
     <t>65 cm</t>
   </si>
   <si>
-    <t>L=145 cm</t>
-  </si>
-  <si>
-    <t>T=23.5</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
     <t>x</t>
   </si>
   <si>
@@ -155,6 +146,21 @@
   </si>
   <si>
     <t>Distanza (m)</t>
+  </si>
+  <si>
+    <t>Argon</t>
+  </si>
+  <si>
+    <t>Kripton</t>
+  </si>
+  <si>
+    <t>L (m)</t>
+  </si>
+  <si>
+    <t>T (K)</t>
+  </si>
+  <si>
+    <t>Massa molare (kg/mol)</t>
   </si>
 </sst>
 </file>
@@ -197,7 +203,7 @@
       <name val="Arial Unicode MS"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -222,8 +228,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -348,12 +360,64 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -363,14 +427,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -384,9 +447,6 @@
     <xf numFmtId="12" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="12" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="12" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -402,6 +462,39 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="12" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Migliaia" xfId="1" builtinId="3"/>
@@ -746,7 +839,7 @@
     <col min="6" max="6" width="16.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" ht="14.65" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -756,27 +849,27 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>26</v>
+      <c r="E1" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="15">
         <v>190.1</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="20">
         <v>3.5</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="14">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="6">
         <v>296.14999999999998</v>
       </c>
     </row>
@@ -784,33 +877,33 @@
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="14">
         <v>381</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="17">
         <v>3.5</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>31</v>
+      <c r="D3" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="14">
         <v>561</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="17">
         <v>4</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="14">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="6">
         <v>0.5</v>
       </c>
     </row>
@@ -818,69 +911,69 @@
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="14">
         <v>760.2</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="17">
         <v>4</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="D5" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="14.65" thickBot="1">
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="23">
         <v>935.6</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="11">
         <v>4</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="14">
         <v>0.9</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="6">
         <v>2.8964699999999999E-2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="D7" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>28</v>
+      <c r="D7" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="14.65" thickBot="1">
-      <c r="D8" s="8">
+      <c r="D8" s="23">
         <v>0.01</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="6">
         <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="E9" s="1" t="s">
-        <v>29</v>
+      <c r="E9" s="7" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="E10">
+      <c r="E10" s="6">
         <v>1.4</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="E11" s="9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="E12" s="10">
+      <c r="E11" s="53" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="14.65" thickBot="1">
+      <c r="E12" s="54">
         <v>8.3144626180000003</v>
       </c>
     </row>
@@ -909,143 +1002,143 @@
       <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="14" t="s">
+      <c r="C1" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="56" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="11" t="s">
-        <v>35</v>
-      </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="37">
+      <c r="B2" s="35">
         <v>1.5</v>
       </c>
-      <c r="C2" s="20">
+      <c r="C2" s="19">
         <v>0.34499999999999997</v>
       </c>
-      <c r="D2" s="21">
+      <c r="D2" s="20">
         <v>0.05</v>
       </c>
-      <c r="E2" s="36">
+      <c r="E2" s="34">
         <f>G2/G4</f>
         <v>0.45381056300973421</v>
       </c>
-      <c r="F2" s="32">
+      <c r="F2" s="30">
         <f>C4-C3</f>
         <v>0.22799999999999998</v>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="21">
         <v>344.98678999999998</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="30"/>
-      <c r="B3" s="26">
+      <c r="A3" s="28"/>
+      <c r="B3" s="25">
         <v>2.5</v>
       </c>
-      <c r="C3" s="35">
+      <c r="C3" s="33">
         <v>0.56000000000000005</v>
       </c>
-      <c r="D3" s="18">
+      <c r="D3" s="17">
         <v>0.05</v>
       </c>
-      <c r="E3" s="36"/>
-      <c r="F3" s="32">
+      <c r="E3" s="34"/>
+      <c r="F3" s="30">
         <f>C7-C6</f>
         <v>0.22500000000000003</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="G3" s="22" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A4" s="31"/>
-      <c r="B4" s="27">
+      <c r="A4" s="29"/>
+      <c r="B4" s="26">
         <v>3.5</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="18">
         <v>0.78800000000000003</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="11">
         <v>0.05</v>
       </c>
-      <c r="E4" s="36"/>
-      <c r="F4" s="32">
+      <c r="E4" s="34"/>
+      <c r="F4" s="30">
         <f>C6-C5</f>
         <v>0.22</v>
       </c>
-      <c r="G4" s="24">
+      <c r="G4" s="23">
         <v>760.2</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="25">
         <v>1</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="33">
         <v>0.23</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="17">
         <v>0.05</v>
       </c>
-      <c r="E5" s="16"/>
-      <c r="F5" s="32">
+      <c r="E5" s="14"/>
+      <c r="F5" s="30">
         <f>C3-C2</f>
         <v>0.21500000000000008</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="30"/>
-      <c r="B6" s="26">
+      <c r="A6" s="28"/>
+      <c r="B6" s="25">
         <v>2</v>
       </c>
-      <c r="C6" s="35">
+      <c r="C6" s="33">
         <v>0.45</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="17">
         <v>0.05</v>
       </c>
-      <c r="E6" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="33">
+      <c r="E6" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="31">
         <f>AVERAGE(F2:F5)</f>
         <v>0.22200000000000003</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A7" s="31"/>
-      <c r="B7" s="27">
+      <c r="A7" s="29"/>
+      <c r="B7" s="26">
         <v>3</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="18">
         <v>0.67500000000000004</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="11">
         <v>0.05</v>
       </c>
-      <c r="E7" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="34">
+      <c r="E7" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="32">
         <f>2*F6</f>
         <v>0.44400000000000006</v>
       </c>
@@ -1069,179 +1162,182 @@
   <cols>
     <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="13.59765625" customWidth="1"/>
+    <col min="4" max="4" width="12.19921875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.86328125" customWidth="1"/>
     <col min="6" max="6" width="13.59765625" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="B1" s="28" t="s">
+    <row r="1" spans="1:8" ht="14.65" thickBot="1">
+      <c r="A1" s="15"/>
+      <c r="B1" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28" t="s">
+      <c r="C1" s="45"/>
+      <c r="D1" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="G1" s="28" t="s">
+      <c r="E1" s="45"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="28"/>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
+      <c r="H1" s="45"/>
+    </row>
+    <row r="2" spans="1:8" ht="14.65" thickBot="1">
+      <c r="A2" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="49" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="2">
+      <c r="A3" s="51">
         <v>1</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="34">
         <v>319.2</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="17">
         <v>5</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="14">
         <v>377</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="17">
         <v>5</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="51">
         <v>1</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="34">
         <v>760</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="2">
+      <c r="A4" s="51">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="34">
         <v>534.29999999999995</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="17">
         <v>5</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="14">
         <v>632</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="17">
         <v>5</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="51">
         <v>3</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="34">
         <v>1068</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="2">
+      <c r="A5" s="51">
         <v>5</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="34">
         <v>741.2</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="17">
         <v>6</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="14">
         <v>884</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="17">
         <v>6</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="51">
         <v>7</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="34">
         <v>1688</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="17">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="2">
+      <c r="A6" s="51">
         <v>7</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="34">
         <v>954.1</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="17">
         <v>6</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="14">
         <v>1146</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="17">
         <v>6</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="51">
         <v>9</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="34">
         <v>1990</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="17">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="2">
+    <row r="7" spans="1:8" ht="14.65" thickBot="1">
+      <c r="A7" s="52">
         <v>9</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="40">
         <v>1155.0999999999999</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="11">
         <v>6</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="23">
         <v>1404.5</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="11">
         <v>6</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="52">
         <v>11</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="40">
         <v>2290</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="11">
         <v>6</v>
       </c>
     </row>
@@ -1257,184 +1353,225 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{358E4CEC-525A-4BCF-91E4-363DE62CA86F}">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="14.86328125" customWidth="1"/>
+    <col min="4" max="4" width="18.53125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.3984375" customWidth="1"/>
-    <col min="8" max="8" width="12.86328125" customWidth="1"/>
+    <col min="8" max="9" width="18.53125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" ht="14.65" thickBot="1">
+      <c r="A1" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="43"/>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="D2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="F2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="G2" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="2">
+      <c r="H2" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="14.65" thickBot="1">
+      <c r="A3" s="38">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B3" s="34">
         <v>440.2</v>
       </c>
-      <c r="C2">
+      <c r="C3" s="34">
         <v>2</v>
       </c>
-      <c r="F2" s="2">
+      <c r="D3" s="6">
+        <v>1.45</v>
+      </c>
+      <c r="E3" s="38">
         <v>1</v>
       </c>
-      <c r="G2">
+      <c r="F3" s="34">
         <v>314.5</v>
       </c>
-      <c r="H2">
+      <c r="G3" s="34">
         <v>3</v>
       </c>
-      <c r="K2">
-        <v>83.8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="2">
+      <c r="H3" s="6">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="38">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B4" s="34">
         <v>549.5</v>
       </c>
-      <c r="C3">
+      <c r="C4" s="34">
         <v>2</v>
       </c>
-      <c r="F3" s="2">
+      <c r="D4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="38">
         <v>2</v>
       </c>
-      <c r="G3">
+      <c r="F4" s="34">
         <v>400</v>
       </c>
-      <c r="H3">
+      <c r="G4" s="34">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="2">
+      <c r="H4" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="14.65" thickBot="1">
+      <c r="A5" s="38">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B5" s="34">
         <v>659.5</v>
       </c>
-      <c r="C4">
+      <c r="C5" s="34">
         <v>2</v>
       </c>
-      <c r="F4" s="2">
+      <c r="D5" s="6">
+        <v>296.64999999999998</v>
+      </c>
+      <c r="E5" s="38">
         <v>3</v>
       </c>
-      <c r="G4">
+      <c r="F5" s="34">
         <v>500</v>
       </c>
-      <c r="H4">
+      <c r="G5" s="34">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="2">
+      <c r="H5" s="6">
+        <v>296.64999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="38">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B6" s="34">
         <v>769.5</v>
       </c>
-      <c r="C5">
+      <c r="C6" s="34">
         <v>2</v>
       </c>
-      <c r="F5" s="2">
+      <c r="D6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="38">
         <v>4</v>
       </c>
-      <c r="G5">
+      <c r="F6" s="34">
         <v>600</v>
       </c>
-      <c r="H5">
+      <c r="G6" s="34">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="2">
+      <c r="H6" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="14.65" thickBot="1">
+      <c r="A7" s="39">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B7" s="40">
         <v>882</v>
       </c>
-      <c r="C6">
+      <c r="C7" s="40">
         <v>2</v>
       </c>
-      <c r="F6" s="2">
+      <c r="D7" s="8">
+        <v>3.9947999999999997E-2</v>
+      </c>
+      <c r="E7" s="39">
         <v>5</v>
       </c>
-      <c r="G6">
+      <c r="F7" s="40">
         <v>700</v>
       </c>
-      <c r="H6">
+      <c r="G7" s="40">
         <v>1</v>
       </c>
+      <c r="H7" s="8">
+        <v>8.3797999999999997E-2</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:H1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF3685B9-F09A-4019-850A-B546C03596ED}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>1.57</v>
       </c>
@@ -1453,10 +1590,10 @@
         <v>348.88888888888891</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1.37</v>
       </c>
@@ -1475,7 +1612,7 @@
         <v>349.48979591836741</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>1.17</v>
       </c>
@@ -1494,7 +1631,7 @@
         <v>349.25373134328356</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>0.97</v>
       </c>
@@ -1513,7 +1650,7 @@
         <v>350.18050541516249</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>0.77</v>
       </c>
@@ -1532,7 +1669,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>0.56999999999999995</v>
       </c>
@@ -1551,7 +1688,7 @@
         <v>351.85185185185185</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>0.37</v>
       </c>
@@ -1586,13 +1723,13 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1675,75 +1812,75 @@
     </row>
     <row r="13" spans="1:7" ht="14.65" thickBot="1"/>
     <row r="14" spans="1:7">
-      <c r="A14" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="14" t="s">
+      <c r="A14" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C14" s="15" t="s">
-        <v>36</v>
+      <c r="C14" s="13" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="22">
+      <c r="A15" s="21">
         <v>344.98678999999998</v>
       </c>
-      <c r="B15" s="16">
+      <c r="B15" s="14">
         <v>1</v>
       </c>
-      <c r="C15" s="18">
+      <c r="C15" s="17">
         <f>A15/(2*A17)</f>
         <v>0.22690528150486711</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="24">
         <v>1.5</v>
       </c>
-      <c r="C16" s="18">
+      <c r="C16" s="17">
         <f>3*A15/(4*A17)</f>
         <v>0.34035792225730072</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.65" thickBot="1">
-      <c r="A17" s="24">
+      <c r="A17" s="23">
         <v>760.2</v>
       </c>
-      <c r="B17" s="16">
+      <c r="B17" s="14">
         <v>2</v>
       </c>
-      <c r="C17" s="18">
+      <c r="C17" s="17">
         <f>A15/A17</f>
         <v>0.45381056300973421</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="B18" s="26">
+      <c r="B18" s="25">
         <v>2.5</v>
       </c>
-      <c r="C18" s="18">
+      <c r="C18" s="17">
         <f>(5*A15)/(4*A17)</f>
         <v>0.56726320376216777</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="B19" s="25">
+      <c r="B19" s="24">
         <v>3</v>
       </c>
-      <c r="C19" s="18">
+      <c r="C19" s="17">
         <f>3*A15/(2*A17)</f>
         <v>0.68071584451460143</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="14.65" thickBot="1">
-      <c r="B20" s="27">
+      <c r="B20" s="26">
         <v>3.5</v>
       </c>
-      <c r="C20" s="13">
+      <c r="C20" s="11">
         <f>(A15*7)/(4*A17)</f>
         <v>0.79416848526703487</v>
       </c>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="770" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{070CFC06-9C8F-4F9D-95EF-55E3BD663ECA}"/>
+  <xr:revisionPtr revIDLastSave="784" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{198CB006-340A-4603-88B1-BA1345A4DBEC}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
@@ -1411,7 +1411,7 @@
         <v>440.2</v>
       </c>
       <c r="C3" s="34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="6">
         <v>1.45</v>
@@ -1431,19 +1431,19 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="34">
         <v>549.5</v>
       </c>
       <c r="C4" s="34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E4" s="38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" s="34">
         <v>400</v>
@@ -1457,25 +1457,25 @@
     </row>
     <row r="5" spans="1:8" ht="14.65" thickBot="1">
       <c r="A5" s="38">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B5" s="34">
         <v>659.5</v>
       </c>
       <c r="C5" s="34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="6">
         <v>296.64999999999998</v>
       </c>
       <c r="E5" s="38">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F5" s="34">
         <v>500</v>
       </c>
       <c r="G5" s="34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H5" s="6">
         <v>296.64999999999998</v>
@@ -1483,25 +1483,25 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="38">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B6" s="34">
         <v>769.5</v>
       </c>
       <c r="C6" s="34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>39</v>
       </c>
       <c r="E6" s="38">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F6" s="34">
         <v>600</v>
       </c>
       <c r="G6" s="34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>39</v>
@@ -1509,25 +1509,25 @@
     </row>
     <row r="7" spans="1:8" ht="14.65" thickBot="1">
       <c r="A7" s="39">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B7" s="40">
         <v>882</v>
       </c>
-      <c r="C7" s="40">
-        <v>2</v>
+      <c r="C7" s="11">
+        <v>3</v>
       </c>
       <c r="D7" s="8">
         <v>3.9947999999999997E-2</v>
       </c>
       <c r="E7" s="39">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F7" s="40">
         <v>700</v>
       </c>
-      <c r="G7" s="40">
-        <v>1</v>
+      <c r="G7" s="11">
+        <v>3</v>
       </c>
       <c r="H7" s="8">
         <v>8.3797999999999997E-2</v>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="784" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{198CB006-340A-4603-88B1-BA1345A4DBEC}"/>
+  <xr:revisionPtr revIDLastSave="788" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA0D7E80-FBC0-4F40-AE30-404E876B9EE2}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
@@ -1411,7 +1411,7 @@
         <v>440.2</v>
       </c>
       <c r="C3" s="34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="6">
         <v>1.45</v>
@@ -1423,7 +1423,7 @@
         <v>314.5</v>
       </c>
       <c r="G3" s="34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3" s="6">
         <v>1.45</v>
@@ -1437,7 +1437,7 @@
         <v>549.5</v>
       </c>
       <c r="C4" s="34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>38</v>
@@ -1449,7 +1449,7 @@
         <v>400</v>
       </c>
       <c r="G4" s="34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>38</v>
@@ -1463,7 +1463,7 @@
         <v>659.5</v>
       </c>
       <c r="C5" s="34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="6">
         <v>296.64999999999998</v>
@@ -1475,7 +1475,7 @@
         <v>500</v>
       </c>
       <c r="G5" s="34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5" s="6">
         <v>296.64999999999998</v>
@@ -1489,7 +1489,7 @@
         <v>769.5</v>
       </c>
       <c r="C6" s="34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>39</v>
@@ -1501,7 +1501,7 @@
         <v>600</v>
       </c>
       <c r="G6" s="34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>39</v>
@@ -1514,8 +1514,8 @@
       <c r="B7" s="40">
         <v>882</v>
       </c>
-      <c r="C7" s="11">
-        <v>3</v>
+      <c r="C7" s="34">
+        <v>4</v>
       </c>
       <c r="D7" s="8">
         <v>3.9947999999999997E-2</v>
@@ -1526,8 +1526,8 @@
       <c r="F7" s="40">
         <v>700</v>
       </c>
-      <c r="G7" s="11">
-        <v>3</v>
+      <c r="G7" s="34">
+        <v>4</v>
       </c>
       <c r="H7" s="8">
         <v>8.3797999999999997E-2</v>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="788" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA0D7E80-FBC0-4F40-AE30-404E876B9EE2}"/>
+  <xr:revisionPtr revIDLastSave="808" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8838932-39A3-40B6-80F4-CACE801FCD52}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="40">
   <si>
     <t>n</t>
   </si>
@@ -115,12 +115,6 @@
     <t>Temperatura stanza (k)</t>
   </si>
   <si>
-    <t>Massa molare aria (g/mol)</t>
-  </si>
-  <si>
-    <t>Incertezza (g/mol)</t>
-  </si>
-  <si>
     <t>γ</t>
   </si>
   <si>
@@ -161,6 +155,12 @@
   </si>
   <si>
     <t>Massa molare (kg/mol)</t>
+  </si>
+  <si>
+    <t>Massa molare aria (kg/mol)</t>
+  </si>
+  <si>
+    <t>Incertezza (kg/mol)</t>
   </si>
 </sst>
 </file>
@@ -417,7 +417,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -462,6 +462,7 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="12" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="12" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
@@ -887,7 +888,7 @@
         <v>21</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -921,7 +922,7 @@
         <v>22</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="14.65" thickBot="1">
@@ -946,7 +947,7 @@
         <v>21</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="14.65" thickBot="1">
@@ -959,7 +960,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="E9" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -968,12 +969,12 @@
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="E11" s="53" t="s">
-        <v>27</v>
+      <c r="E11" s="54" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="14.65" thickBot="1">
-      <c r="E12" s="54">
+      <c r="E12" s="55">
         <v>8.3144626180000003</v>
       </c>
     </row>
@@ -1006,19 +1007,19 @@
         <v>0</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D1" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="55" t="s">
+      <c r="E1" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="56" t="s">
-        <v>29</v>
+      <c r="F1" s="57" t="s">
+        <v>27</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -1117,7 +1118,7 @@
         <v>0.05</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F6" s="31">
         <f>AVERAGE(F2:F5)</f>
@@ -1136,7 +1137,7 @@
         <v>0.05</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F7" s="32">
         <f>2*F6</f>
@@ -1171,48 +1172,48 @@
   <sheetData>
     <row r="1" spans="1:8" ht="14.65" thickBot="1">
       <c r="A1" s="15"/>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="45"/>
-      <c r="D1" s="44" t="s">
+      <c r="C1" s="46"/>
+      <c r="D1" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="45"/>
+      <c r="E1" s="46"/>
       <c r="F1" s="15"/>
-      <c r="G1" s="44" t="s">
+      <c r="G1" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="45"/>
+      <c r="H1" s="46"/>
     </row>
     <row r="2" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="49" t="s">
+      <c r="C2" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="47" t="s">
+      <c r="D2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="49" t="s">
+      <c r="E2" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="47" t="s">
+      <c r="F2" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="47" t="s">
+      <c r="G2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="49" t="s">
+      <c r="H2" s="50" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="51">
+      <c r="A3" s="52">
         <v>1</v>
       </c>
       <c r="B3" s="34">
@@ -1227,7 +1228,7 @@
       <c r="E3" s="17">
         <v>5</v>
       </c>
-      <c r="F3" s="51">
+      <c r="F3" s="52">
         <v>1</v>
       </c>
       <c r="G3" s="34">
@@ -1238,7 +1239,7 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="51">
+      <c r="A4" s="52">
         <v>3</v>
       </c>
       <c r="B4" s="34">
@@ -1253,7 +1254,7 @@
       <c r="E4" s="17">
         <v>5</v>
       </c>
-      <c r="F4" s="51">
+      <c r="F4" s="52">
         <v>3</v>
       </c>
       <c r="G4" s="34">
@@ -1264,7 +1265,7 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="51">
+      <c r="A5" s="52">
         <v>5</v>
       </c>
       <c r="B5" s="34">
@@ -1279,7 +1280,7 @@
       <c r="E5" s="17">
         <v>6</v>
       </c>
-      <c r="F5" s="51">
+      <c r="F5" s="52">
         <v>7</v>
       </c>
       <c r="G5" s="34">
@@ -1290,7 +1291,7 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="51">
+      <c r="A6" s="52">
         <v>7</v>
       </c>
       <c r="B6" s="34">
@@ -1305,7 +1306,7 @@
       <c r="E6" s="17">
         <v>6</v>
       </c>
-      <c r="F6" s="51">
+      <c r="F6" s="52">
         <v>9</v>
       </c>
       <c r="G6" s="34">
@@ -1316,10 +1317,10 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A7" s="52">
+      <c r="A7" s="53">
         <v>9</v>
       </c>
-      <c r="B7" s="40">
+      <c r="B7" s="41">
         <v>1155.0999999999999</v>
       </c>
       <c r="C7" s="11">
@@ -1331,10 +1332,10 @@
       <c r="E7" s="11">
         <v>6</v>
       </c>
-      <c r="F7" s="52">
+      <c r="F7" s="53">
         <v>11</v>
       </c>
-      <c r="G7" s="40">
+      <c r="G7" s="41">
         <v>2290</v>
       </c>
       <c r="H7" s="11">
@@ -1353,58 +1354,60 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{358E4CEC-525A-4BCF-91E4-363DE62CA86F}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="14.86328125" customWidth="1"/>
-    <col min="4" max="4" width="18.53125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.19921875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.3984375" customWidth="1"/>
-    <col min="8" max="9" width="18.53125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.53125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A1" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="41" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="43"/>
+      <c r="A1" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="44"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="38" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="37" t="s">
+      <c r="F2" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="37" t="s">
+      <c r="G2" s="38" t="s">
         <v>2</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A3" s="38">
+      <c r="A3" s="39">
         <v>1</v>
       </c>
       <c r="B3" s="34">
@@ -1416,7 +1419,7 @@
       <c r="D3" s="6">
         <v>1.45</v>
       </c>
-      <c r="E3" s="38">
+      <c r="E3" s="39">
         <v>1</v>
       </c>
       <c r="F3" s="34">
@@ -1430,7 +1433,7 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="38">
+      <c r="A4" s="39">
         <v>3</v>
       </c>
       <c r="B4" s="34">
@@ -1440,9 +1443,9 @@
         <v>4</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="38">
+        <v>36</v>
+      </c>
+      <c r="E4" s="39">
         <v>3</v>
       </c>
       <c r="F4" s="34">
@@ -1452,11 +1455,11 @@
         <v>4</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A5" s="38">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="39">
         <v>5</v>
       </c>
       <c r="B5" s="34">
@@ -1468,7 +1471,7 @@
       <c r="D5" s="6">
         <v>296.64999999999998</v>
       </c>
-      <c r="E5" s="38">
+      <c r="E5" s="39">
         <v>5</v>
       </c>
       <c r="F5" s="34">
@@ -1482,7 +1485,7 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="38">
+      <c r="A6" s="39">
         <v>7</v>
       </c>
       <c r="B6" s="34">
@@ -1492,9 +1495,9 @@
         <v>4</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" s="38">
+        <v>26</v>
+      </c>
+      <c r="E6" s="39">
         <v>7</v>
       </c>
       <c r="F6" s="34">
@@ -1503,34 +1506,82 @@
       <c r="G6" s="34">
         <v>4</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="14.65" thickBot="1">
+      <c r="A7" s="40">
+        <v>9</v>
+      </c>
+      <c r="B7" s="41">
+        <v>882</v>
+      </c>
+      <c r="C7" s="11">
+        <v>4</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="E7" s="40">
+        <v>9</v>
+      </c>
+      <c r="F7" s="41">
+        <v>700</v>
+      </c>
+      <c r="G7" s="41">
+        <v>4</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="D8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="14.65" thickBot="1">
+      <c r="D9" s="8">
+        <v>3.9947999999999997E-2</v>
+      </c>
+      <c r="H9" s="8">
+        <v>8.3797999999999997E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="D10" s="7" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A7" s="39">
-        <v>9</v>
-      </c>
-      <c r="B7" s="40">
-        <v>882</v>
-      </c>
-      <c r="C7" s="34">
-        <v>4</v>
-      </c>
-      <c r="D7" s="8">
-        <v>3.9947999999999997E-2</v>
-      </c>
-      <c r="E7" s="39">
-        <v>9</v>
-      </c>
-      <c r="F7" s="40">
-        <v>700</v>
-      </c>
-      <c r="G7" s="34">
-        <v>4</v>
-      </c>
-      <c r="H7" s="8">
-        <v>8.3797999999999997E-2</v>
+      <c r="H10" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="D11" s="6">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="H11" s="6">
+        <v>5.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="D12" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="14.65" thickBot="1">
+      <c r="D13" s="36">
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="H13" s="36">
+        <v>1.6666666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -1569,7 +1620,7 @@
       <c r="F1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="36"/>
+      <c r="G1" s="37"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
@@ -1813,13 +1864,13 @@
     <row r="13" spans="1:7" ht="14.65" thickBot="1"/>
     <row r="14" spans="1:7">
       <c r="A14" s="9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>0</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:7">

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="808" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8838932-39A3-40B6-80F4-CACE801FCD52}"/>
+  <xr:revisionPtr revIDLastSave="813" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A6EFD28-7B8F-4CC5-8CC6-D59B0570CE94}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
@@ -417,7 +417,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -466,7 +466,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -969,12 +968,12 @@
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="E11" s="54" t="s">
+      <c r="E11" s="53" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="14.65" thickBot="1">
-      <c r="E12" s="55">
+      <c r="E12" s="54">
         <v>8.3144626180000003</v>
       </c>
     </row>
@@ -1012,10 +1011,10 @@
       <c r="D1" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="56" t="s">
+      <c r="E1" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="57" t="s">
+      <c r="F1" s="56" t="s">
         <v>27</v>
       </c>
       <c r="G1" s="9" t="s">
@@ -1172,48 +1171,48 @@
   <sheetData>
     <row r="1" spans="1:8" ht="14.65" thickBot="1">
       <c r="A1" s="15"/>
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="46"/>
-      <c r="D1" s="45" t="s">
+      <c r="C1" s="45"/>
+      <c r="D1" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="46"/>
+      <c r="E1" s="45"/>
       <c r="F1" s="15"/>
-      <c r="G1" s="45" t="s">
+      <c r="G1" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="46"/>
+      <c r="H1" s="45"/>
     </row>
     <row r="2" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="C2" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="48" t="s">
+      <c r="D2" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="50" t="s">
+      <c r="E2" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="48" t="s">
+      <c r="F2" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="48" t="s">
+      <c r="G2" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="50" t="s">
+      <c r="H2" s="49" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="52">
+      <c r="A3" s="51">
         <v>1</v>
       </c>
       <c r="B3" s="34">
@@ -1228,7 +1227,7 @@
       <c r="E3" s="17">
         <v>5</v>
       </c>
-      <c r="F3" s="52">
+      <c r="F3" s="51">
         <v>1</v>
       </c>
       <c r="G3" s="34">
@@ -1239,7 +1238,7 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="52">
+      <c r="A4" s="51">
         <v>3</v>
       </c>
       <c r="B4" s="34">
@@ -1254,7 +1253,7 @@
       <c r="E4" s="17">
         <v>5</v>
       </c>
-      <c r="F4" s="52">
+      <c r="F4" s="51">
         <v>3</v>
       </c>
       <c r="G4" s="34">
@@ -1265,7 +1264,7 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="52">
+      <c r="A5" s="51">
         <v>5</v>
       </c>
       <c r="B5" s="34">
@@ -1280,7 +1279,7 @@
       <c r="E5" s="17">
         <v>6</v>
       </c>
-      <c r="F5" s="52">
+      <c r="F5" s="51">
         <v>7</v>
       </c>
       <c r="G5" s="34">
@@ -1291,7 +1290,7 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="52">
+      <c r="A6" s="51">
         <v>7</v>
       </c>
       <c r="B6" s="34">
@@ -1306,7 +1305,7 @@
       <c r="E6" s="17">
         <v>6</v>
       </c>
-      <c r="F6" s="52">
+      <c r="F6" s="51">
         <v>9</v>
       </c>
       <c r="G6" s="34">
@@ -1317,10 +1316,10 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A7" s="53">
+      <c r="A7" s="52">
         <v>9</v>
       </c>
-      <c r="B7" s="41">
+      <c r="B7" s="40">
         <v>1155.0999999999999</v>
       </c>
       <c r="C7" s="11">
@@ -1332,10 +1331,10 @@
       <c r="E7" s="11">
         <v>6</v>
       </c>
-      <c r="F7" s="53">
+      <c r="F7" s="52">
         <v>11</v>
       </c>
-      <c r="G7" s="41">
+      <c r="G7" s="40">
         <v>2290</v>
       </c>
       <c r="H7" s="11">
@@ -1367,18 +1366,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="42" t="s">
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="44"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="43"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="9" t="s">
@@ -1434,7 +1433,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="34">
         <v>549.5</v>
@@ -1446,7 +1445,7 @@
         <v>36</v>
       </c>
       <c r="E4" s="39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" s="34">
         <v>400</v>
@@ -1460,7 +1459,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="39">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B5" s="34">
         <v>659.5</v>
@@ -1472,7 +1471,7 @@
         <v>296.64999999999998</v>
       </c>
       <c r="E5" s="39">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5" s="34">
         <v>500</v>
@@ -1486,7 +1485,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="39">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B6" s="34">
         <v>769.5</v>
@@ -1498,7 +1497,7 @@
         <v>26</v>
       </c>
       <c r="E6" s="39">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F6" s="34">
         <v>600</v>
@@ -1511,10 +1510,10 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A7" s="40">
-        <v>9</v>
-      </c>
-      <c r="B7" s="41">
+      <c r="A7" s="39">
+        <v>5</v>
+      </c>
+      <c r="B7" s="40">
         <v>882</v>
       </c>
       <c r="C7" s="11">
@@ -1523,13 +1522,13 @@
       <c r="D7" s="6">
         <v>0.5</v>
       </c>
-      <c r="E7" s="40">
-        <v>9</v>
-      </c>
-      <c r="F7" s="41">
+      <c r="E7" s="39">
+        <v>5</v>
+      </c>
+      <c r="F7" s="40">
         <v>700</v>
       </c>
-      <c r="G7" s="41">
+      <c r="G7" s="40">
         <v>4</v>
       </c>
       <c r="H7" s="6">

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="813" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A6EFD28-7B8F-4CC5-8CC6-D59B0570CE94}"/>
+  <xr:revisionPtr revIDLastSave="826" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FE062A9-A5FB-4A5B-9FCF-134333A645ED}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="4" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Aria (tubo aperto)" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="38">
   <si>
     <t>n</t>
   </si>
@@ -76,27 +76,15 @@
     <t>65 cm</t>
   </si>
   <si>
-    <t>x</t>
-  </si>
-  <si>
     <t>Delta T_1</t>
   </si>
   <si>
     <t>Delta T_2</t>
   </si>
   <si>
-    <t>v_1</t>
-  </si>
-  <si>
-    <t>v_2</t>
-  </si>
-  <si>
     <t>incertezza su Δt</t>
   </si>
   <si>
-    <t>0,1 ms</t>
-  </si>
-  <si>
     <t>Frequenza hz</t>
   </si>
   <si>
@@ -161,6 +149,12 @@
   </si>
   <si>
     <t>Incertezza (kg/mol)</t>
+  </si>
+  <si>
+    <t>x (m)</t>
+  </si>
+  <si>
+    <t>Δt medio (s)</t>
   </si>
 </sst>
 </file>
@@ -417,7 +411,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -463,7 +457,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="12" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="12" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
@@ -853,7 +846,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -884,10 +877,10 @@
         <v>3.5</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -918,10 +911,10 @@
         <v>4</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="14.65" thickBot="1">
@@ -943,10 +936,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="D7" s="22" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="14.65" thickBot="1">
@@ -959,7 +952,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="E9" s="7" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -968,12 +961,12 @@
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="E11" s="53" t="s">
-        <v>25</v>
+      <c r="E11" s="52" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="14.65" thickBot="1">
-      <c r="E12" s="54">
+      <c r="E12" s="53">
         <v>8.3144626180000003</v>
       </c>
     </row>
@@ -1006,19 +999,19 @@
         <v>0</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="56" t="s">
-        <v>27</v>
+      <c r="F1" s="55" t="s">
+        <v>23</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -1117,7 +1110,7 @@
         <v>0.05</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F6" s="31">
         <f>AVERAGE(F2:F5)</f>
@@ -1136,7 +1129,7 @@
         <v>0.05</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F7" s="32">
         <f>2*F6</f>
@@ -1171,48 +1164,48 @@
   <sheetData>
     <row r="1" spans="1:8" ht="14.65" thickBot="1">
       <c r="A1" s="15"/>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="45"/>
-      <c r="D1" s="44" t="s">
+      <c r="C1" s="44"/>
+      <c r="D1" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="45"/>
+      <c r="E1" s="44"/>
       <c r="F1" s="15"/>
-      <c r="G1" s="44" t="s">
+      <c r="G1" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="45"/>
+      <c r="H1" s="44"/>
     </row>
     <row r="2" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="49" t="s">
+      <c r="C2" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="47" t="s">
+      <c r="D2" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="49" t="s">
+      <c r="E2" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="47" t="s">
+      <c r="F2" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="47" t="s">
+      <c r="G2" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="49" t="s">
+      <c r="H2" s="48" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="51">
+      <c r="A3" s="50">
         <v>1</v>
       </c>
       <c r="B3" s="34">
@@ -1227,7 +1220,7 @@
       <c r="E3" s="17">
         <v>5</v>
       </c>
-      <c r="F3" s="51">
+      <c r="F3" s="50">
         <v>1</v>
       </c>
       <c r="G3" s="34">
@@ -1238,7 +1231,7 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="51">
+      <c r="A4" s="50">
         <v>3</v>
       </c>
       <c r="B4" s="34">
@@ -1253,7 +1246,7 @@
       <c r="E4" s="17">
         <v>5</v>
       </c>
-      <c r="F4" s="51">
+      <c r="F4" s="50">
         <v>3</v>
       </c>
       <c r="G4" s="34">
@@ -1264,7 +1257,7 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="51">
+      <c r="A5" s="50">
         <v>5</v>
       </c>
       <c r="B5" s="34">
@@ -1279,7 +1272,7 @@
       <c r="E5" s="17">
         <v>6</v>
       </c>
-      <c r="F5" s="51">
+      <c r="F5" s="50">
         <v>7</v>
       </c>
       <c r="G5" s="34">
@@ -1290,7 +1283,7 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="51">
+      <c r="A6" s="50">
         <v>7</v>
       </c>
       <c r="B6" s="34">
@@ -1305,7 +1298,7 @@
       <c r="E6" s="17">
         <v>6</v>
       </c>
-      <c r="F6" s="51">
+      <c r="F6" s="50">
         <v>9</v>
       </c>
       <c r="G6" s="34">
@@ -1316,10 +1309,10 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A7" s="52">
+      <c r="A7" s="51">
         <v>9</v>
       </c>
-      <c r="B7" s="40">
+      <c r="B7" s="39">
         <v>1155.0999999999999</v>
       </c>
       <c r="C7" s="11">
@@ -1331,10 +1324,10 @@
       <c r="E7" s="11">
         <v>6</v>
       </c>
-      <c r="F7" s="52">
+      <c r="F7" s="51">
         <v>11</v>
       </c>
-      <c r="G7" s="40">
+      <c r="G7" s="39">
         <v>2290</v>
       </c>
       <c r="H7" s="11">
@@ -1366,47 +1359,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A1" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="43"/>
+      <c r="A1" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="42"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="38" t="s">
+      <c r="C2" s="37" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="38" t="s">
+      <c r="F2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="38" t="s">
+      <c r="G2" s="37" t="s">
         <v>2</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A3" s="39">
+      <c r="A3" s="38">
         <v>1</v>
       </c>
       <c r="B3" s="34">
@@ -1418,7 +1411,7 @@
       <c r="D3" s="6">
         <v>1.45</v>
       </c>
-      <c r="E3" s="39">
+      <c r="E3" s="38">
         <v>1</v>
       </c>
       <c r="F3" s="34">
@@ -1432,7 +1425,7 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="39">
+      <c r="A4" s="38">
         <v>2</v>
       </c>
       <c r="B4" s="34">
@@ -1442,9 +1435,9 @@
         <v>4</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="39">
+        <v>32</v>
+      </c>
+      <c r="E4" s="38">
         <v>2</v>
       </c>
       <c r="F4" s="34">
@@ -1454,11 +1447,11 @@
         <v>4</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="39">
+      <c r="A5" s="38">
         <v>3</v>
       </c>
       <c r="B5" s="34">
@@ -1470,7 +1463,7 @@
       <c r="D5" s="6">
         <v>296.64999999999998</v>
       </c>
-      <c r="E5" s="39">
+      <c r="E5" s="38">
         <v>3</v>
       </c>
       <c r="F5" s="34">
@@ -1484,7 +1477,7 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="39">
+      <c r="A6" s="38">
         <v>4</v>
       </c>
       <c r="B6" s="34">
@@ -1494,9 +1487,9 @@
         <v>4</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="39">
+        <v>22</v>
+      </c>
+      <c r="E6" s="38">
         <v>4</v>
       </c>
       <c r="F6" s="34">
@@ -1506,14 +1499,14 @@
         <v>4</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A7" s="39">
+      <c r="A7" s="38">
         <v>5</v>
       </c>
-      <c r="B7" s="40">
+      <c r="B7" s="39">
         <v>882</v>
       </c>
       <c r="C7" s="11">
@@ -1522,13 +1515,13 @@
       <c r="D7" s="6">
         <v>0.5</v>
       </c>
-      <c r="E7" s="39">
+      <c r="E7" s="38">
         <v>5</v>
       </c>
-      <c r="F7" s="40">
+      <c r="F7" s="39">
         <v>700</v>
       </c>
-      <c r="G7" s="40">
+      <c r="G7" s="39">
         <v>4</v>
       </c>
       <c r="H7" s="6">
@@ -1537,10 +1530,10 @@
     </row>
     <row r="8" spans="1:8">
       <c r="D8" s="7" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="14.65" thickBot="1">
@@ -1553,10 +1546,10 @@
     </row>
     <row r="10" spans="1:8">
       <c r="D10" s="7" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1569,10 +1562,10 @@
     </row>
     <row r="12" spans="1:8">
       <c r="D12" s="7" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="14.65" thickBot="1">
@@ -1594,34 +1587,31 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF3685B9-F09A-4019-850A-B546C03596ED}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.06640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="37"/>
-    </row>
-    <row r="2" spans="1:7">
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1.57</v>
       </c>
@@ -1632,18 +1622,14 @@
         <v>4.4999999999999997E-3</v>
       </c>
       <c r="D2">
-        <f t="shared" ref="D2:D8" si="0">A2/B2</f>
-        <v>348.88888888888891</v>
+        <f>AVERAGE(B2:C2)</f>
+        <v>4.4999999999999997E-3</v>
       </c>
       <c r="E2">
-        <f>A2/C2</f>
-        <v>348.88888888888891</v>
-      </c>
-      <c r="F2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>5.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1.37</v>
       </c>
@@ -1654,15 +1640,11 @@
         <v>3.9199999999999999E-3</v>
       </c>
       <c r="D3">
-        <f t="shared" si="0"/>
-        <v>349.48979591836741</v>
-      </c>
-      <c r="E3">
-        <f t="shared" ref="E3:E8" si="1">A3/C3</f>
-        <v>349.48979591836741</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <f t="shared" ref="D3:D8" si="0">AVERAGE(B3:C3)</f>
+        <v>3.9199999999999999E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>1.17</v>
       </c>
@@ -1674,14 +1656,10 @@
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>348.21428571428567</v>
-      </c>
-      <c r="E4">
-        <f t="shared" si="1"/>
-        <v>349.25373134328356</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>3.3550000000000003E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>0.97</v>
       </c>
@@ -1693,14 +1671,10 @@
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>347.67025089605733</v>
-      </c>
-      <c r="E5">
-        <f t="shared" si="1"/>
-        <v>350.18050541516249</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>2.7799999999999999E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>0.77</v>
       </c>
@@ -1712,14 +1686,10 @@
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>350</v>
-      </c>
-      <c r="E6">
-        <f t="shared" si="1"/>
-        <v>350</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>2.2000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>0.56999999999999995</v>
       </c>
@@ -1731,14 +1701,10 @@
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>351.85185185185185</v>
-      </c>
-      <c r="E7">
-        <f t="shared" si="1"/>
-        <v>351.85185185185185</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>1.6199999999999999E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>0.37</v>
       </c>
@@ -1750,11 +1716,7 @@
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
-        <v>352.38095238095241</v>
-      </c>
-      <c r="E8">
-        <f t="shared" si="1"/>
-        <v>355.76923076923077</v>
+        <v>1.0449999999999999E-3</v>
       </c>
     </row>
   </sheetData>
@@ -1773,13 +1735,13 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1863,13 +1825,13 @@
     <row r="13" spans="1:7" ht="14.65" thickBot="1"/>
     <row r="14" spans="1:7">
       <c r="A14" s="9" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>0</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:7">

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="826" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FE062A9-A5FB-4A5B-9FCF-134333A645ED}"/>
+  <xr:revisionPtr revIDLastSave="845" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D8EC28D-ACCD-4E3E-AF77-24C7443C8A5C}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="4" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="5" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Aria (tubo aperto)" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Aria (tubo chiuso)" sheetId="2" r:id="rId3"/>
     <sheet name="Argon e Kripton" sheetId="3" r:id="rId4"/>
     <sheet name="Onde quadre-riflessione" sheetId="4" r:id="rId5"/>
-    <sheet name="Punto 5" sheetId="5" r:id="rId6"/>
+    <sheet name="Ampiezza e fase" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="36">
   <si>
     <t>n</t>
   </si>
@@ -82,18 +82,12 @@
     <t>Delta T_2</t>
   </si>
   <si>
-    <t>incertezza su Δt</t>
-  </si>
-  <si>
     <t>Frequenza hz</t>
   </si>
   <si>
     <t>Ampiezza  V</t>
   </si>
   <si>
-    <t>Dt micro s</t>
-  </si>
-  <si>
     <t>Incertezza (m)</t>
   </si>
   <si>
@@ -124,9 +118,6 @@
     <t>V suono (m/s)</t>
   </si>
   <si>
-    <t>Posizione teorica (m)</t>
-  </si>
-  <si>
     <t>Distanza (m)</t>
   </si>
   <si>
@@ -155,20 +146,22 @@
   </si>
   <si>
     <t>Δt medio (s)</t>
+  </si>
+  <si>
+    <t>Δt micro (μs)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.000000000"/>
     <numFmt numFmtId="166" formatCode="#,##0.00000"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -178,13 +171,6 @@
     </font>
     <font>
       <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -407,9 +393,8 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -433,12 +418,11 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="12" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="12" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="12" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -488,9 +472,9 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Migliaia" xfId="1" builtinId="3"/>
+  <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -846,7 +830,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -877,10 +861,10 @@
         <v>3.5</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -911,10 +895,10 @@
         <v>4</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="14.65" thickBot="1">
@@ -936,10 +920,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="D7" s="22" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="14.65" thickBot="1">
@@ -952,7 +936,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="E9" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -961,12 +945,12 @@
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="E11" s="52" t="s">
-        <v>21</v>
+      <c r="E11" s="51" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="14.65" thickBot="1">
-      <c r="E12" s="53">
+      <c r="E12" s="52">
         <v>8.3144626180000003</v>
       </c>
     </row>
@@ -999,26 +983,26 @@
         <v>0</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="55" t="s">
-        <v>23</v>
+      <c r="F1" s="54" t="s">
+        <v>21</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="35">
+      <c r="B2" s="34">
         <v>1.5</v>
       </c>
       <c r="C2" s="19">
@@ -1027,11 +1011,11 @@
       <c r="D2" s="20">
         <v>0.05</v>
       </c>
-      <c r="E2" s="34">
+      <c r="E2" s="33">
         <f>G2/G4</f>
         <v>0.45381056300973421</v>
       </c>
-      <c r="F2" s="30">
+      <c r="F2" s="29">
         <f>C4-C3</f>
         <v>0.22799999999999998</v>
       </c>
@@ -1040,18 +1024,18 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="28"/>
-      <c r="B3" s="25">
+      <c r="A3" s="27"/>
+      <c r="B3" s="24">
         <v>2.5</v>
       </c>
-      <c r="C3" s="33">
+      <c r="C3" s="32">
         <v>0.56000000000000005</v>
       </c>
       <c r="D3" s="17">
         <v>0.05</v>
       </c>
-      <c r="E3" s="34"/>
-      <c r="F3" s="30">
+      <c r="E3" s="33"/>
+      <c r="F3" s="29">
         <f>C7-C6</f>
         <v>0.22500000000000003</v>
       </c>
@@ -1060,8 +1044,8 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A4" s="29"/>
-      <c r="B4" s="26">
+      <c r="A4" s="28"/>
+      <c r="B4" s="25">
         <v>3.5</v>
       </c>
       <c r="C4" s="18">
@@ -1070,8 +1054,8 @@
       <c r="D4" s="11">
         <v>0.05</v>
       </c>
-      <c r="E4" s="34"/>
-      <c r="F4" s="30">
+      <c r="E4" s="33"/>
+      <c r="F4" s="29">
         <f>C6-C5</f>
         <v>0.22</v>
       </c>
@@ -1080,46 +1064,46 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="25">
+      <c r="B5" s="24">
         <v>1</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="32">
         <v>0.23</v>
       </c>
       <c r="D5" s="17">
         <v>0.05</v>
       </c>
       <c r="E5" s="14"/>
-      <c r="F5" s="30">
+      <c r="F5" s="29">
         <f>C3-C2</f>
         <v>0.21500000000000008</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="28"/>
-      <c r="B6" s="25">
+      <c r="A6" s="27"/>
+      <c r="B6" s="24">
         <v>2</v>
       </c>
-      <c r="C6" s="33">
+      <c r="C6" s="32">
         <v>0.45</v>
       </c>
       <c r="D6" s="17">
         <v>0.05</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="31">
+        <v>22</v>
+      </c>
+      <c r="F6" s="30">
         <f>AVERAGE(F2:F5)</f>
         <v>0.22200000000000003</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A7" s="29"/>
-      <c r="B7" s="26">
+      <c r="A7" s="28"/>
+      <c r="B7" s="25">
         <v>3</v>
       </c>
       <c r="C7" s="18">
@@ -1129,9 +1113,9 @@
         <v>0.05</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="32">
+        <v>23</v>
+      </c>
+      <c r="F7" s="31">
         <f>2*F6</f>
         <v>0.44400000000000006</v>
       </c>
@@ -1164,51 +1148,51 @@
   <sheetData>
     <row r="1" spans="1:8" ht="14.65" thickBot="1">
       <c r="A1" s="15"/>
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="44"/>
-      <c r="D1" s="43" t="s">
+      <c r="C1" s="43"/>
+      <c r="D1" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="44"/>
+      <c r="E1" s="43"/>
       <c r="F1" s="15"/>
-      <c r="G1" s="43" t="s">
+      <c r="G1" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="44"/>
+      <c r="H1" s="43"/>
     </row>
     <row r="2" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="46" t="s">
+      <c r="D2" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="48" t="s">
+      <c r="E2" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="46" t="s">
+      <c r="F2" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="46" t="s">
+      <c r="G2" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="48" t="s">
+      <c r="H2" s="47" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="50">
+      <c r="A3" s="49">
         <v>1</v>
       </c>
-      <c r="B3" s="34">
+      <c r="B3" s="33">
         <v>319.2</v>
       </c>
       <c r="C3" s="17">
@@ -1220,10 +1204,10 @@
       <c r="E3" s="17">
         <v>5</v>
       </c>
-      <c r="F3" s="50">
+      <c r="F3" s="49">
         <v>1</v>
       </c>
-      <c r="G3" s="34">
+      <c r="G3" s="33">
         <v>760</v>
       </c>
       <c r="H3" s="17">
@@ -1231,10 +1215,10 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="50">
+      <c r="A4" s="49">
         <v>3</v>
       </c>
-      <c r="B4" s="34">
+      <c r="B4" s="33">
         <v>534.29999999999995</v>
       </c>
       <c r="C4" s="17">
@@ -1246,10 +1230,10 @@
       <c r="E4" s="17">
         <v>5</v>
       </c>
-      <c r="F4" s="50">
+      <c r="F4" s="49">
         <v>3</v>
       </c>
-      <c r="G4" s="34">
+      <c r="G4" s="33">
         <v>1068</v>
       </c>
       <c r="H4" s="17">
@@ -1257,10 +1241,10 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="50">
+      <c r="A5" s="49">
         <v>5</v>
       </c>
-      <c r="B5" s="34">
+      <c r="B5" s="33">
         <v>741.2</v>
       </c>
       <c r="C5" s="17">
@@ -1272,10 +1256,10 @@
       <c r="E5" s="17">
         <v>6</v>
       </c>
-      <c r="F5" s="50">
+      <c r="F5" s="49">
         <v>7</v>
       </c>
-      <c r="G5" s="34">
+      <c r="G5" s="33">
         <v>1688</v>
       </c>
       <c r="H5" s="17">
@@ -1283,10 +1267,10 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="50">
+      <c r="A6" s="49">
         <v>7</v>
       </c>
-      <c r="B6" s="34">
+      <c r="B6" s="33">
         <v>954.1</v>
       </c>
       <c r="C6" s="17">
@@ -1298,10 +1282,10 @@
       <c r="E6" s="17">
         <v>6</v>
       </c>
-      <c r="F6" s="50">
+      <c r="F6" s="49">
         <v>9</v>
       </c>
-      <c r="G6" s="34">
+      <c r="G6" s="33">
         <v>1990</v>
       </c>
       <c r="H6" s="17">
@@ -1309,10 +1293,10 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A7" s="51">
+      <c r="A7" s="50">
         <v>9</v>
       </c>
-      <c r="B7" s="39">
+      <c r="B7" s="38">
         <v>1155.0999999999999</v>
       </c>
       <c r="C7" s="11">
@@ -1324,10 +1308,10 @@
       <c r="E7" s="11">
         <v>6</v>
       </c>
-      <c r="F7" s="51">
+      <c r="F7" s="50">
         <v>11</v>
       </c>
-      <c r="G7" s="39">
+      <c r="G7" s="38">
         <v>2290</v>
       </c>
       <c r="H7" s="11">
@@ -1359,65 +1343,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A1" s="40" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="42"/>
+      <c r="A1" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="41"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="36" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="37" t="s">
+      <c r="F2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="37" t="s">
+      <c r="G2" s="36" t="s">
         <v>2</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A3" s="38">
+      <c r="A3" s="37">
         <v>1</v>
       </c>
-      <c r="B3" s="34">
+      <c r="B3" s="33">
         <v>440.2</v>
       </c>
-      <c r="C3" s="34">
+      <c r="C3" s="33">
         <v>4</v>
       </c>
       <c r="D3" s="6">
         <v>1.45</v>
       </c>
-      <c r="E3" s="38">
+      <c r="E3" s="37">
         <v>1</v>
       </c>
-      <c r="F3" s="34">
+      <c r="F3" s="33">
         <v>314.5</v>
       </c>
-      <c r="G3" s="34">
+      <c r="G3" s="33">
         <v>4</v>
       </c>
       <c r="H3" s="6">
@@ -1425,51 +1409,51 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="38">
+      <c r="A4" s="37">
         <v>2</v>
       </c>
-      <c r="B4" s="34">
+      <c r="B4" s="33">
         <v>549.5</v>
       </c>
-      <c r="C4" s="34">
+      <c r="C4" s="33">
         <v>4</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="38">
+        <v>29</v>
+      </c>
+      <c r="E4" s="37">
         <v>2</v>
       </c>
-      <c r="F4" s="34">
+      <c r="F4" s="33">
         <v>400</v>
       </c>
-      <c r="G4" s="34">
+      <c r="G4" s="33">
         <v>4</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="38">
+      <c r="A5" s="37">
         <v>3</v>
       </c>
-      <c r="B5" s="34">
+      <c r="B5" s="33">
         <v>659.5</v>
       </c>
-      <c r="C5" s="34">
+      <c r="C5" s="33">
         <v>4</v>
       </c>
       <c r="D5" s="6">
         <v>296.64999999999998</v>
       </c>
-      <c r="E5" s="38">
+      <c r="E5" s="37">
         <v>3</v>
       </c>
-      <c r="F5" s="34">
+      <c r="F5" s="33">
         <v>500</v>
       </c>
-      <c r="G5" s="34">
+      <c r="G5" s="33">
         <v>4</v>
       </c>
       <c r="H5" s="6">
@@ -1477,36 +1461,36 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="38">
+      <c r="A6" s="37">
         <v>4</v>
       </c>
-      <c r="B6" s="34">
+      <c r="B6" s="33">
         <v>769.5</v>
       </c>
-      <c r="C6" s="34">
+      <c r="C6" s="33">
         <v>4</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="38">
+        <v>20</v>
+      </c>
+      <c r="E6" s="37">
         <v>4</v>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="33">
         <v>600</v>
       </c>
-      <c r="G6" s="34">
+      <c r="G6" s="33">
         <v>4</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A7" s="38">
+      <c r="A7" s="37">
         <v>5</v>
       </c>
-      <c r="B7" s="39">
+      <c r="B7" s="38">
         <v>882</v>
       </c>
       <c r="C7" s="11">
@@ -1515,13 +1499,13 @@
       <c r="D7" s="6">
         <v>0.5</v>
       </c>
-      <c r="E7" s="38">
+      <c r="E7" s="37">
         <v>5</v>
       </c>
-      <c r="F7" s="39">
+      <c r="F7" s="38">
         <v>700</v>
       </c>
-      <c r="G7" s="39">
+      <c r="G7" s="38">
         <v>4</v>
       </c>
       <c r="H7" s="6">
@@ -1530,10 +1514,10 @@
     </row>
     <row r="8" spans="1:8">
       <c r="D8" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="14.65" thickBot="1">
@@ -1546,10 +1530,10 @@
     </row>
     <row r="10" spans="1:8">
       <c r="D10" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1562,17 +1546,17 @@
     </row>
     <row r="12" spans="1:8">
       <c r="D12" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="14.65" thickBot="1">
-      <c r="D13" s="36">
+      <c r="D13" s="35">
         <v>1.6666666666666667</v>
       </c>
-      <c r="H13" s="36">
+      <c r="H13" s="35">
         <v>1.6666666666666667</v>
       </c>
     </row>
@@ -1587,16 +1571,16 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF3685B9-F09A-4019-850A-B546C03596ED}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="10.06640625" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>11</v>
@@ -1605,13 +1589,10 @@
         <v>12</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>1.57</v>
       </c>
@@ -1625,11 +1606,8 @@
         <f>AVERAGE(B2:C2)</f>
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="E2">
-        <v>5.0000000000000001E-4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>1.37</v>
       </c>
@@ -1644,7 +1622,7 @@
         <v>3.9199999999999999E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>1.17</v>
       </c>
@@ -1659,7 +1637,7 @@
         <v>3.3550000000000003E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:4">
       <c r="A5">
         <v>0.97</v>
       </c>
@@ -1674,7 +1652,7 @@
         <v>2.7799999999999999E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:4">
       <c r="A6">
         <v>0.77</v>
       </c>
@@ -1689,7 +1667,7 @@
         <v>2.2000000000000001E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:4">
       <c r="A7">
         <v>0.56999999999999995</v>
       </c>
@@ -1704,7 +1682,7 @@
         <v>1.6199999999999999E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:4">
       <c r="A8">
         <v>0.37</v>
       </c>
@@ -1726,52 +1704,67 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA895F12-453C-425C-ABA4-7F1645AB6AC5}">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="15.1328125" customWidth="1"/>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.86328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
         <v>14</v>
       </c>
-      <c r="B1" t="s">
-        <v>15</v>
-      </c>
       <c r="C1" t="s">
-        <v>16</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>490</v>
+      </c>
+      <c r="B2">
+        <v>0.4</v>
+      </c>
+      <c r="C2" s="55">
+        <v>-7.1000000000000002E-4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>490</v>
-      </c>
-      <c r="C3">
-        <v>-710</v>
+        <v>500</v>
+      </c>
+      <c r="B3">
+        <v>3.44</v>
+      </c>
+      <c r="C3" s="55">
+        <v>-6.2E-4</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="B4">
-        <v>3.44</v>
-      </c>
-      <c r="C4">
-        <v>-620</v>
+        <v>3.22</v>
+      </c>
+      <c r="C4" s="55">
+        <v>-4.6000000000000001E-4</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="B5">
-        <v>3.22</v>
-      </c>
-      <c r="C5">
-        <v>-460</v>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C5" s="55">
+        <v>-8.0000000000000007E-5</v>
       </c>
       <c r="G5">
         <f>(730*490)*2*PI()*10^-6</f>
@@ -1780,121 +1773,35 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>520</v>
+        <v>534.29999999999995</v>
       </c>
       <c r="B6">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C6">
-        <v>-80</v>
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="C6" s="55">
+        <v>1.4999999999999999E-4</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>534.29999999999995</v>
+        <v>540</v>
       </c>
       <c r="B7">
-        <v>2.2200000000000002</v>
-      </c>
-      <c r="C7">
-        <v>150</v>
+        <v>1.8</v>
+      </c>
+      <c r="C7" s="55">
+        <v>1.4999999999999999E-4</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="B8">
-        <v>1.8</v>
-      </c>
-      <c r="C8">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>550</v>
-      </c>
-      <c r="B9">
         <v>1.42</v>
       </c>
-      <c r="C9">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="14.65" thickBot="1"/>
-    <row r="14" spans="1:7">
-      <c r="A14" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="21">
-        <v>344.98678999999998</v>
-      </c>
-      <c r="B15" s="14">
-        <v>1</v>
-      </c>
-      <c r="C15" s="17">
-        <f>A15/(2*A17)</f>
-        <v>0.22690528150486711</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="24">
-        <v>1.5</v>
-      </c>
-      <c r="C16" s="17">
-        <f>3*A15/(4*A17)</f>
-        <v>0.34035792225730072</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="14.65" thickBot="1">
-      <c r="A17" s="23">
-        <v>760.2</v>
-      </c>
-      <c r="B17" s="14">
-        <v>2</v>
-      </c>
-      <c r="C17" s="17">
-        <f>A15/A17</f>
-        <v>0.45381056300973421</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="B18" s="25">
-        <v>2.5</v>
-      </c>
-      <c r="C18" s="17">
-        <f>(5*A15)/(4*A17)</f>
-        <v>0.56726320376216777</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="B19" s="24">
-        <v>3</v>
-      </c>
-      <c r="C19" s="17">
-        <f>3*A15/(2*A17)</f>
-        <v>0.68071584451460143</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="14.65" thickBot="1">
-      <c r="B20" s="26">
-        <v>3.5</v>
-      </c>
-      <c r="C20" s="11">
-        <f>(A15*7)/(4*A17)</f>
-        <v>0.79416848526703487</v>
+      <c r="C8" s="55">
+        <v>1.8000000000000001E-4</v>
       </c>
     </row>
   </sheetData>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="845" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D8EC28D-ACCD-4E3E-AF77-24C7443C8A5C}"/>
+  <xr:revisionPtr revIDLastSave="846" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEA13045-A387-4D8C-96E9-A2AB0CCFDE13}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="5" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
@@ -1704,7 +1704,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA895F12-453C-425C-ABA4-7F1645AB6AC5}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -1712,7 +1712,7 @@
     <col min="4" max="4" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -1723,7 +1723,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>490</v>
       </c>
@@ -1734,7 +1734,7 @@
         <v>-7.1000000000000002E-4</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>500</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>-6.2E-4</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>510</v>
       </c>
@@ -1756,7 +1756,7 @@
         <v>-4.6000000000000001E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>520</v>
       </c>
@@ -1766,12 +1766,8 @@
       <c r="C5" s="55">
         <v>-8.0000000000000007E-5</v>
       </c>
-      <c r="G5">
-        <f>(730*490)*2*PI()*10^-6</f>
-        <v>2.247495384378138</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>534.29999999999995</v>
       </c>
@@ -1782,7 +1778,7 @@
         <v>1.4999999999999999E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>540</v>
       </c>
@@ -1793,7 +1789,7 @@
         <v>1.4999999999999999E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:3">
       <c r="A8">
         <v>550</v>
       </c>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="846" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEA13045-A387-4D8C-96E9-A2AB0CCFDE13}"/>
+  <xr:revisionPtr revIDLastSave="852" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96D65130-B505-4490-B08E-EF53A93ADC57}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="5" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="35">
   <si>
     <t>n</t>
   </si>
@@ -82,12 +82,6 @@
     <t>Delta T_2</t>
   </si>
   <si>
-    <t>Frequenza hz</t>
-  </si>
-  <si>
-    <t>Ampiezza  V</t>
-  </si>
-  <si>
     <t>Incertezza (m)</t>
   </si>
   <si>
@@ -148,7 +142,10 @@
     <t>Δt medio (s)</t>
   </si>
   <si>
-    <t>Δt micro (μs)</t>
+    <t>Δt micro (s)</t>
+  </si>
+  <si>
+    <t>Ampiezza  (V)</t>
   </si>
 </sst>
 </file>
@@ -396,7 +393,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -442,6 +439,7 @@
     <xf numFmtId="12" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="12" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -472,7 +470,8 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -830,7 +829,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -861,10 +860,10 @@
         <v>3.5</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -895,10 +894,10 @@
         <v>4</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="14.65" thickBot="1">
@@ -920,10 +919,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="D7" s="22" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="14.65" thickBot="1">
@@ -936,7 +935,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="E9" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -945,12 +944,12 @@
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="E11" s="51" t="s">
-        <v>19</v>
+      <c r="E11" s="52" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="14.65" thickBot="1">
-      <c r="E12" s="52">
+      <c r="E12" s="53">
         <v>8.3144626180000003</v>
       </c>
     </row>
@@ -983,19 +982,19 @@
         <v>0</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="54" t="s">
-        <v>21</v>
+      <c r="F1" s="55" t="s">
+        <v>19</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -1094,7 +1093,7 @@
         <v>0.05</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F6" s="30">
         <f>AVERAGE(F2:F5)</f>
@@ -1113,7 +1112,7 @@
         <v>0.05</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F7" s="31">
         <f>2*F6</f>
@@ -1148,48 +1147,48 @@
   <sheetData>
     <row r="1" spans="1:8" ht="14.65" thickBot="1">
       <c r="A1" s="15"/>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="43"/>
-      <c r="D1" s="42" t="s">
+      <c r="C1" s="44"/>
+      <c r="D1" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="43"/>
+      <c r="E1" s="44"/>
       <c r="F1" s="15"/>
-      <c r="G1" s="42" t="s">
+      <c r="G1" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="43"/>
+      <c r="H1" s="44"/>
     </row>
     <row r="2" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="47" t="s">
+      <c r="C2" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="45" t="s">
+      <c r="D2" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="47" t="s">
+      <c r="E2" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="45" t="s">
+      <c r="F2" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="45" t="s">
+      <c r="G2" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="47" t="s">
+      <c r="H2" s="48" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="49">
+      <c r="A3" s="50">
         <v>1</v>
       </c>
       <c r="B3" s="33">
@@ -1204,7 +1203,7 @@
       <c r="E3" s="17">
         <v>5</v>
       </c>
-      <c r="F3" s="49">
+      <c r="F3" s="50">
         <v>1</v>
       </c>
       <c r="G3" s="33">
@@ -1215,7 +1214,7 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="49">
+      <c r="A4" s="50">
         <v>3</v>
       </c>
       <c r="B4" s="33">
@@ -1230,7 +1229,7 @@
       <c r="E4" s="17">
         <v>5</v>
       </c>
-      <c r="F4" s="49">
+      <c r="F4" s="50">
         <v>3</v>
       </c>
       <c r="G4" s="33">
@@ -1241,7 +1240,7 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="49">
+      <c r="A5" s="50">
         <v>5</v>
       </c>
       <c r="B5" s="33">
@@ -1256,7 +1255,7 @@
       <c r="E5" s="17">
         <v>6</v>
       </c>
-      <c r="F5" s="49">
+      <c r="F5" s="50">
         <v>7</v>
       </c>
       <c r="G5" s="33">
@@ -1267,7 +1266,7 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="49">
+      <c r="A6" s="50">
         <v>7</v>
       </c>
       <c r="B6" s="33">
@@ -1282,7 +1281,7 @@
       <c r="E6" s="17">
         <v>6</v>
       </c>
-      <c r="F6" s="49">
+      <c r="F6" s="50">
         <v>9</v>
       </c>
       <c r="G6" s="33">
@@ -1293,10 +1292,10 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A7" s="50">
+      <c r="A7" s="51">
         <v>9</v>
       </c>
-      <c r="B7" s="38">
+      <c r="B7" s="39">
         <v>1155.0999999999999</v>
       </c>
       <c r="C7" s="11">
@@ -1308,10 +1307,10 @@
       <c r="E7" s="11">
         <v>6</v>
       </c>
-      <c r="F7" s="50">
+      <c r="F7" s="51">
         <v>11</v>
       </c>
-      <c r="G7" s="38">
+      <c r="G7" s="39">
         <v>2290</v>
       </c>
       <c r="H7" s="11">
@@ -1343,18 +1342,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A1" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="41"/>
+      <c r="A1" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="42"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="9" t="s">
@@ -1367,7 +1366,7 @@
         <v>2</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>0</v>
@@ -1379,11 +1378,11 @@
         <v>2</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A3" s="37">
+      <c r="A3" s="38">
         <v>1</v>
       </c>
       <c r="B3" s="33">
@@ -1395,7 +1394,7 @@
       <c r="D3" s="6">
         <v>1.45</v>
       </c>
-      <c r="E3" s="37">
+      <c r="E3" s="38">
         <v>1</v>
       </c>
       <c r="F3" s="33">
@@ -1409,7 +1408,7 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="37">
+      <c r="A4" s="38">
         <v>2</v>
       </c>
       <c r="B4" s="33">
@@ -1419,9 +1418,9 @@
         <v>4</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="37">
+        <v>27</v>
+      </c>
+      <c r="E4" s="38">
         <v>2</v>
       </c>
       <c r="F4" s="33">
@@ -1431,11 +1430,11 @@
         <v>4</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="37">
+      <c r="A5" s="38">
         <v>3</v>
       </c>
       <c r="B5" s="33">
@@ -1447,7 +1446,7 @@
       <c r="D5" s="6">
         <v>296.64999999999998</v>
       </c>
-      <c r="E5" s="37">
+      <c r="E5" s="38">
         <v>3</v>
       </c>
       <c r="F5" s="33">
@@ -1461,7 +1460,7 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="37">
+      <c r="A6" s="38">
         <v>4</v>
       </c>
       <c r="B6" s="33">
@@ -1471,9 +1470,9 @@
         <v>4</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="37">
+        <v>18</v>
+      </c>
+      <c r="E6" s="38">
         <v>4</v>
       </c>
       <c r="F6" s="33">
@@ -1483,14 +1482,14 @@
         <v>4</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A7" s="37">
+      <c r="A7" s="38">
         <v>5</v>
       </c>
-      <c r="B7" s="38">
+      <c r="B7" s="39">
         <v>882</v>
       </c>
       <c r="C7" s="11">
@@ -1499,13 +1498,13 @@
       <c r="D7" s="6">
         <v>0.5</v>
       </c>
-      <c r="E7" s="37">
+      <c r="E7" s="38">
         <v>5</v>
       </c>
-      <c r="F7" s="38">
+      <c r="F7" s="39">
         <v>700</v>
       </c>
-      <c r="G7" s="38">
+      <c r="G7" s="39">
         <v>4</v>
       </c>
       <c r="H7" s="6">
@@ -1514,10 +1513,10 @@
     </row>
     <row r="8" spans="1:8">
       <c r="D8" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="14.65" thickBot="1">
@@ -1530,10 +1529,10 @@
     </row>
     <row r="10" spans="1:8">
       <c r="D10" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1546,10 +1545,10 @@
     </row>
     <row r="12" spans="1:8">
       <c r="D12" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="14.65" thickBot="1">
@@ -1580,7 +1579,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>11</v>
@@ -1589,7 +1588,7 @@
         <v>12</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1709,94 +1708,95 @@
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" t="s">
-        <v>35</v>
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="37" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2">
+      <c r="A2" s="14">
         <v>490</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="33">
         <v>0.4</v>
       </c>
-      <c r="C2" s="55">
+      <c r="C2" s="56">
         <v>-7.1000000000000002E-4</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3">
+      <c r="A3" s="14">
         <v>500</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="33">
         <v>3.44</v>
       </c>
-      <c r="C3" s="55">
+      <c r="C3" s="56">
         <v>-6.2E-4</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4">
+      <c r="A4" s="14">
         <v>510</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="33">
         <v>3.22</v>
       </c>
-      <c r="C4" s="55">
+      <c r="C4" s="56">
         <v>-4.6000000000000001E-4</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5">
+      <c r="A5" s="14">
         <v>520</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="33">
         <v>4.4000000000000004</v>
       </c>
-      <c r="C5" s="55">
+      <c r="C5" s="56">
         <v>-8.0000000000000007E-5</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6">
+      <c r="A6" s="14">
         <v>534.29999999999995</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="33">
         <v>2.2200000000000002</v>
       </c>
-      <c r="C6" s="55">
+      <c r="C6" s="56">
         <v>1.4999999999999999E-4</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7">
+      <c r="A7" s="14">
         <v>540</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="33">
         <v>1.8</v>
       </c>
-      <c r="C7" s="55">
+      <c r="C7" s="56">
         <v>1.4999999999999999E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8">
+    <row r="8" spans="1:3" ht="14.65" thickBot="1">
+      <c r="A8" s="23">
         <v>550</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="39">
         <v>1.42</v>
       </c>
-      <c r="C8" s="55">
+      <c r="C8" s="57">
         <v>1.8000000000000001E-4</v>
       </c>
     </row>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="852" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96D65130-B505-4490-B08E-EF53A93ADC57}"/>
+  <xr:revisionPtr revIDLastSave="854" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{560CE815-8982-4719-AEA2-957299907F39}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="5" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
+    <workbookView xWindow="675" yWindow="1657" windowWidth="16200" windowHeight="9308" firstSheet="1" activeTab="2" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Aria (tubo aperto)" sheetId="1" r:id="rId1"/>
@@ -393,7 +393,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -422,44 +422,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="12" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="12" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="12" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="12" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
@@ -472,6 +444,33 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -944,12 +943,12 @@
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="E11" s="52" t="s">
+      <c r="E11" s="42" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="14.65" thickBot="1">
-      <c r="E12" s="53">
+      <c r="E12" s="43">
         <v>8.3144626180000003</v>
       </c>
     </row>
@@ -987,10 +986,10 @@
       <c r="D1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="54" t="s">
+      <c r="E1" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="55" t="s">
+      <c r="F1" s="45" t="s">
         <v>19</v>
       </c>
       <c r="G1" s="9" t="s">
@@ -998,10 +997,10 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="34">
+      <c r="B2" s="30">
         <v>1.5</v>
       </c>
       <c r="C2" s="19">
@@ -1010,11 +1009,11 @@
       <c r="D2" s="20">
         <v>0.05</v>
       </c>
-      <c r="E2" s="33">
+      <c r="E2">
         <f>G2/G4</f>
         <v>0.45381056300973421</v>
       </c>
-      <c r="F2" s="29">
+      <c r="F2" s="26">
         <f>C4-C3</f>
         <v>0.22799999999999998</v>
       </c>
@@ -1023,18 +1022,17 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="27"/>
+      <c r="A3" s="49"/>
       <c r="B3" s="24">
         <v>2.5</v>
       </c>
-      <c r="C3" s="32">
+      <c r="C3" s="29">
         <v>0.56000000000000005</v>
       </c>
       <c r="D3" s="17">
         <v>0.05</v>
       </c>
-      <c r="E3" s="33"/>
-      <c r="F3" s="29">
+      <c r="F3" s="26">
         <f>C7-C6</f>
         <v>0.22500000000000003</v>
       </c>
@@ -1043,7 +1041,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A4" s="28"/>
+      <c r="A4" s="50"/>
       <c r="B4" s="25">
         <v>3.5</v>
       </c>
@@ -1053,8 +1051,7 @@
       <c r="D4" s="11">
         <v>0.05</v>
       </c>
-      <c r="E4" s="33"/>
-      <c r="F4" s="29">
+      <c r="F4" s="26">
         <f>C6-C5</f>
         <v>0.22</v>
       </c>
@@ -1063,30 +1060,30 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="48" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="24">
         <v>1</v>
       </c>
-      <c r="C5" s="32">
+      <c r="C5" s="29">
         <v>0.23</v>
       </c>
       <c r="D5" s="17">
         <v>0.05</v>
       </c>
       <c r="E5" s="14"/>
-      <c r="F5" s="29">
+      <c r="F5" s="26">
         <f>C3-C2</f>
         <v>0.21500000000000008</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="27"/>
+      <c r="A6" s="49"/>
       <c r="B6" s="24">
         <v>2</v>
       </c>
-      <c r="C6" s="32">
+      <c r="C6" s="29">
         <v>0.45</v>
       </c>
       <c r="D6" s="17">
@@ -1095,13 +1092,13 @@
       <c r="E6" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="27">
         <f>AVERAGE(F2:F5)</f>
         <v>0.22200000000000003</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A7" s="28"/>
+      <c r="A7" s="50"/>
       <c r="B7" s="25">
         <v>3</v>
       </c>
@@ -1114,7 +1111,7 @@
       <c r="E7" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="28">
         <f>2*F6</f>
         <v>0.44400000000000006</v>
       </c>
@@ -1147,55 +1144,55 @@
   <sheetData>
     <row r="1" spans="1:8" ht="14.65" thickBot="1">
       <c r="A1" s="15"/>
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="44"/>
-      <c r="D1" s="43" t="s">
+      <c r="C1" s="52"/>
+      <c r="D1" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="44"/>
+      <c r="E1" s="52"/>
       <c r="F1" s="15"/>
-      <c r="G1" s="43" t="s">
+      <c r="G1" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="44"/>
+      <c r="H1" s="52"/>
     </row>
     <row r="2" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="46" t="s">
+      <c r="D2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="48" t="s">
+      <c r="E2" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="46" t="s">
+      <c r="F2" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="46" t="s">
+      <c r="G2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="48" t="s">
+      <c r="H2" s="38" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="50">
+      <c r="A3" s="40">
         <v>1</v>
       </c>
-      <c r="B3" s="33">
+      <c r="B3">
         <v>319.2</v>
       </c>
       <c r="C3" s="17">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D3" s="14">
         <v>377</v>
@@ -1203,10 +1200,10 @@
       <c r="E3" s="17">
         <v>5</v>
       </c>
-      <c r="F3" s="50">
+      <c r="F3" s="40">
         <v>1</v>
       </c>
-      <c r="G3" s="33">
+      <c r="G3">
         <v>760</v>
       </c>
       <c r="H3" s="17">
@@ -1214,14 +1211,14 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="50">
+      <c r="A4" s="40">
         <v>3</v>
       </c>
-      <c r="B4" s="33">
+      <c r="B4">
         <v>534.29999999999995</v>
       </c>
       <c r="C4" s="17">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D4" s="14">
         <v>632</v>
@@ -1229,10 +1226,10 @@
       <c r="E4" s="17">
         <v>5</v>
       </c>
-      <c r="F4" s="50">
+      <c r="F4" s="40">
         <v>3</v>
       </c>
-      <c r="G4" s="33">
+      <c r="G4">
         <v>1068</v>
       </c>
       <c r="H4" s="17">
@@ -1240,14 +1237,14 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="50">
+      <c r="A5" s="40">
         <v>5</v>
       </c>
-      <c r="B5" s="33">
+      <c r="B5">
         <v>741.2</v>
       </c>
       <c r="C5" s="17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D5" s="14">
         <v>884</v>
@@ -1255,10 +1252,10 @@
       <c r="E5" s="17">
         <v>6</v>
       </c>
-      <c r="F5" s="50">
+      <c r="F5" s="40">
         <v>7</v>
       </c>
-      <c r="G5" s="33">
+      <c r="G5">
         <v>1688</v>
       </c>
       <c r="H5" s="17">
@@ -1266,14 +1263,14 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="50">
+      <c r="A6" s="40">
         <v>7</v>
       </c>
-      <c r="B6" s="33">
+      <c r="B6">
         <v>954.1</v>
       </c>
       <c r="C6" s="17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D6" s="14">
         <v>1146</v>
@@ -1281,10 +1278,10 @@
       <c r="E6" s="17">
         <v>6</v>
       </c>
-      <c r="F6" s="50">
+      <c r="F6" s="40">
         <v>9</v>
       </c>
-      <c r="G6" s="33">
+      <c r="G6">
         <v>1990</v>
       </c>
       <c r="H6" s="17">
@@ -1292,14 +1289,14 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A7" s="51">
+      <c r="A7" s="41">
         <v>9</v>
       </c>
-      <c r="B7" s="39">
+      <c r="B7" s="35">
         <v>1155.0999999999999</v>
       </c>
-      <c r="C7" s="11">
-        <v>6</v>
+      <c r="C7" s="17">
+        <v>10</v>
       </c>
       <c r="D7" s="23">
         <v>1404.5</v>
@@ -1307,10 +1304,10 @@
       <c r="E7" s="11">
         <v>6</v>
       </c>
-      <c r="F7" s="51">
+      <c r="F7" s="41">
         <v>11</v>
       </c>
-      <c r="G7" s="39">
+      <c r="G7" s="35">
         <v>2290</v>
       </c>
       <c r="H7" s="11">
@@ -1342,27 +1339,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="40" t="s">
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="42"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="56"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="36" t="s">
+      <c r="C2" s="32" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -1371,10 +1368,10 @@
       <c r="E2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="36" t="s">
+      <c r="F2" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="36" t="s">
+      <c r="G2" s="32" t="s">
         <v>2</v>
       </c>
       <c r="H2" s="5" t="s">
@@ -1382,25 +1379,25 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A3" s="38">
+      <c r="A3" s="34">
         <v>1</v>
       </c>
-      <c r="B3" s="33">
+      <c r="B3">
         <v>440.2</v>
       </c>
-      <c r="C3" s="33">
+      <c r="C3">
         <v>4</v>
       </c>
       <c r="D3" s="6">
         <v>1.45</v>
       </c>
-      <c r="E3" s="38">
+      <c r="E3" s="34">
         <v>1</v>
       </c>
-      <c r="F3" s="33">
+      <c r="F3">
         <v>314.5</v>
       </c>
-      <c r="G3" s="33">
+      <c r="G3">
         <v>4</v>
       </c>
       <c r="H3" s="6">
@@ -1408,25 +1405,25 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="38">
+      <c r="A4" s="34">
         <v>2</v>
       </c>
-      <c r="B4" s="33">
+      <c r="B4">
         <v>549.5</v>
       </c>
-      <c r="C4" s="33">
+      <c r="C4">
         <v>4</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="38">
+      <c r="E4" s="34">
         <v>2</v>
       </c>
-      <c r="F4" s="33">
+      <c r="F4">
         <v>400</v>
       </c>
-      <c r="G4" s="33">
+      <c r="G4">
         <v>4</v>
       </c>
       <c r="H4" s="5" t="s">
@@ -1434,25 +1431,25 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="38">
+      <c r="A5" s="34">
         <v>3</v>
       </c>
-      <c r="B5" s="33">
+      <c r="B5">
         <v>659.5</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C5">
         <v>4</v>
       </c>
       <c r="D5" s="6">
         <v>296.64999999999998</v>
       </c>
-      <c r="E5" s="38">
+      <c r="E5" s="34">
         <v>3</v>
       </c>
-      <c r="F5" s="33">
+      <c r="F5">
         <v>500</v>
       </c>
-      <c r="G5" s="33">
+      <c r="G5">
         <v>4</v>
       </c>
       <c r="H5" s="6">
@@ -1460,25 +1457,25 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="38">
+      <c r="A6" s="34">
         <v>4</v>
       </c>
-      <c r="B6" s="33">
+      <c r="B6">
         <v>769.5</v>
       </c>
-      <c r="C6" s="33">
+      <c r="C6">
         <v>4</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="38">
+      <c r="E6" s="34">
         <v>4</v>
       </c>
-      <c r="F6" s="33">
+      <c r="F6">
         <v>600</v>
       </c>
-      <c r="G6" s="33">
+      <c r="G6">
         <v>4</v>
       </c>
       <c r="H6" s="7" t="s">
@@ -1486,10 +1483,10 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A7" s="38">
+      <c r="A7" s="34">
         <v>5</v>
       </c>
-      <c r="B7" s="39">
+      <c r="B7" s="35">
         <v>882</v>
       </c>
       <c r="C7" s="11">
@@ -1498,13 +1495,13 @@
       <c r="D7" s="6">
         <v>0.5</v>
       </c>
-      <c r="E7" s="38">
+      <c r="E7" s="34">
         <v>5</v>
       </c>
-      <c r="F7" s="39">
+      <c r="F7" s="35">
         <v>700</v>
       </c>
-      <c r="G7" s="39">
+      <c r="G7" s="35">
         <v>4</v>
       </c>
       <c r="H7" s="6">
@@ -1552,10 +1549,10 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="14.65" thickBot="1">
-      <c r="D13" s="35">
+      <c r="D13" s="31">
         <v>1.6666666666666667</v>
       </c>
-      <c r="H13" s="35">
+      <c r="H13" s="31">
         <v>1.6666666666666667</v>
       </c>
     </row>
@@ -1716,10 +1713,10 @@
       <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="33" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1727,10 +1724,10 @@
       <c r="A2" s="14">
         <v>490</v>
       </c>
-      <c r="B2" s="33">
+      <c r="B2">
         <v>0.4</v>
       </c>
-      <c r="C2" s="56">
+      <c r="C2" s="46">
         <v>-7.1000000000000002E-4</v>
       </c>
     </row>
@@ -1738,10 +1735,10 @@
       <c r="A3" s="14">
         <v>500</v>
       </c>
-      <c r="B3" s="33">
+      <c r="B3">
         <v>3.44</v>
       </c>
-      <c r="C3" s="56">
+      <c r="C3" s="46">
         <v>-6.2E-4</v>
       </c>
     </row>
@@ -1749,10 +1746,10 @@
       <c r="A4" s="14">
         <v>510</v>
       </c>
-      <c r="B4" s="33">
+      <c r="B4">
         <v>3.22</v>
       </c>
-      <c r="C4" s="56">
+      <c r="C4" s="46">
         <v>-4.6000000000000001E-4</v>
       </c>
     </row>
@@ -1760,10 +1757,10 @@
       <c r="A5" s="14">
         <v>520</v>
       </c>
-      <c r="B5" s="33">
+      <c r="B5">
         <v>4.4000000000000004</v>
       </c>
-      <c r="C5" s="56">
+      <c r="C5" s="46">
         <v>-8.0000000000000007E-5</v>
       </c>
     </row>
@@ -1771,10 +1768,10 @@
       <c r="A6" s="14">
         <v>534.29999999999995</v>
       </c>
-      <c r="B6" s="33">
+      <c r="B6">
         <v>2.2200000000000002</v>
       </c>
-      <c r="C6" s="56">
+      <c r="C6" s="46">
         <v>1.4999999999999999E-4</v>
       </c>
     </row>
@@ -1782,10 +1779,10 @@
       <c r="A7" s="14">
         <v>540</v>
       </c>
-      <c r="B7" s="33">
+      <c r="B7">
         <v>1.8</v>
       </c>
-      <c r="C7" s="56">
+      <c r="C7" s="46">
         <v>1.4999999999999999E-4</v>
       </c>
     </row>
@@ -1793,10 +1790,10 @@
       <c r="A8" s="23">
         <v>550</v>
       </c>
-      <c r="B8" s="39">
+      <c r="B8" s="35">
         <v>1.42</v>
       </c>
-      <c r="C8" s="57">
+      <c r="C8" s="47">
         <v>1.8000000000000001E-4</v>
       </c>
     </row>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="854" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{560CE815-8982-4719-AEA2-957299907F39}"/>
+  <xr:revisionPtr revIDLastSave="856" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7591734-20E2-4527-97F3-4302F8190250}"/>
   <bookViews>
     <workbookView xWindow="675" yWindow="1657" windowWidth="16200" windowHeight="9308" firstSheet="1" activeTab="2" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
@@ -1192,7 +1192,7 @@
         <v>319.2</v>
       </c>
       <c r="C3" s="17">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D3" s="14">
         <v>377</v>
@@ -1218,7 +1218,7 @@
         <v>534.29999999999995</v>
       </c>
       <c r="C4" s="17">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D4" s="14">
         <v>632</v>
@@ -1244,7 +1244,7 @@
         <v>741.2</v>
       </c>
       <c r="C5" s="17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D5" s="14">
         <v>884</v>
@@ -1270,7 +1270,7 @@
         <v>954.1</v>
       </c>
       <c r="C6" s="17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D6" s="14">
         <v>1146</v>
@@ -1295,8 +1295,8 @@
       <c r="B7" s="35">
         <v>1155.0999999999999</v>
       </c>
-      <c r="C7" s="17">
-        <v>10</v>
+      <c r="C7" s="11">
+        <v>6</v>
       </c>
       <c r="D7" s="23">
         <v>1404.5</v>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="856" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7591734-20E2-4527-97F3-4302F8190250}"/>
+  <xr:revisionPtr revIDLastSave="866" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D51D7BF1-BC36-409E-94E7-583FDB8E7ACD}"/>
   <bookViews>
-    <workbookView xWindow="675" yWindow="1657" windowWidth="16200" windowHeight="9308" firstSheet="1" activeTab="2" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="3" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Aria (tubo aperto)" sheetId="1" r:id="rId1"/>
@@ -444,6 +444,15 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -452,15 +461,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -997,7 +997,7 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="51" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="30">
@@ -1022,7 +1022,7 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="49"/>
+      <c r="A3" s="52"/>
       <c r="B3" s="24">
         <v>2.5</v>
       </c>
@@ -1041,7 +1041,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A4" s="50"/>
+      <c r="A4" s="53"/>
       <c r="B4" s="25">
         <v>3.5</v>
       </c>
@@ -1060,7 +1060,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="51" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="24">
@@ -1079,7 +1079,7 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="49"/>
+      <c r="A6" s="52"/>
       <c r="B6" s="24">
         <v>2</v>
       </c>
@@ -1098,7 +1098,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A7" s="50"/>
+      <c r="A7" s="53"/>
       <c r="B7" s="25">
         <v>3</v>
       </c>
@@ -1144,19 +1144,19 @@
   <sheetData>
     <row r="1" spans="1:8" ht="14.65" thickBot="1">
       <c r="A1" s="15"/>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="52"/>
-      <c r="D1" s="53" t="s">
+      <c r="C1" s="49"/>
+      <c r="D1" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="52"/>
+      <c r="E1" s="49"/>
       <c r="F1" s="15"/>
-      <c r="G1" s="53" t="s">
+      <c r="G1" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="52"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="2" spans="1:8" ht="14.65" thickBot="1">
       <c r="A2" s="39" t="s">
@@ -1380,7 +1380,7 @@
     </row>
     <row r="3" spans="1:8" ht="14.65" thickBot="1">
       <c r="A3" s="34">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>440.2</v>
@@ -1392,10 +1392,10 @@
         <v>1.45</v>
       </c>
       <c r="E3" s="34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>314.5</v>
+        <v>300</v>
       </c>
       <c r="G3">
         <v>4</v>
@@ -1406,7 +1406,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="34">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B4">
         <v>549.5</v>
@@ -1418,7 +1418,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="34">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F4">
         <v>400</v>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="34">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B5">
         <v>659.5</v>
@@ -1444,7 +1444,7 @@
         <v>296.64999999999998</v>
       </c>
       <c r="E5" s="34">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F5">
         <v>500</v>
@@ -1458,7 +1458,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="34">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B6">
         <v>769.5</v>
@@ -1470,7 +1470,7 @@
         <v>18</v>
       </c>
       <c r="E6" s="34">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F6">
         <v>600</v>
@@ -1484,7 +1484,7 @@
     </row>
     <row r="7" spans="1:8" ht="14.65" thickBot="1">
       <c r="A7" s="34">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B7" s="35">
         <v>882</v>
@@ -1496,7 +1496,7 @@
         <v>0.5</v>
       </c>
       <c r="E7" s="34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F7" s="35">
         <v>700</v>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="866" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D51D7BF1-BC36-409E-94E7-583FDB8E7ACD}"/>
+  <xr:revisionPtr revIDLastSave="867" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99E7D779-D97B-4DE5-84EB-5B2A84AF1CE9}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="3" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
@@ -1395,7 +1395,7 @@
         <v>3</v>
       </c>
       <c r="F3">
-        <v>300</v>
+        <v>314.5</v>
       </c>
       <c r="G3">
         <v>4</v>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="867" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99E7D779-D97B-4DE5-84EB-5B2A84AF1CE9}"/>
+  <xr:revisionPtr revIDLastSave="877" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BEA166E-4FE1-418A-A486-790CD0994675}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="3" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Aria (tubo aperto)" sheetId="1" r:id="rId1"/>
@@ -1186,7 +1186,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B3">
         <v>319.2</v>
@@ -1201,7 +1201,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="40">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G3">
         <v>760</v>
@@ -1212,7 +1212,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="40">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4">
         <v>534.29999999999995</v>
@@ -1227,7 +1227,7 @@
         <v>5</v>
       </c>
       <c r="F4" s="40">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G4">
         <v>1068</v>
@@ -1238,7 +1238,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>741.2</v>
@@ -1253,7 +1253,7 @@
         <v>6</v>
       </c>
       <c r="F5" s="40">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G5">
         <v>1688</v>
@@ -1264,7 +1264,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="40">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>954.1</v>
@@ -1279,7 +1279,7 @@
         <v>6</v>
       </c>
       <c r="F6" s="40">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>1990</v>
@@ -1290,7 +1290,7 @@
     </row>
     <row r="7" spans="1:8" ht="14.65" thickBot="1">
       <c r="A7" s="41">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B7" s="35">
         <v>1155.0999999999999</v>
@@ -1305,7 +1305,7 @@
         <v>6</v>
       </c>
       <c r="F7" s="41">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G7" s="35">
         <v>2290</v>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="877" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BEA166E-4FE1-418A-A486-790CD0994675}"/>
+  <xr:revisionPtr revIDLastSave="880" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{483A4E3E-AF66-44BA-AB31-7EF505E5716F}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
@@ -1253,7 +1253,7 @@
         <v>6</v>
       </c>
       <c r="F5" s="40">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>1688</v>
@@ -1279,7 +1279,7 @@
         <v>6</v>
       </c>
       <c r="F6" s="40">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>1990</v>
@@ -1305,7 +1305,7 @@
         <v>6</v>
       </c>
       <c r="F7" s="41">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G7" s="35">
         <v>2290</v>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="880" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{483A4E3E-AF66-44BA-AB31-7EF505E5716F}"/>
+  <xr:revisionPtr revIDLastSave="978" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA55E21A-C25D-4B23-8F36-ABE8A641E4A0}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="6" activeTab="9" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Aria (tubo aperto)" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,10 @@
     <sheet name="Argon e Kripton" sheetId="3" r:id="rId4"/>
     <sheet name="Onde quadre-riflessione" sheetId="4" r:id="rId5"/>
     <sheet name="Ampiezza e fase" sheetId="5" r:id="rId6"/>
+    <sheet name="Aria 2 (tubo chiuso)" sheetId="7" r:id="rId7"/>
+    <sheet name="Argon e kripton 2" sheetId="8" r:id="rId8"/>
+    <sheet name="Onde quadre (Argon e Kripton)" sheetId="9" r:id="rId9"/>
+    <sheet name="Ampiezza e fase 2" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -41,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="38">
   <si>
     <t>n</t>
   </si>
@@ -146,6 +150,15 @@
   </si>
   <si>
     <t>Ampiezza  (V)</t>
+  </si>
+  <si>
+    <t>sx (m)</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Δt (s)</t>
   </si>
 </sst>
 </file>
@@ -393,7 +406,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -444,6 +457,15 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -453,15 +475,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -469,6 +482,24 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -957,6 +988,61 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9FBD33A-E969-4B4D-8F9E-2B427EE50E6E}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="14"/>
+      <c r="C2" s="46"/>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="14"/>
+      <c r="C3" s="46"/>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="14"/>
+      <c r="C4" s="46"/>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="14"/>
+      <c r="C5" s="46"/>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="14"/>
+      <c r="C6" s="46"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="14"/>
+      <c r="C7" s="46"/>
+    </row>
+    <row r="8" spans="1:3" ht="14.65" thickBot="1">
+      <c r="A8" s="23"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="47"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B0617E3-9B4E-4B1F-B0F5-FBC89FE8E318}">
   <dimension ref="A1:G11"/>
@@ -997,7 +1083,7 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="48" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="30">
@@ -1022,7 +1108,7 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="52"/>
+      <c r="A3" s="49"/>
       <c r="B3" s="24">
         <v>2.5</v>
       </c>
@@ -1041,7 +1127,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A4" s="53"/>
+      <c r="A4" s="50"/>
       <c r="B4" s="25">
         <v>3.5</v>
       </c>
@@ -1060,7 +1146,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="48" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="24">
@@ -1079,7 +1165,7 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="52"/>
+      <c r="A6" s="49"/>
       <c r="B6" s="24">
         <v>2</v>
       </c>
@@ -1098,7 +1184,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A7" s="53"/>
+      <c r="A7" s="50"/>
       <c r="B7" s="25">
         <v>3</v>
       </c>
@@ -1144,19 +1230,19 @@
   <sheetData>
     <row r="1" spans="1:8" ht="14.65" thickBot="1">
       <c r="A1" s="15"/>
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="49"/>
-      <c r="D1" s="50" t="s">
+      <c r="C1" s="52"/>
+      <c r="D1" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="49"/>
+      <c r="E1" s="52"/>
       <c r="F1" s="15"/>
-      <c r="G1" s="50" t="s">
+      <c r="G1" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="49"/>
+      <c r="H1" s="52"/>
     </row>
     <row r="2" spans="1:8" ht="14.65" thickBot="1">
       <c r="A2" s="39" t="s">
@@ -1800,4 +1886,624 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB667721-4124-4197-8679-F244BEB69CE5}">
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="2" max="2" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.06640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="14.65" thickBot="1">
+      <c r="A1" s="15"/>
+      <c r="B1" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="52"/>
+      <c r="D1" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="52"/>
+      <c r="F1" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="58"/>
+    </row>
+    <row r="2" spans="1:7" ht="14.65" thickBot="1">
+      <c r="A2" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="38" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="38" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="38" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="40">
+        <v>1</v>
+      </c>
+      <c r="B3" s="15"/>
+      <c r="C3" s="20">
+        <v>5</v>
+      </c>
+      <c r="D3" s="15"/>
+      <c r="E3" s="20">
+        <v>5</v>
+      </c>
+      <c r="G3" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="40">
+        <v>3</v>
+      </c>
+      <c r="B4" s="14"/>
+      <c r="C4" s="17">
+        <v>5</v>
+      </c>
+      <c r="D4" s="14"/>
+      <c r="E4" s="17">
+        <v>5</v>
+      </c>
+      <c r="G4" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="40">
+        <v>5</v>
+      </c>
+      <c r="B5" s="14"/>
+      <c r="C5" s="17">
+        <v>6</v>
+      </c>
+      <c r="D5" s="14"/>
+      <c r="E5" s="17">
+        <v>6</v>
+      </c>
+      <c r="G5" s="17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="40">
+        <v>7</v>
+      </c>
+      <c r="B6" s="14"/>
+      <c r="C6" s="17">
+        <v>6</v>
+      </c>
+      <c r="D6" s="14"/>
+      <c r="E6" s="17">
+        <v>6</v>
+      </c>
+      <c r="G6" s="17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="14.65" thickBot="1">
+      <c r="A7" s="41">
+        <v>9</v>
+      </c>
+      <c r="B7" s="23"/>
+      <c r="C7" s="11">
+        <v>6</v>
+      </c>
+      <c r="D7" s="23"/>
+      <c r="E7" s="11">
+        <v>6</v>
+      </c>
+      <c r="F7" s="35"/>
+      <c r="G7" s="11">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E6B7E5F-66CC-46E0-B48D-7AED69B96410}">
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="2" max="2" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="14.65" thickBot="1">
+      <c r="A1" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="56"/>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="14.65" thickBot="1">
+      <c r="A3" s="34">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3" s="6">
+        <v>1.45</v>
+      </c>
+      <c r="E3" s="34">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3" s="6">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="34">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="34">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="34">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5" s="6">
+        <v>296.64999999999998</v>
+      </c>
+      <c r="E5" s="34">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5" s="6">
+        <v>296.64999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="34">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="34">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="14.65" thickBot="1">
+      <c r="A7" s="34">
+        <v>5</v>
+      </c>
+      <c r="B7" s="35"/>
+      <c r="C7" s="11">
+        <v>4</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="E7" s="34">
+        <v>5</v>
+      </c>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35">
+        <v>4</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="D8" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="14.65" thickBot="1">
+      <c r="D9" s="8">
+        <v>3.9947999999999997E-2</v>
+      </c>
+      <c r="H9" s="8">
+        <v>8.3797999999999997E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="D10" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="D11" s="6">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="H11" s="6">
+        <v>5.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="D12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="14.65" thickBot="1">
+      <c r="D13" s="31">
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="H13" s="31">
+        <v>1.6666666666666667</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="D14" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="14.65" thickBot="1">
+      <c r="D15" s="8"/>
+      <c r="H15" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73ADE9FB-B547-41CD-8278-951487520755}">
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="4.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.73046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="7.86328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.06640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.73046875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="7.86328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.06640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="62" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="62" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="64"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="59" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="59" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="59" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="60" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="59" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" s="59" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="59" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="60" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="14">
+        <v>1.57</v>
+      </c>
+      <c r="B3" s="61">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="17" t="e">
+        <f>AVERAGE(C3:D3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F3" s="14">
+        <v>1.57</v>
+      </c>
+      <c r="G3" s="61">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="17" t="e">
+        <f>AVERAGE(H3:I3)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="14">
+        <v>1.37</v>
+      </c>
+      <c r="B4" s="61">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="17" t="e">
+        <f t="shared" ref="E4:E9" si="0">AVERAGE(C4:D4)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F4" s="14">
+        <v>1.37</v>
+      </c>
+      <c r="G4" s="61">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="17" t="e">
+        <f t="shared" ref="J4:J9" si="1">AVERAGE(H4:I4)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="14">
+        <v>1.17</v>
+      </c>
+      <c r="B5" s="61">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="17" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F5" s="14">
+        <v>1.17</v>
+      </c>
+      <c r="G5" s="61">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="17" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="14">
+        <v>0.97</v>
+      </c>
+      <c r="B6" s="61">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C6" s="61"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="17" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F6" s="14">
+        <v>0.97</v>
+      </c>
+      <c r="G6" s="61">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="17" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="14">
+        <v>0.77</v>
+      </c>
+      <c r="B7" s="61">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C7" s="61"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="17" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F7" s="14">
+        <v>0.77</v>
+      </c>
+      <c r="G7" s="61">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="H7" s="61"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="17" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="14">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="B8" s="61">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C8" s="61"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="17" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F8" s="14">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="G8" s="61">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="H8" s="61"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="17" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="14.65" thickBot="1">
+      <c r="A9" s="23">
+        <v>0.37</v>
+      </c>
+      <c r="B9" s="35">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F9" s="23">
+        <v>0.37</v>
+      </c>
+      <c r="G9" s="35">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="H9" s="35"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="11" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="F1:J1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="978" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA55E21A-C25D-4B23-8F36-ABE8A641E4A0}"/>
+  <xr:revisionPtr revIDLastSave="982" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1F867A8-3F6D-4C15-AD3B-CE5CC12C6BE2}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="6" activeTab="9" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="4" activeTab="4" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Aria (tubo aperto)" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="38">
   <si>
     <t>n</t>
   </si>
@@ -1653,128 +1653,152 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF3685B9-F09A-4019-850A-B546C03596ED}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="10.06640625" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="13" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2">
+    <row r="2" spans="1:5">
+      <c r="A2" s="14">
         <v>1.57</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="61">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C2" s="61">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="C2">
+      <c r="D2" s="61">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="D2">
-        <f>AVERAGE(B2:C2)</f>
+      <c r="E2" s="17">
+        <f>AVERAGE(C2:D2)</f>
         <v>4.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3">
+    <row r="3" spans="1:5">
+      <c r="A3" s="14">
         <v>1.37</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="61">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C3" s="61">
         <v>3.9199999999999999E-3</v>
       </c>
-      <c r="C3">
+      <c r="D3" s="61">
         <v>3.9199999999999999E-3</v>
       </c>
-      <c r="D3">
-        <f t="shared" ref="D3:D8" si="0">AVERAGE(B3:C3)</f>
+      <c r="E3" s="17">
+        <f t="shared" ref="E3:E8" si="0">AVERAGE(C3:D3)</f>
         <v>3.9199999999999999E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4">
+    <row r="4" spans="1:5">
+      <c r="A4" s="14">
         <v>1.17</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="61">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C4" s="61">
         <v>3.3600000000000001E-3</v>
       </c>
-      <c r="C4">
+      <c r="D4" s="61">
         <v>3.3500000000000001E-3</v>
       </c>
-      <c r="D4">
+      <c r="E4" s="17">
         <f t="shared" si="0"/>
         <v>3.3550000000000003E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
-      <c r="A5">
+    <row r="5" spans="1:5">
+      <c r="A5" s="14">
         <v>0.97</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="61">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C5" s="61">
         <v>2.7899999999999999E-3</v>
       </c>
-      <c r="C5">
+      <c r="D5" s="61">
         <v>2.7699999999999999E-3</v>
       </c>
-      <c r="D5">
+      <c r="E5" s="17">
         <f t="shared" si="0"/>
         <v>2.7799999999999999E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
-      <c r="A6">
+    <row r="6" spans="1:5">
+      <c r="A6" s="14">
         <v>0.77</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="61">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C6" s="61">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="C6">
+      <c r="D6" s="61">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="D6">
+      <c r="E6" s="17">
         <f t="shared" si="0"/>
         <v>2.2000000000000001E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
-      <c r="A7">
+    <row r="7" spans="1:5">
+      <c r="A7" s="14">
         <v>0.56999999999999995</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="61">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C7" s="61">
         <v>1.6199999999999999E-3</v>
       </c>
-      <c r="C7">
+      <c r="D7" s="61">
         <v>1.6199999999999999E-3</v>
       </c>
-      <c r="D7">
+      <c r="E7" s="17">
         <f t="shared" si="0"/>
         <v>1.6199999999999999E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
-      <c r="A8">
+    <row r="8" spans="1:5" ht="14.65" thickBot="1">
+      <c r="A8" s="23">
         <v>0.37</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="35">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C8" s="35">
         <v>1.0499999999999999E-3</v>
       </c>
-      <c r="C8">
+      <c r="D8" s="35">
         <v>1.0399999999999999E-3</v>
       </c>
-      <c r="D8">
+      <c r="E8" s="11">
         <f t="shared" si="0"/>
         <v>1.0449999999999999E-3</v>
       </c>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="982" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1F867A8-3F6D-4C15-AD3B-CE5CC12C6BE2}"/>
+  <xr:revisionPtr revIDLastSave="984" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F48634E3-6424-4A6E-BF93-1AA23B8C36B6}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="4" activeTab="4" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="5" activeTab="6" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Aria (tubo aperto)" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="38">
   <si>
     <t>n</t>
   </si>
@@ -1914,7 +1914,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB667721-4124-4197-8679-F244BEB69CE5}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="12.19921875" bestFit="1" customWidth="1"/>
@@ -1922,10 +1922,10 @@
     <col min="4" max="4" width="12.19921875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.06640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="14.65" thickBot="1">
+    <row r="1" spans="1:8" ht="14.65" thickBot="1">
       <c r="A1" s="15"/>
       <c r="B1" s="51" t="s">
         <v>8</v>
@@ -1939,8 +1939,11 @@
         <v>9</v>
       </c>
       <c r="G1" s="58"/>
-    </row>
-    <row r="2" spans="1:7" ht="14.65" thickBot="1">
+      <c r="H1" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="14.65" thickBot="1">
       <c r="A2" s="39" t="s">
         <v>0</v>
       </c>
@@ -1962,8 +1965,11 @@
       <c r="G2" s="38" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="H2" s="6">
+        <v>296.14999999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="40">
         <v>1</v>
       </c>
@@ -1978,8 +1984,11 @@
       <c r="G3" s="17">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="H3" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="40">
         <v>3</v>
       </c>
@@ -1994,8 +2003,11 @@
       <c r="G4" s="17">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="H4" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="40">
         <v>5</v>
       </c>
@@ -2011,7 +2023,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:8">
       <c r="A6" s="40">
         <v>7</v>
       </c>
@@ -2027,7 +2039,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="14.65" thickBot="1">
+    <row r="7" spans="1:8" ht="14.65" thickBot="1">
       <c r="A7" s="41">
         <v>9</v>
       </c>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="984" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F48634E3-6424-4A6E-BF93-1AA23B8C36B6}"/>
+  <xr:revisionPtr revIDLastSave="986" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72AE6AB2-F57F-45CA-80EC-584A112F44FE}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="5" activeTab="6" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
@@ -1965,9 +1965,7 @@
       <c r="G2" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="6">
-        <v>296.14999999999998</v>
-      </c>
+      <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="40">
@@ -1988,7 +1986,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" ht="14.65" thickBot="1">
       <c r="A4" s="40">
         <v>3</v>
       </c>
@@ -2003,7 +2001,7 @@
       <c r="G4" s="17">
         <v>5</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="8">
         <v>0.5</v>
       </c>
     </row>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="986" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72AE6AB2-F57F-45CA-80EC-584A112F44FE}"/>
+  <xr:revisionPtr revIDLastSave="998" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEFE7A51-A5F1-49EF-A580-766464A3B571}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="5" activeTab="6" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="5" activeTab="7" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Aria (tubo aperto)" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="39">
   <si>
     <t>n</t>
   </si>
@@ -155,10 +155,13 @@
     <t>sx (m)</t>
   </si>
   <si>
-    <t>D</t>
-  </si>
-  <si>
     <t>Δt (s)</t>
+  </si>
+  <si>
+    <t>D (m)</t>
+  </si>
+  <si>
+    <t>Incertezza su D (m)</t>
   </si>
 </sst>
 </file>
@@ -1006,7 +1009,7 @@
         <v>34</v>
       </c>
       <c r="C1" s="33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2066,7 +2069,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E6B7E5F-66CC-46E0-B48D-7AED69B96410}">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="12.19921875" bestFit="1" customWidth="1"/>
@@ -2164,18 +2167,14 @@
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5" s="6">
-        <v>296.64999999999998</v>
-      </c>
+      <c r="D5" s="6"/>
       <c r="E5" s="34">
         <v>3</v>
       </c>
       <c r="G5">
         <v>4</v>
       </c>
-      <c r="H5" s="6">
-        <v>296.64999999999998</v>
-      </c>
+      <c r="H5" s="6"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="34">
@@ -2269,15 +2268,31 @@
     </row>
     <row r="14" spans="1:8">
       <c r="D14" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="14.65" thickBot="1">
       <c r="D15" s="8"/>
       <c r="H15" s="8"/>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="D16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="4:8" ht="14.65" thickBot="1">
+      <c r="D17" s="8">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="H17" s="8">
+        <v>5.0000000000000001E-3</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="998" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEFE7A51-A5F1-49EF-A580-766464A3B571}"/>
+  <xr:revisionPtr revIDLastSave="1000" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0B4BEF4-C4FA-4B4E-98B3-7FDE8DA2BF8D}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="5" activeTab="7" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="6" activeTab="9" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Aria (tubo aperto)" sheetId="1" r:id="rId1"/>
@@ -993,7 +993,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9FBD33A-E969-4B4D-8F9E-2B427EE50E6E}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12.19921875" bestFit="1" customWidth="1"/>
@@ -1014,32 +1014,53 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="14"/>
+      <c r="B2" s="61"/>
       <c r="C2" s="46"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="14"/>
+      <c r="B3" s="61"/>
       <c r="C3" s="46"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="14"/>
+      <c r="B4" s="61"/>
       <c r="C4" s="46"/>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="14"/>
+      <c r="B5" s="61"/>
       <c r="C5" s="46"/>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="14"/>
+      <c r="B6" s="61"/>
       <c r="C6" s="46"/>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="14"/>
+      <c r="B7" s="61"/>
       <c r="C7" s="46"/>
     </row>
-    <row r="8" spans="1:3" ht="14.65" thickBot="1">
-      <c r="A8" s="23"/>
-      <c r="B8" s="35"/>
-      <c r="C8" s="47"/>
+    <row r="8" spans="1:3">
+      <c r="A8" s="14"/>
+      <c r="B8" s="61"/>
+      <c r="C8" s="46"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="14"/>
+      <c r="B9" s="61"/>
+      <c r="C9" s="17"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="14"/>
+      <c r="B10" s="61"/>
+      <c r="C10" s="17"/>
+    </row>
+    <row r="11" spans="1:3" ht="14.65" thickBot="1">
+      <c r="A11" s="23"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1000" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0B4BEF4-C4FA-4B4E-98B3-7FDE8DA2BF8D}"/>
+  <xr:revisionPtr revIDLastSave="1039" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01D0F305-B7F0-41D5-9FA4-ECBD9F93719D}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="6" activeTab="9" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="6" activeTab="8" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Aria (tubo aperto)" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="40">
   <si>
     <t>n</t>
   </si>
@@ -162,6 +162,9 @@
   </si>
   <si>
     <t>Incertezza su D (m)</t>
+  </si>
+  <si>
+    <t>Errore sulla media</t>
   </si>
 </sst>
 </file>
@@ -409,7 +412,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -493,18 +496,22 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1014,47 +1021,38 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="14"/>
-      <c r="B2" s="61"/>
       <c r="C2" s="46"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="14"/>
-      <c r="B3" s="61"/>
       <c r="C3" s="46"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="14"/>
-      <c r="B4" s="61"/>
       <c r="C4" s="46"/>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="14"/>
-      <c r="B5" s="61"/>
       <c r="C5" s="46"/>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="14"/>
-      <c r="B6" s="61"/>
       <c r="C6" s="46"/>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="14"/>
-      <c r="B7" s="61"/>
       <c r="C7" s="46"/>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="14"/>
-      <c r="B8" s="61"/>
       <c r="C8" s="46"/>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="14"/>
-      <c r="B9" s="61"/>
       <c r="C9" s="17"/>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="14"/>
-      <c r="B10" s="61"/>
       <c r="C10" s="17"/>
     </row>
     <row r="11" spans="1:3" ht="14.65" thickBot="1">
@@ -1705,13 +1703,13 @@
       <c r="A2" s="14">
         <v>1.57</v>
       </c>
-      <c r="B2" s="61">
+      <c r="B2">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="C2" s="61">
+      <c r="C2">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="D2" s="61">
+      <c r="D2">
         <v>4.4999999999999997E-3</v>
       </c>
       <c r="E2" s="17">
@@ -1723,13 +1721,13 @@
       <c r="A3" s="14">
         <v>1.37</v>
       </c>
-      <c r="B3" s="61">
+      <c r="B3">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="C3" s="61">
+      <c r="C3">
         <v>3.9199999999999999E-3</v>
       </c>
-      <c r="D3" s="61">
+      <c r="D3">
         <v>3.9199999999999999E-3</v>
       </c>
       <c r="E3" s="17">
@@ -1741,13 +1739,13 @@
       <c r="A4" s="14">
         <v>1.17</v>
       </c>
-      <c r="B4" s="61">
+      <c r="B4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="C4" s="61">
+      <c r="C4">
         <v>3.3600000000000001E-3</v>
       </c>
-      <c r="D4" s="61">
+      <c r="D4">
         <v>3.3500000000000001E-3</v>
       </c>
       <c r="E4" s="17">
@@ -1759,13 +1757,13 @@
       <c r="A5" s="14">
         <v>0.97</v>
       </c>
-      <c r="B5" s="61">
+      <c r="B5">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="C5" s="61">
+      <c r="C5">
         <v>2.7899999999999999E-3</v>
       </c>
-      <c r="D5" s="61">
+      <c r="D5">
         <v>2.7699999999999999E-3</v>
       </c>
       <c r="E5" s="17">
@@ -1777,13 +1775,13 @@
       <c r="A6" s="14">
         <v>0.77</v>
       </c>
-      <c r="B6" s="61">
+      <c r="B6">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="C6" s="61">
+      <c r="C6">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="D6" s="61">
+      <c r="D6">
         <v>2.2000000000000001E-3</v>
       </c>
       <c r="E6" s="17">
@@ -1795,13 +1793,13 @@
       <c r="A7" s="14">
         <v>0.56999999999999995</v>
       </c>
-      <c r="B7" s="61">
+      <c r="B7">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="C7" s="61">
+      <c r="C7">
         <v>1.6199999999999999E-3</v>
       </c>
-      <c r="D7" s="61">
+      <c r="D7">
         <v>1.6199999999999999E-3</v>
       </c>
       <c r="E7" s="17">
@@ -2326,12 +2324,13 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73ADE9FB-B547-41CD-8278-951487520755}">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="4.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.73046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="7.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.06640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.9296875" customWidth="1"/>
     <col min="5" max="5" width="10.06640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="4.73046875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.73046875" bestFit="1" customWidth="1"/>
@@ -2339,240 +2338,112 @@
     <col min="10" max="10" width="10.06640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="62" t="s">
+    <row r="1" spans="1:4" ht="14.65" thickBot="1">
+      <c r="A1" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="62" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
-      <c r="J1" s="64"/>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="34" t="s">
+      <c r="D1" s="60"/>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="59" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" s="59" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="59" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="F2" s="34" t="s">
+      <c r="B2" s="61" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="59" t="s">
-        <v>35</v>
-      </c>
-      <c r="H2" s="59" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="59" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="60" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="14">
-        <v>1.57</v>
-      </c>
-      <c r="B3" s="61">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="17" t="e">
-        <f>AVERAGE(C3:D3)</f>
+      <c r="D2" s="61" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="14.65" thickBot="1">
+      <c r="A3" s="23">
+        <v>1.45</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="23">
+        <v>1.45</v>
+      </c>
+      <c r="D3" s="6"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="14"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="6"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="14"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="6"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="14"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="6"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="14"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="6"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="14"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="6"/>
+    </row>
+    <row r="9" spans="1:4" ht="14.65" thickBot="1">
+      <c r="A9" s="14"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="66"/>
+      <c r="D9" s="6"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="62" t="e">
+        <f>AVERAGE(B3:B9)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F3" s="14">
-        <v>1.57</v>
-      </c>
-      <c r="G3" s="61">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="17" t="e">
-        <f>AVERAGE(H3:I3)</f>
+      <c r="C10" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="62" t="e">
+        <f>AVERAGE(D3:D9)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="14">
-        <v>1.37</v>
-      </c>
-      <c r="B4" s="61">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="C4" s="61"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="17" t="e">
-        <f t="shared" ref="E4:E9" si="0">AVERAGE(C4:D4)</f>
+    <row r="11" spans="1:4" ht="14.65" thickBot="1">
+      <c r="A11" s="63" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="8" t="e">
+        <f>_xlfn.STDEV.S(B3:B9)/COUNT(B3:B9)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F4" s="14">
-        <v>1.37</v>
-      </c>
-      <c r="G4" s="61">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="H4" s="61"/>
-      <c r="I4" s="61"/>
-      <c r="J4" s="17" t="e">
-        <f t="shared" ref="J4:J9" si="1">AVERAGE(H4:I4)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="14">
-        <v>1.17</v>
-      </c>
-      <c r="B5" s="61">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="17" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F5" s="14">
-        <v>1.17</v>
-      </c>
-      <c r="G5" s="61">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="17" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="14">
-        <v>0.97</v>
-      </c>
-      <c r="B6" s="61">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="C6" s="61"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="17" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F6" s="14">
-        <v>0.97</v>
-      </c>
-      <c r="G6" s="61">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="17" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="14">
-        <v>0.77</v>
-      </c>
-      <c r="B7" s="61">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="C7" s="61"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="17" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F7" s="14">
-        <v>0.77</v>
-      </c>
-      <c r="G7" s="61">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="H7" s="61"/>
-      <c r="I7" s="61"/>
-      <c r="J7" s="17" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="14">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="B8" s="61">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="C8" s="61"/>
-      <c r="D8" s="61"/>
-      <c r="E8" s="17" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F8" s="14">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="G8" s="61">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="H8" s="61"/>
-      <c r="I8" s="61"/>
-      <c r="J8" s="17" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="14.65" thickBot="1">
-      <c r="A9" s="23">
-        <v>0.37</v>
-      </c>
-      <c r="B9" s="35">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="11" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F9" s="23">
-        <v>0.37</v>
-      </c>
-      <c r="G9" s="35">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="H9" s="35"/>
-      <c r="I9" s="35"/>
-      <c r="J9" s="11" t="e">
-        <f t="shared" si="1"/>
+      <c r="C11" s="63" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="8" t="e">
+        <f>_xlfn.STDEV.S(D3:D9)/COUNT(D3:D9)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1039" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01D0F305-B7F0-41D5-9FA4-ECBD9F93719D}"/>
+  <xr:revisionPtr revIDLastSave="1043" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{069E42B8-AF43-447C-B9F0-C07E45AA6987}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="6" activeTab="8" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="5" activeTab="7" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Aria (tubo aperto)" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="38">
   <si>
     <t>n</t>
   </si>
@@ -156,12 +156,6 @@
   </si>
   <si>
     <t>Δt (s)</t>
-  </si>
-  <si>
-    <t>D (m)</t>
-  </si>
-  <si>
-    <t>Incertezza su D (m)</t>
   </si>
   <si>
     <t>Errore sulla media</t>
@@ -412,7 +406,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -463,6 +457,21 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -496,22 +505,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -527,6 +520,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1105,7 +1102,7 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="55" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="30">
@@ -1130,7 +1127,7 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="49"/>
+      <c r="A3" s="56"/>
       <c r="B3" s="24">
         <v>2.5</v>
       </c>
@@ -1149,7 +1146,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A4" s="50"/>
+      <c r="A4" s="57"/>
       <c r="B4" s="25">
         <v>3.5</v>
       </c>
@@ -1168,7 +1165,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="55" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="24">
@@ -1187,7 +1184,7 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="49"/>
+      <c r="A6" s="56"/>
       <c r="B6" s="24">
         <v>2</v>
       </c>
@@ -1206,7 +1203,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A7" s="50"/>
+      <c r="A7" s="57"/>
       <c r="B7" s="25">
         <v>3</v>
       </c>
@@ -1252,19 +1249,19 @@
   <sheetData>
     <row r="1" spans="1:8" ht="14.65" thickBot="1">
       <c r="A1" s="15"/>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="52"/>
-      <c r="D1" s="53" t="s">
+      <c r="C1" s="59"/>
+      <c r="D1" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="52"/>
+      <c r="E1" s="59"/>
       <c r="F1" s="15"/>
-      <c r="G1" s="53" t="s">
+      <c r="G1" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="52"/>
+      <c r="H1" s="59"/>
     </row>
     <row r="2" spans="1:8" ht="14.65" thickBot="1">
       <c r="A2" s="39" t="s">
@@ -1447,18 +1444,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="54" t="s">
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="61" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="56"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="63"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="9" t="s">
@@ -1949,18 +1946,18 @@
   <sheetData>
     <row r="1" spans="1:8" ht="14.65" thickBot="1">
       <c r="A1" s="15"/>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="52"/>
-      <c r="D1" s="53" t="s">
+      <c r="C1" s="59"/>
+      <c r="D1" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="52"/>
-      <c r="F1" s="57" t="s">
+      <c r="E1" s="59"/>
+      <c r="F1" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="58"/>
+      <c r="G1" s="65"/>
       <c r="H1" s="5" t="s">
         <v>15</v>
       </c>
@@ -2088,7 +2085,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E6B7E5F-66CC-46E0-B48D-7AED69B96410}">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="12.19921875" bestFit="1" customWidth="1"/>
@@ -2100,18 +2097,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="54" t="s">
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="61" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="56"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="63"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="9" t="s">
@@ -2283,34 +2280,6 @@
       </c>
       <c r="H13" s="31">
         <v>1.6666666666666667</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="D14" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="14.65" thickBot="1">
-      <c r="D15" s="8"/>
-      <c r="H15" s="8"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="D16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="4:8" ht="14.65" thickBot="1">
-      <c r="D17" s="8">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="H17" s="8">
-        <v>5.0000000000000001E-3</v>
       </c>
     </row>
   </sheetData>
@@ -2339,26 +2308,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="14.65" thickBot="1">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="59" t="s">
+      <c r="B1" s="52"/>
+      <c r="C1" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="60"/>
+      <c r="D1" s="54"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="48" t="s">
         <v>36</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="61" t="s">
+      <c r="D2" s="48" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2375,65 +2344,59 @@
     <row r="4" spans="1:4">
       <c r="A4" s="14"/>
       <c r="B4" s="6"/>
-      <c r="C4" s="66"/>
       <c r="D4" s="6"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="14"/>
       <c r="B5" s="6"/>
-      <c r="C5" s="66"/>
       <c r="D5" s="6"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="14"/>
       <c r="B6" s="6"/>
-      <c r="C6" s="66"/>
       <c r="D6" s="6"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="14"/>
       <c r="B7" s="6"/>
-      <c r="C7" s="66"/>
       <c r="D7" s="6"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="14"/>
       <c r="B8" s="6"/>
-      <c r="C8" s="66"/>
       <c r="D8" s="6"/>
     </row>
     <row r="9" spans="1:4" ht="14.65" thickBot="1">
       <c r="A9" s="14"/>
       <c r="B9" s="6"/>
-      <c r="C9" s="66"/>
       <c r="D9" s="6"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="62" t="e">
+      <c r="B10" s="49" t="e">
         <f>AVERAGE(B3:B9)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="62" t="e">
+      <c r="D10" s="49" t="e">
         <f>AVERAGE(D3:D9)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="14.65" thickBot="1">
-      <c r="A11" s="63" t="s">
-        <v>39</v>
+      <c r="A11" s="50" t="s">
+        <v>37</v>
       </c>
       <c r="B11" s="8" t="e">
         <f>_xlfn.STDEV.S(B3:B9)/COUNT(B3:B9)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C11" s="63" t="s">
-        <v>39</v>
+      <c r="C11" s="50" t="s">
+        <v>37</v>
       </c>
       <c r="D11" s="8" t="e">
         <f>_xlfn.STDEV.S(D3:D9)/COUNT(D3:D9)</f>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1043" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{069E42B8-AF43-447C-B9F0-C07E45AA6987}"/>
+  <xr:revisionPtr revIDLastSave="1064" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2662D5D-AA24-437C-88A0-F35BA4142DFA}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="5" activeTab="7" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="3" activeTab="6" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Aria (tubo aperto)" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="40">
   <si>
     <t>n</t>
   </si>
@@ -159,6 +159,12 @@
   </si>
   <si>
     <t>Errore sulla media</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distanza dal tubo </t>
+  </si>
+  <si>
+    <t>1,5 cm</t>
   </si>
 </sst>
 </file>
@@ -406,7 +412,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -460,16 +466,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -490,21 +493,30 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -520,10 +532,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1102,7 +1110,7 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="54" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="30">
@@ -1127,7 +1135,7 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="56"/>
+      <c r="A3" s="55"/>
       <c r="B3" s="24">
         <v>2.5</v>
       </c>
@@ -1146,7 +1154,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A4" s="57"/>
+      <c r="A4" s="56"/>
       <c r="B4" s="25">
         <v>3.5</v>
       </c>
@@ -1165,7 +1173,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="54" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="24">
@@ -1184,7 +1192,7 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="56"/>
+      <c r="A6" s="55"/>
       <c r="B6" s="24">
         <v>2</v>
       </c>
@@ -1203,7 +1211,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A7" s="57"/>
+      <c r="A7" s="56"/>
       <c r="B7" s="25">
         <v>3</v>
       </c>
@@ -1249,19 +1257,19 @@
   <sheetData>
     <row r="1" spans="1:8" ht="14.65" thickBot="1">
       <c r="A1" s="15"/>
-      <c r="B1" s="58" t="s">
+      <c r="B1" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="59"/>
-      <c r="D1" s="60" t="s">
+      <c r="C1" s="58"/>
+      <c r="D1" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="59"/>
+      <c r="E1" s="58"/>
       <c r="F1" s="15"/>
-      <c r="G1" s="60" t="s">
+      <c r="G1" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="59"/>
+      <c r="H1" s="58"/>
     </row>
     <row r="2" spans="1:8" ht="14.65" thickBot="1">
       <c r="A2" s="39" t="s">
@@ -1444,18 +1452,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="61" t="s">
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="63"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="53"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="9" t="s">
@@ -1933,7 +1941,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB667721-4124-4197-8679-F244BEB69CE5}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="12.19921875" bestFit="1" customWidth="1"/>
@@ -1942,27 +1950,31 @@
     <col min="5" max="5" width="12.06640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.19921875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="14.65" thickBot="1">
+    <row r="1" spans="1:9" ht="14.65" thickBot="1">
       <c r="A1" s="15"/>
-      <c r="B1" s="58" t="s">
+      <c r="B1" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="59"/>
-      <c r="D1" s="60" t="s">
+      <c r="C1" s="58"/>
+      <c r="D1" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="59"/>
-      <c r="F1" s="64" t="s">
+      <c r="E1" s="58"/>
+      <c r="F1" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="65"/>
+      <c r="G1" s="61"/>
       <c r="H1" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="14.65" thickBot="1">
+      <c r="I1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="14.65" thickBot="1">
       <c r="A2" s="39" t="s">
         <v>0</v>
       </c>
@@ -1972,106 +1984,140 @@
       <c r="C2" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="36" t="s">
+      <c r="D2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="38" t="s">
+      <c r="E2" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="36" t="s">
+      <c r="F2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="38" t="s">
+      <c r="G2" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="6"/>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="40">
+      <c r="H2" s="6">
+        <v>294.64999999999998</v>
+      </c>
+      <c r="I2" s="66" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="48">
         <v>1</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="20">
+      <c r="B3" s="15">
+        <v>105</v>
+      </c>
+      <c r="C3" s="68">
+        <v>1</v>
+      </c>
+      <c r="D3" s="15"/>
+      <c r="E3" s="68">
         <v>5</v>
       </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="20">
+      <c r="F3" s="68"/>
+      <c r="G3" s="20">
         <v>5</v>
       </c>
-      <c r="G3" s="17">
-        <v>5</v>
-      </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="71" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="14.65" thickBot="1">
+    <row r="4" spans="1:9" ht="14.65" thickBot="1">
       <c r="A4" s="40">
         <v>3</v>
       </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="17">
+      <c r="B4" s="14">
+        <v>315.60000000000002</v>
+      </c>
+      <c r="C4" s="67">
+        <v>1</v>
+      </c>
+      <c r="D4" s="14"/>
+      <c r="E4" s="67">
         <v>5</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="17">
-        <v>5</v>
-      </c>
+      <c r="F4" s="67"/>
       <c r="G4" s="17">
         <v>5</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="11">
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:9">
       <c r="A5" s="40">
         <v>5</v>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="17">
+      <c r="B5" s="14">
+        <v>525.70000000000005</v>
+      </c>
+      <c r="C5" s="67">
+        <v>1</v>
+      </c>
+      <c r="D5" s="14"/>
+      <c r="E5" s="67">
         <v>6</v>
       </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="17">
-        <v>6</v>
-      </c>
+      <c r="F5" s="67"/>
       <c r="G5" s="17">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:9">
       <c r="A6" s="40">
         <v>7</v>
       </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="17">
+      <c r="B6" s="14">
+        <v>737.4</v>
+      </c>
+      <c r="C6" s="67">
+        <v>1</v>
+      </c>
+      <c r="D6" s="14"/>
+      <c r="E6" s="67">
         <v>6</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="17">
-        <v>6</v>
-      </c>
+      <c r="F6" s="67"/>
       <c r="G6" s="17">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A7" s="41">
+    <row r="7" spans="1:9">
+      <c r="A7" s="40">
         <v>9</v>
       </c>
-      <c r="B7" s="23"/>
-      <c r="C7" s="11">
+      <c r="B7" s="14">
+        <v>949.3</v>
+      </c>
+      <c r="C7" s="67">
+        <v>1</v>
+      </c>
+      <c r="D7" s="14"/>
+      <c r="E7" s="67">
         <v>6</v>
       </c>
-      <c r="D7" s="23"/>
-      <c r="E7" s="11">
+      <c r="F7" s="67"/>
+      <c r="G7" s="17">
         <v>6</v>
       </c>
-      <c r="F7" s="35"/>
-      <c r="G7" s="11">
-        <v>6</v>
-      </c>
+    </row>
+    <row r="8" spans="1:9" ht="14.65" thickBot="1">
+      <c r="A8" s="41">
+        <v>11</v>
+      </c>
+      <c r="B8" s="69">
+        <v>1155.4000000000001</v>
+      </c>
+      <c r="C8" s="70">
+        <v>2</v>
+      </c>
+      <c r="D8" s="23"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2097,18 +2143,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="61" t="s">
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="63"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="53"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="9" t="s">
@@ -2308,14 +2354,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="14.65" thickBot="1">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="53" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="54"/>
+      <c r="D1" s="65"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="12" t="s">

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1064" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2662D5D-AA24-437C-88A0-F35BA4142DFA}"/>
+  <xr:revisionPtr revIDLastSave="1086" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8276B8A-2BA6-452C-8F63-7CC270A8C937}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="3" activeTab="6" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
@@ -2013,13 +2013,15 @@
       <c r="C3" s="68">
         <v>1</v>
       </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="68">
-        <v>5</v>
+      <c r="D3" s="15">
+        <v>129.30000000000001</v>
+      </c>
+      <c r="E3" s="20">
+        <v>1</v>
       </c>
       <c r="F3" s="68"/>
       <c r="G3" s="20">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H3" s="71" t="s">
         <v>18</v>
@@ -2035,13 +2037,15 @@
       <c r="C4" s="67">
         <v>1</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="67">
-        <v>5</v>
+      <c r="D4" s="14">
+        <v>386.6</v>
+      </c>
+      <c r="E4" s="17">
+        <v>1</v>
       </c>
       <c r="F4" s="67"/>
       <c r="G4" s="17">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H4" s="11">
         <v>0.5</v>
@@ -2057,13 +2061,15 @@
       <c r="C5" s="67">
         <v>1</v>
       </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="67">
-        <v>6</v>
+      <c r="D5" s="14">
+        <v>645.70000000000005</v>
+      </c>
+      <c r="E5" s="17">
+        <v>1</v>
       </c>
       <c r="F5" s="67"/>
       <c r="G5" s="17">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2076,13 +2082,15 @@
       <c r="C6" s="67">
         <v>1</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="67">
-        <v>6</v>
+      <c r="D6" s="14">
+        <v>903.5</v>
+      </c>
+      <c r="E6" s="17">
+        <v>1</v>
       </c>
       <c r="F6" s="67"/>
       <c r="G6" s="17">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2095,13 +2103,15 @@
       <c r="C7" s="67">
         <v>1</v>
       </c>
-      <c r="D7" s="14"/>
-      <c r="E7" s="67">
-        <v>6</v>
+      <c r="D7" s="14">
+        <v>1162.7</v>
+      </c>
+      <c r="E7" s="17">
+        <v>2</v>
       </c>
       <c r="F7" s="67"/>
       <c r="G7" s="17">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="14.65" thickBot="1">
@@ -2114,10 +2124,16 @@
       <c r="C8" s="70">
         <v>2</v>
       </c>
-      <c r="D8" s="23"/>
-      <c r="E8" s="35"/>
+      <c r="D8" s="23">
+        <v>1430</v>
+      </c>
+      <c r="E8" s="11">
+        <v>2</v>
+      </c>
       <c r="F8" s="35"/>
-      <c r="G8" s="11"/>
+      <c r="G8" s="11">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1086" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8276B8A-2BA6-452C-8F63-7CC270A8C937}"/>
+  <xr:revisionPtr revIDLastSave="1093" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18B9068D-EF12-4368-BB45-A0F6C4C019AB}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="3" activeTab="6" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
@@ -412,7 +412,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -513,6 +513,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1970,7 +1971,7 @@
       <c r="H1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="66" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2010,7 +2011,7 @@
       <c r="B3" s="15">
         <v>105</v>
       </c>
-      <c r="C3" s="68">
+      <c r="C3" s="69">
         <v>1</v>
       </c>
       <c r="D3" s="15">
@@ -2019,11 +2020,13 @@
       <c r="E3" s="20">
         <v>1</v>
       </c>
-      <c r="F3" s="68"/>
+      <c r="F3" s="69">
+        <v>151</v>
+      </c>
       <c r="G3" s="20">
         <v>1</v>
       </c>
-      <c r="H3" s="71" t="s">
+      <c r="H3" s="72" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2043,7 +2046,9 @@
       <c r="E4" s="17">
         <v>1</v>
       </c>
-      <c r="F4" s="67"/>
+      <c r="F4" s="68">
+        <v>456.5</v>
+      </c>
       <c r="G4" s="17">
         <v>1</v>
       </c>
@@ -2067,7 +2072,9 @@
       <c r="E5" s="17">
         <v>1</v>
       </c>
-      <c r="F5" s="67"/>
+      <c r="F5" s="68">
+        <v>760</v>
+      </c>
       <c r="G5" s="17">
         <v>1</v>
       </c>
@@ -2088,7 +2095,9 @@
       <c r="E6" s="17">
         <v>1</v>
       </c>
-      <c r="F6" s="67"/>
+      <c r="F6" s="68">
+        <v>1063</v>
+      </c>
       <c r="G6" s="17">
         <v>1</v>
       </c>
@@ -2109,7 +2118,9 @@
       <c r="E7" s="17">
         <v>2</v>
       </c>
-      <c r="F7" s="67"/>
+      <c r="F7" s="68">
+        <v>1380</v>
+      </c>
       <c r="G7" s="17">
         <v>2</v>
       </c>
@@ -2118,10 +2129,10 @@
       <c r="A8" s="41">
         <v>11</v>
       </c>
-      <c r="B8" s="69">
+      <c r="B8" s="70">
         <v>1155.4000000000001</v>
       </c>
-      <c r="C8" s="70">
+      <c r="C8" s="71">
         <v>2</v>
       </c>
       <c r="D8" s="23">
@@ -2130,7 +2141,9 @@
       <c r="E8" s="11">
         <v>2</v>
       </c>
-      <c r="F8" s="35"/>
+      <c r="F8" s="35">
+        <v>1680</v>
+      </c>
       <c r="G8" s="11">
         <v>2</v>
       </c>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1093" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18B9068D-EF12-4368-BB45-A0F6C4C019AB}"/>
+  <xr:revisionPtr revIDLastSave="1103" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B6EFC83-32F2-471A-884C-65A1180AA88A}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="3" activeTab="6" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
@@ -2018,13 +2018,13 @@
         <v>129.30000000000001</v>
       </c>
       <c r="E3" s="20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="69">
         <v>151</v>
       </c>
       <c r="G3" s="20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" s="72" t="s">
         <v>18</v>
@@ -2044,13 +2044,13 @@
         <v>386.6</v>
       </c>
       <c r="E4" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="68">
         <v>456.5</v>
       </c>
       <c r="G4" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" s="11">
         <v>0.5</v>
@@ -2070,13 +2070,13 @@
         <v>645.70000000000005</v>
       </c>
       <c r="E5" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="68">
         <v>760</v>
       </c>
       <c r="G5" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2093,13 +2093,13 @@
         <v>903.5</v>
       </c>
       <c r="E6" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="68">
         <v>1063</v>
       </c>
       <c r="G6" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2139,13 +2139,13 @@
         <v>1430</v>
       </c>
       <c r="E8" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" s="35">
         <v>1680</v>
       </c>
       <c r="G8" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1103" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B6EFC83-32F2-471A-884C-65A1180AA88A}"/>
+  <xr:revisionPtr revIDLastSave="1109" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FCC3DDC-2801-4A42-8186-B0674BE25F63}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="3" activeTab="6" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
@@ -2024,7 +2024,7 @@
         <v>151</v>
       </c>
       <c r="G3" s="20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3" s="72" t="s">
         <v>18</v>
@@ -2050,7 +2050,7 @@
         <v>456.5</v>
       </c>
       <c r="G4" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" s="11">
         <v>0.5</v>
@@ -2076,7 +2076,7 @@
         <v>760</v>
       </c>
       <c r="G5" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2099,7 +2099,7 @@
         <v>1063</v>
       </c>
       <c r="G6" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2122,7 +2122,7 @@
         <v>1380</v>
       </c>
       <c r="G7" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="14.65" thickBot="1">
@@ -2145,7 +2145,7 @@
         <v>1680</v>
       </c>
       <c r="G8" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1109" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FCC3DDC-2801-4A42-8186-B0674BE25F63}"/>
+  <xr:revisionPtr revIDLastSave="1167" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F630840-F85B-42A7-91F1-4802B7CBBDE0}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="3" activeTab="6" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="6" activeTab="9" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Aria (tubo aperto)" sheetId="1" r:id="rId1"/>
@@ -24,6 +24,9 @@
     <sheet name="Onde quadre (Argon e Kripton)" sheetId="9" r:id="rId9"/>
     <sheet name="Ampiezza e fase 2" sheetId="10" r:id="rId10"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Ampiezza e fase 2'!$A$1:$C$11</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -171,11 +174,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.000000000"/>
     <numFmt numFmtId="166" formatCode="#,##0.00000"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="171" formatCode="0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -412,7 +416,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -512,12 +516,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1006,7 +1014,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9FBD33A-E969-4B4D-8F9E-2B427EE50E6E}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12.19921875" bestFit="1" customWidth="1"/>
@@ -1014,7 +1022,7 @@
     <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
@@ -1025,48 +1033,147 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="14"/>
-      <c r="C2" s="46"/>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="14"/>
-      <c r="C3" s="46"/>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="14"/>
-      <c r="C4" s="46"/>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="14"/>
-      <c r="C5" s="46"/>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="14"/>
-      <c r="C6" s="46"/>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="14"/>
-      <c r="C7" s="46"/>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="14"/>
-      <c r="C8" s="46"/>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="14"/>
-      <c r="C9" s="17"/>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="14"/>
-      <c r="C10" s="17"/>
-    </row>
-    <row r="11" spans="1:3" ht="14.65" thickBot="1">
-      <c r="A11" s="23"/>
-      <c r="B11" s="35"/>
-      <c r="C11" s="11"/>
+    <row r="2" spans="1:4">
+      <c r="A2" s="68">
+        <v>222</v>
+      </c>
+      <c r="B2" s="68">
+        <v>0.05</v>
+      </c>
+      <c r="C2" s="68"/>
+      <c r="D2" s="74"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="68">
+        <v>232</v>
+      </c>
+      <c r="B3" s="68">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="C3" s="68"/>
+      <c r="D3" s="74"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="69">
+        <v>242</v>
+      </c>
+      <c r="B4" s="75">
+        <v>0.09</v>
+      </c>
+      <c r="C4" s="68"/>
+      <c r="D4" s="74"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="68">
+        <v>252</v>
+      </c>
+      <c r="B5" s="75">
+        <v>0.16400000000000001</v>
+      </c>
+      <c r="C5" s="76"/>
+      <c r="D5" s="74"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="68">
+        <v>262</v>
+      </c>
+      <c r="B6" s="75">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="C6" s="76"/>
+      <c r="D6" s="74"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="68">
+        <v>272</v>
+      </c>
+      <c r="B7" s="75">
+        <v>0.27</v>
+      </c>
+      <c r="C7" s="76"/>
+      <c r="D7" s="74"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="67">
+        <v>282</v>
+      </c>
+      <c r="B8" s="75">
+        <v>0.32200000000000001</v>
+      </c>
+      <c r="C8" s="76">
+        <v>4.2999999999999999E-4</v>
+      </c>
+      <c r="D8" s="74"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="68">
+        <v>292</v>
+      </c>
+      <c r="B9" s="75">
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="C9" s="76"/>
+      <c r="D9" s="74"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="68">
+        <v>302</v>
+      </c>
+      <c r="B10" s="75">
+        <v>0.21</v>
+      </c>
+      <c r="C10" s="76"/>
+      <c r="D10" s="74"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="68">
+        <v>312</v>
+      </c>
+      <c r="B11" s="75">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="C11" s="76"/>
+      <c r="D11" s="74"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="68">
+        <v>322</v>
+      </c>
+      <c r="B12" s="75">
+        <v>0.13800000000000001</v>
+      </c>
+      <c r="C12" s="76"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="68">
+        <v>332</v>
+      </c>
+      <c r="B13" s="75">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="C13" s="76"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="68">
+        <v>342</v>
+      </c>
+      <c r="B14" s="75">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="C14" s="76"/>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" s="29"/>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" s="29"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C9" xr:uid="{D9FBD33A-E969-4B4D-8F9E-2B427EE50E6E}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C12">
+      <sortCondition ref="A1:A9"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2000,7 +2107,7 @@
       <c r="H2" s="6">
         <v>294.64999999999998</v>
       </c>
-      <c r="I2" s="66" t="s">
+      <c r="I2" s="69" t="s">
         <v>39</v>
       </c>
     </row>
@@ -2011,7 +2118,7 @@
       <c r="B3" s="15">
         <v>105</v>
       </c>
-      <c r="C3" s="69">
+      <c r="C3" s="70">
         <v>1</v>
       </c>
       <c r="D3" s="15">
@@ -2020,13 +2127,13 @@
       <c r="E3" s="20">
         <v>2</v>
       </c>
-      <c r="F3" s="69">
+      <c r="F3" s="70">
         <v>151</v>
       </c>
       <c r="G3" s="20">
         <v>3</v>
       </c>
-      <c r="H3" s="72" t="s">
+      <c r="H3" s="73" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2037,7 +2144,7 @@
       <c r="B4" s="14">
         <v>315.60000000000002</v>
       </c>
-      <c r="C4" s="67">
+      <c r="C4" s="68">
         <v>1</v>
       </c>
       <c r="D4" s="14">
@@ -2046,7 +2153,7 @@
       <c r="E4" s="17">
         <v>2</v>
       </c>
-      <c r="F4" s="68">
+      <c r="F4" s="69">
         <v>456.5</v>
       </c>
       <c r="G4" s="17">
@@ -2063,7 +2170,7 @@
       <c r="B5" s="14">
         <v>525.70000000000005</v>
       </c>
-      <c r="C5" s="67">
+      <c r="C5" s="68">
         <v>1</v>
       </c>
       <c r="D5" s="14">
@@ -2072,7 +2179,7 @@
       <c r="E5" s="17">
         <v>2</v>
       </c>
-      <c r="F5" s="68">
+      <c r="F5" s="69">
         <v>760</v>
       </c>
       <c r="G5" s="17">
@@ -2086,7 +2193,7 @@
       <c r="B6" s="14">
         <v>737.4</v>
       </c>
-      <c r="C6" s="67">
+      <c r="C6" s="68">
         <v>1</v>
       </c>
       <c r="D6" s="14">
@@ -2095,7 +2202,7 @@
       <c r="E6" s="17">
         <v>2</v>
       </c>
-      <c r="F6" s="68">
+      <c r="F6" s="69">
         <v>1063</v>
       </c>
       <c r="G6" s="17">
@@ -2109,7 +2216,7 @@
       <c r="B7" s="14">
         <v>949.3</v>
       </c>
-      <c r="C7" s="67">
+      <c r="C7" s="68">
         <v>1</v>
       </c>
       <c r="D7" s="14">
@@ -2118,7 +2225,7 @@
       <c r="E7" s="17">
         <v>2</v>
       </c>
-      <c r="F7" s="68">
+      <c r="F7" s="69">
         <v>1380</v>
       </c>
       <c r="G7" s="17">
@@ -2129,10 +2236,10 @@
       <c r="A8" s="41">
         <v>11</v>
       </c>
-      <c r="B8" s="70">
+      <c r="B8" s="71">
         <v>1155.4000000000001</v>
       </c>
-      <c r="C8" s="71">
+      <c r="C8" s="72">
         <v>2</v>
       </c>
       <c r="D8" s="23">

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1167" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F630840-F85B-42A7-91F1-4802B7CBBDE0}"/>
+  <xr:revisionPtr revIDLastSave="1199" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5972859D-3801-4EFA-8DA2-6FB95AEC447D}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="6" activeTab="9" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
@@ -179,7 +179,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.000000000"/>
     <numFmt numFmtId="166" formatCode="#,##0.00000"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
-    <numFmt numFmtId="171" formatCode="0.000000"/>
+    <numFmt numFmtId="170" formatCode="0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -416,7 +416,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -516,16 +516,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1019,10 +1021,10 @@
   <cols>
     <col min="1" max="1" width="12.19921875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.06640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" ht="14.65" thickBot="1">
       <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
@@ -1034,133 +1036,160 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="68">
+      <c r="A2" s="15">
         <v>222</v>
       </c>
-      <c r="B2" s="68">
+      <c r="B2" s="70">
         <v>0.05</v>
       </c>
-      <c r="C2" s="68"/>
+      <c r="C2" s="78">
+        <v>6.4000000000000005E-4</v>
+      </c>
       <c r="D2" s="74"/>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="68">
+      <c r="A3" s="14">
         <v>232</v>
       </c>
       <c r="B3" s="68">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="C3" s="68"/>
+      <c r="C3" s="75">
+        <v>5.2999999999999998E-4</v>
+      </c>
       <c r="D3" s="74"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="69">
+      <c r="A4" s="67">
         <v>242</v>
       </c>
-      <c r="B4" s="75">
+      <c r="B4" s="77">
         <v>0.09</v>
       </c>
-      <c r="C4" s="68"/>
+      <c r="C4" s="75">
+        <v>5.9999999999999995E-4</v>
+      </c>
       <c r="D4" s="74"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="68">
+      <c r="A5" s="14">
         <v>252</v>
       </c>
-      <c r="B5" s="75">
+      <c r="B5" s="77">
         <v>0.16400000000000001</v>
       </c>
-      <c r="C5" s="76"/>
+      <c r="C5" s="75">
+        <v>5.2999999999999998E-4</v>
+      </c>
       <c r="D5" s="74"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="68">
+      <c r="A6" s="14">
         <v>262</v>
       </c>
-      <c r="B6" s="75">
+      <c r="B6" s="77">
         <v>0.20599999999999999</v>
       </c>
-      <c r="C6" s="76"/>
+      <c r="C6" s="75">
+        <v>4.4000000000000002E-4</v>
+      </c>
       <c r="D6" s="74"/>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="68">
+      <c r="A7" s="14">
         <v>272</v>
       </c>
-      <c r="B7" s="75">
+      <c r="B7" s="77">
         <v>0.27</v>
       </c>
-      <c r="C7" s="76"/>
+      <c r="C7" s="75">
+        <v>3.6000000000000002E-4</v>
+      </c>
       <c r="D7" s="74"/>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="67">
+      <c r="A8" s="34">
         <v>282</v>
       </c>
-      <c r="B8" s="75">
+      <c r="B8" s="77">
         <v>0.32200000000000001</v>
       </c>
-      <c r="C8" s="76">
-        <v>4.2999999999999999E-4</v>
+      <c r="C8" s="75">
+        <v>2.5999999999999998E-4</v>
       </c>
       <c r="D8" s="74"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="68">
+      <c r="A9" s="14">
         <v>292</v>
       </c>
-      <c r="B9" s="75">
+      <c r="B9" s="77">
         <v>0.27800000000000002</v>
       </c>
-      <c r="C9" s="76"/>
+      <c r="C9" s="75">
+        <v>8.0000000000000007E-5</v>
+      </c>
       <c r="D9" s="74"/>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="68">
+      <c r="A10" s="14">
         <v>302</v>
       </c>
-      <c r="B10" s="75">
+      <c r="B10" s="77">
         <v>0.21</v>
       </c>
-      <c r="C10" s="76"/>
+      <c r="C10" s="75">
+        <v>5.9000000000000003E-4</v>
+      </c>
       <c r="D10" s="74"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="68">
+      <c r="A11" s="14">
         <v>312</v>
       </c>
-      <c r="B11" s="75">
+      <c r="B11" s="77">
         <v>0.16600000000000001</v>
       </c>
-      <c r="C11" s="76"/>
+      <c r="C11" s="75">
+        <v>8.7000000000000001E-4</v>
+      </c>
       <c r="D11" s="74"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="68">
+      <c r="A12" s="14">
         <v>322</v>
       </c>
-      <c r="B12" s="75">
+      <c r="B12" s="77">
         <v>0.13800000000000001</v>
       </c>
-      <c r="C12" s="76"/>
+      <c r="C12" s="75">
+        <v>9.6000000000000002E-4</v>
+      </c>
+      <c r="D12" s="74"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="68">
+      <c r="A13" s="14">
         <v>332</v>
       </c>
-      <c r="B13" s="75">
+      <c r="B13" s="77">
         <v>0.11600000000000001</v>
       </c>
-      <c r="C13" s="76"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="68">
+      <c r="C13" s="75">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="D13" s="74"/>
+    </row>
+    <row r="14" spans="1:4" ht="14.65" thickBot="1">
+      <c r="A14" s="23">
         <v>342</v>
       </c>
-      <c r="B14" s="75">
+      <c r="B14" s="18">
         <v>0.10199999999999999</v>
       </c>
-      <c r="C14" s="76"/>
+      <c r="C14" s="76">
+        <v>1.06E-3</v>
+      </c>
+      <c r="D14" s="74"/>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" s="29"/>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1199" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5972859D-3801-4EFA-8DA2-6FB95AEC447D}"/>
+  <xr:revisionPtr revIDLastSave="1216" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9581DF2-5BAE-4AF9-BCC3-34BD130C76DD}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="6" activeTab="9" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="7" activeTab="9" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Aria (tubo aperto)" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="Argon e kripton 2" sheetId="8" r:id="rId8"/>
     <sheet name="Onde quadre (Argon e Kripton)" sheetId="9" r:id="rId9"/>
     <sheet name="Ampiezza e fase 2" sheetId="10" r:id="rId10"/>
+    <sheet name="Foglio1" sheetId="11" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Ampiezza e fase 2'!$A$1:$C$11</definedName>
@@ -1067,7 +1068,7 @@
         <v>0.09</v>
       </c>
       <c r="C4" s="75">
-        <v>5.9999999999999995E-4</v>
+        <v>0.4</v>
       </c>
       <c r="D4" s="74"/>
     </row>
@@ -1079,7 +1080,7 @@
         <v>0.16400000000000001</v>
       </c>
       <c r="C5" s="75">
-        <v>5.2999999999999998E-4</v>
+        <v>4.2999999999999999E-4</v>
       </c>
       <c r="D5" s="74"/>
     </row>
@@ -1091,7 +1092,7 @@
         <v>0.20599999999999999</v>
       </c>
       <c r="C6" s="75">
-        <v>4.4000000000000002E-4</v>
+        <v>5.5000000000000003E-4</v>
       </c>
       <c r="D6" s="74"/>
     </row>
@@ -1103,7 +1104,7 @@
         <v>0.27</v>
       </c>
       <c r="C7" s="75">
-        <v>3.6000000000000002E-4</v>
+        <v>5.8E-4</v>
       </c>
       <c r="D7" s="74"/>
     </row>
@@ -1115,7 +1116,7 @@
         <v>0.32200000000000001</v>
       </c>
       <c r="C8" s="75">
-        <v>2.5999999999999998E-4</v>
+        <v>6.8999999999999997E-4</v>
       </c>
       <c r="D8" s="74"/>
     </row>
@@ -1127,7 +1128,7 @@
         <v>0.27800000000000002</v>
       </c>
       <c r="C9" s="75">
-        <v>8.0000000000000007E-5</v>
+        <v>9.5E-4</v>
       </c>
       <c r="D9" s="74"/>
     </row>
@@ -1139,7 +1140,7 @@
         <v>0.21</v>
       </c>
       <c r="C10" s="75">
-        <v>5.9000000000000003E-4</v>
+        <v>1.4400000000000001E-3</v>
       </c>
       <c r="D10" s="74"/>
     </row>
@@ -1151,7 +1152,7 @@
         <v>0.16600000000000001</v>
       </c>
       <c r="C11" s="75">
-        <v>8.7000000000000001E-4</v>
+        <v>1.7099999999999999E-3</v>
       </c>
       <c r="D11" s="74"/>
     </row>
@@ -1163,7 +1164,7 @@
         <v>0.13800000000000001</v>
       </c>
       <c r="C12" s="75">
-        <v>9.6000000000000002E-4</v>
+        <v>1.7899999999999999E-3</v>
       </c>
       <c r="D12" s="74"/>
     </row>
@@ -1175,7 +1176,7 @@
         <v>0.11600000000000001</v>
       </c>
       <c r="C13" s="75">
-        <v>9.8999999999999999E-4</v>
+        <v>1.8E-3</v>
       </c>
       <c r="D13" s="74"/>
     </row>
@@ -1187,7 +1188,7 @@
         <v>0.10199999999999999</v>
       </c>
       <c r="C14" s="76">
-        <v>1.06E-3</v>
+        <v>1.81E-3</v>
       </c>
       <c r="D14" s="74"/>
     </row>
@@ -1203,6 +1204,15 @@
       <sortCondition ref="A1:A9"/>
     </sortState>
   </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{945BF175-338D-4DE0-99AC-C2E7E5FFDF3D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1216" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9581DF2-5BAE-4AF9-BCC3-34BD130C76DD}"/>
+  <xr:revisionPtr revIDLastSave="1217" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7DD5EB3-E05E-40C2-8CCC-732C43D464FD}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="7" activeTab="9" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
@@ -1068,7 +1068,7 @@
         <v>0.09</v>
       </c>
       <c r="C4" s="75">
-        <v>0.4</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="D4" s="74"/>
     </row>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1217" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7DD5EB3-E05E-40C2-8CCC-732C43D464FD}"/>
+  <xr:revisionPtr revIDLastSave="1230" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62C42EC7-BE73-4824-9809-4EAFFA013B09}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="7" activeTab="9" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="7" activeTab="7" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Aria (tubo aperto)" sheetId="1" r:id="rId1"/>
@@ -2370,11 +2370,14 @@
       <c r="E3" s="34">
         <v>1</v>
       </c>
+      <c r="F3" s="69">
+        <v>93.5</v>
+      </c>
       <c r="G3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H3" s="6">
-        <v>1.45</v>
+        <v>1.454</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -2390,8 +2393,11 @@
       <c r="E4" s="34">
         <v>2</v>
       </c>
+      <c r="F4">
+        <v>188.3</v>
+      </c>
       <c r="G4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>27</v>
@@ -2408,10 +2414,15 @@
       <c r="E5" s="34">
         <v>3</v>
       </c>
+      <c r="F5" s="69">
+        <v>281.89999999999998</v>
+      </c>
       <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="H5" s="6">
+        <v>295.14999999999998</v>
+      </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="34">
@@ -2426,8 +2437,11 @@
       <c r="E6" s="34">
         <v>4</v>
       </c>
+      <c r="F6" s="69">
+        <v>374.9</v>
+      </c>
       <c r="G6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>18</v>
@@ -2456,8 +2470,14 @@
       </c>
     </row>
     <row r="8" spans="1:8">
+      <c r="A8" s="34">
+        <v>6</v>
+      </c>
       <c r="D8" s="7" t="s">
         <v>28</v>
+      </c>
+      <c r="E8" s="34">
+        <v>6</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>28</v>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1230" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62C42EC7-BE73-4824-9809-4EAFFA013B09}"/>
+  <xr:revisionPtr revIDLastSave="1234" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62973C71-2353-42A4-BE82-FFEE4BD8C814}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="7" activeTab="7" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
@@ -2461,9 +2461,11 @@
       <c r="E7" s="34">
         <v>5</v>
       </c>
-      <c r="F7" s="35"/>
+      <c r="F7" s="35">
+        <v>469.1</v>
+      </c>
       <c r="G7" s="35">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H7" s="6">
         <v>0.5</v>
@@ -2478,6 +2480,12 @@
       </c>
       <c r="E8" s="34">
         <v>6</v>
+      </c>
+      <c r="F8" s="69">
+        <v>560</v>
+      </c>
+      <c r="G8" s="69">
+        <v>3</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>28</v>

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1234" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62973C71-2353-42A4-BE82-FFEE4BD8C814}"/>
+  <xr:revisionPtr revIDLastSave="1259" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{117D139B-7957-42A4-86A4-8BDC2AF626D6}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="7" activeTab="7" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
@@ -417,7 +417,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -522,6 +522,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -529,6 +530,13 @@
     <xf numFmtId="170" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1043,10 +1051,10 @@
       <c r="B2" s="70">
         <v>0.05</v>
       </c>
-      <c r="C2" s="78">
+      <c r="C2" s="79">
         <v>6.4000000000000005E-4</v>
       </c>
-      <c r="D2" s="74"/>
+      <c r="D2" s="75"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="14">
@@ -1055,130 +1063,130 @@
       <c r="B3" s="68">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="C3" s="75">
+      <c r="C3" s="76">
         <v>5.2999999999999998E-4</v>
       </c>
-      <c r="D3" s="74"/>
+      <c r="D3" s="75"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="67">
         <v>242</v>
       </c>
-      <c r="B4" s="77">
+      <c r="B4" s="78">
         <v>0.09</v>
       </c>
-      <c r="C4" s="75">
+      <c r="C4" s="76">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="D4" s="74"/>
+      <c r="D4" s="75"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="14">
         <v>252</v>
       </c>
-      <c r="B5" s="77">
+      <c r="B5" s="78">
         <v>0.16400000000000001</v>
       </c>
-      <c r="C5" s="75">
+      <c r="C5" s="76">
         <v>4.2999999999999999E-4</v>
       </c>
-      <c r="D5" s="74"/>
+      <c r="D5" s="75"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="14">
         <v>262</v>
       </c>
-      <c r="B6" s="77">
+      <c r="B6" s="78">
         <v>0.20599999999999999</v>
       </c>
-      <c r="C6" s="75">
+      <c r="C6" s="76">
         <v>5.5000000000000003E-4</v>
       </c>
-      <c r="D6" s="74"/>
+      <c r="D6" s="75"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="14">
         <v>272</v>
       </c>
-      <c r="B7" s="77">
+      <c r="B7" s="78">
         <v>0.27</v>
       </c>
-      <c r="C7" s="75">
+      <c r="C7" s="76">
         <v>5.8E-4</v>
       </c>
-      <c r="D7" s="74"/>
+      <c r="D7" s="75"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="34">
         <v>282</v>
       </c>
-      <c r="B8" s="77">
+      <c r="B8" s="78">
         <v>0.32200000000000001</v>
       </c>
-      <c r="C8" s="75">
+      <c r="C8" s="76">
         <v>6.8999999999999997E-4</v>
       </c>
-      <c r="D8" s="74"/>
+      <c r="D8" s="75"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="14">
         <v>292</v>
       </c>
-      <c r="B9" s="77">
+      <c r="B9" s="78">
         <v>0.27800000000000002</v>
       </c>
-      <c r="C9" s="75">
+      <c r="C9" s="76">
         <v>9.5E-4</v>
       </c>
-      <c r="D9" s="74"/>
+      <c r="D9" s="75"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="14">
         <v>302</v>
       </c>
-      <c r="B10" s="77">
+      <c r="B10" s="78">
         <v>0.21</v>
       </c>
-      <c r="C10" s="75">
+      <c r="C10" s="76">
         <v>1.4400000000000001E-3</v>
       </c>
-      <c r="D10" s="74"/>
+      <c r="D10" s="75"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="14">
         <v>312</v>
       </c>
-      <c r="B11" s="77">
+      <c r="B11" s="78">
         <v>0.16600000000000001</v>
       </c>
-      <c r="C11" s="75">
+      <c r="C11" s="76">
         <v>1.7099999999999999E-3</v>
       </c>
-      <c r="D11" s="74"/>
+      <c r="D11" s="75"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="14">
         <v>322</v>
       </c>
-      <c r="B12" s="77">
+      <c r="B12" s="78">
         <v>0.13800000000000001</v>
       </c>
-      <c r="C12" s="75">
+      <c r="C12" s="76">
         <v>1.7899999999999999E-3</v>
       </c>
-      <c r="D12" s="74"/>
+      <c r="D12" s="75"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="14">
         <v>332</v>
       </c>
-      <c r="B13" s="77">
+      <c r="B13" s="78">
         <v>0.11600000000000001</v>
       </c>
-      <c r="C13" s="75">
+      <c r="C13" s="76">
         <v>1.8E-3</v>
       </c>
-      <c r="D13" s="74"/>
+      <c r="D13" s="75"/>
     </row>
     <row r="14" spans="1:4" ht="14.65" thickBot="1">
       <c r="A14" s="23">
@@ -1187,10 +1195,10 @@
       <c r="B14" s="18">
         <v>0.10199999999999999</v>
       </c>
-      <c r="C14" s="76">
+      <c r="C14" s="77">
         <v>1.81E-3</v>
       </c>
-      <c r="D14" s="74"/>
+      <c r="D14" s="75"/>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" s="29"/>
@@ -2172,7 +2180,7 @@
       <c r="G3" s="20">
         <v>3</v>
       </c>
-      <c r="H3" s="73" t="s">
+      <c r="H3" s="74" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2278,7 +2286,7 @@
       <c r="B8" s="71">
         <v>1155.4000000000001</v>
       </c>
-      <c r="C8" s="72">
+      <c r="C8" s="73">
         <v>2</v>
       </c>
       <c r="D8" s="23">
@@ -2318,33 +2326,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="82" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="51" t="s">
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="52" t="s">
         <v>25</v>
       </c>
       <c r="F1" s="52"/>
       <c r="G1" s="52"/>
       <c r="H1" s="53"/>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="9" t="s">
+    <row r="2" spans="1:8" ht="14.65" thickBot="1">
+      <c r="A2" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="32" t="s">
         <v>0</v>
       </c>
       <c r="F2" s="32" t="s">
@@ -2361,22 +2369,25 @@
       <c r="A3" s="34">
         <v>1</v>
       </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3" s="6">
-        <v>1.45</v>
-      </c>
-      <c r="E3" s="34">
+      <c r="B3" s="68">
+        <v>111.5</v>
+      </c>
+      <c r="C3" s="68">
         <v>1</v>
       </c>
-      <c r="F3" s="69">
+      <c r="D3" s="49">
+        <v>1.46</v>
+      </c>
+      <c r="E3" s="13">
+        <v>1</v>
+      </c>
+      <c r="F3" s="80">
         <v>93.5</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="20">
         <v>1</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="17">
         <v>1.454</v>
       </c>
     </row>
@@ -2384,22 +2395,25 @@
       <c r="A4" s="34">
         <v>2</v>
       </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="B4" s="68">
+        <v>225.3</v>
+      </c>
+      <c r="C4" s="68">
+        <v>2</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="34">
+      <c r="E4" s="81">
         <v>2</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="14">
         <v>188.3</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="17">
         <v>2</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="33" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2407,20 +2421,25 @@
       <c r="A5" s="34">
         <v>3</v>
       </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="34">
+      <c r="B5" s="68">
+        <v>338.4</v>
+      </c>
+      <c r="C5" s="68">
         <v>3</v>
       </c>
-      <c r="F5" s="69">
+      <c r="D5" s="6">
+        <v>295.64999999999998</v>
+      </c>
+      <c r="E5" s="81">
+        <v>3</v>
+      </c>
+      <c r="F5" s="67">
         <v>281.89999999999998</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="17">
         <v>2</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="17">
         <v>295.14999999999998</v>
       </c>
     </row>
@@ -2428,22 +2447,25 @@
       <c r="A6" s="34">
         <v>4</v>
       </c>
-      <c r="C6">
-        <v>4</v>
+      <c r="B6" s="69">
+        <v>449.8</v>
+      </c>
+      <c r="C6" s="68">
+        <v>3</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="34">
+      <c r="E6" s="81">
         <v>4</v>
       </c>
-      <c r="F6" s="69">
+      <c r="F6" s="67">
         <v>374.9</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="17">
         <v>2</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="74" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2451,43 +2473,51 @@
       <c r="A7" s="34">
         <v>5</v>
       </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="11">
-        <v>4</v>
+      <c r="B7" s="69">
+        <v>561.9</v>
+      </c>
+      <c r="C7" s="68">
+        <v>3</v>
       </c>
       <c r="D7" s="6">
         <v>0.5</v>
       </c>
-      <c r="E7" s="34">
+      <c r="E7" s="81">
         <v>5</v>
       </c>
-      <c r="F7" s="35">
+      <c r="F7" s="14">
         <v>469.1</v>
       </c>
-      <c r="G7" s="35">
+      <c r="G7" s="17">
         <v>2</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="17">
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="34">
+    <row r="8" spans="1:8" ht="14.65" thickBot="1">
+      <c r="A8" s="50">
         <v>6</v>
+      </c>
+      <c r="B8" s="35">
+        <v>676.4</v>
+      </c>
+      <c r="C8" s="35">
+        <v>3</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="34">
+      <c r="E8" s="83">
         <v>6</v>
       </c>
-      <c r="F8" s="69">
+      <c r="F8" s="71">
         <v>560</v>
       </c>
-      <c r="G8" s="69">
+      <c r="G8" s="72">
         <v>3</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="33" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2515,8 +2545,8 @@
         <v>5.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
-      <c r="D12" s="7" t="s">
+    <row r="12" spans="1:8" ht="14.65" thickBot="1">
+      <c r="D12" s="84" t="s">
         <v>16</v>
       </c>
       <c r="H12" s="7" t="s">

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1259" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{117D139B-7957-42A4-86A4-8BDC2AF626D6}"/>
+  <xr:revisionPtr revIDLastSave="1263" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32A883AD-2AE6-41D2-B9B0-7DC9288A562F}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="7" activeTab="7" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="4" activeTab="7" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Aria (tubo aperto)" sheetId="1" r:id="rId1"/>
@@ -417,7 +417,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -522,7 +522,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1051,10 +1050,10 @@
       <c r="B2" s="70">
         <v>0.05</v>
       </c>
-      <c r="C2" s="79">
+      <c r="C2" s="78">
         <v>6.4000000000000005E-4</v>
       </c>
-      <c r="D2" s="75"/>
+      <c r="D2" s="74"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="14">
@@ -1063,130 +1062,130 @@
       <c r="B3" s="68">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="C3" s="76">
+      <c r="C3" s="75">
         <v>5.2999999999999998E-4</v>
       </c>
-      <c r="D3" s="75"/>
+      <c r="D3" s="74"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="67">
         <v>242</v>
       </c>
-      <c r="B4" s="78">
+      <c r="B4" s="77">
         <v>0.09</v>
       </c>
-      <c r="C4" s="76">
+      <c r="C4" s="75">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="D4" s="75"/>
+      <c r="D4" s="74"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="14">
         <v>252</v>
       </c>
-      <c r="B5" s="78">
+      <c r="B5" s="77">
         <v>0.16400000000000001</v>
       </c>
-      <c r="C5" s="76">
+      <c r="C5" s="75">
         <v>4.2999999999999999E-4</v>
       </c>
-      <c r="D5" s="75"/>
+      <c r="D5" s="74"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="14">
         <v>262</v>
       </c>
-      <c r="B6" s="78">
+      <c r="B6" s="77">
         <v>0.20599999999999999</v>
       </c>
-      <c r="C6" s="76">
+      <c r="C6" s="75">
         <v>5.5000000000000003E-4</v>
       </c>
-      <c r="D6" s="75"/>
+      <c r="D6" s="74"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="14">
         <v>272</v>
       </c>
-      <c r="B7" s="78">
+      <c r="B7" s="77">
         <v>0.27</v>
       </c>
-      <c r="C7" s="76">
+      <c r="C7" s="75">
         <v>5.8E-4</v>
       </c>
-      <c r="D7" s="75"/>
+      <c r="D7" s="74"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="34">
         <v>282</v>
       </c>
-      <c r="B8" s="78">
+      <c r="B8" s="77">
         <v>0.32200000000000001</v>
       </c>
-      <c r="C8" s="76">
+      <c r="C8" s="75">
         <v>6.8999999999999997E-4</v>
       </c>
-      <c r="D8" s="75"/>
+      <c r="D8" s="74"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="14">
         <v>292</v>
       </c>
-      <c r="B9" s="78">
+      <c r="B9" s="77">
         <v>0.27800000000000002</v>
       </c>
-      <c r="C9" s="76">
+      <c r="C9" s="75">
         <v>9.5E-4</v>
       </c>
-      <c r="D9" s="75"/>
+      <c r="D9" s="74"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="14">
         <v>302</v>
       </c>
-      <c r="B10" s="78">
+      <c r="B10" s="77">
         <v>0.21</v>
       </c>
-      <c r="C10" s="76">
+      <c r="C10" s="75">
         <v>1.4400000000000001E-3</v>
       </c>
-      <c r="D10" s="75"/>
+      <c r="D10" s="74"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="14">
         <v>312</v>
       </c>
-      <c r="B11" s="78">
+      <c r="B11" s="77">
         <v>0.16600000000000001</v>
       </c>
-      <c r="C11" s="76">
+      <c r="C11" s="75">
         <v>1.7099999999999999E-3</v>
       </c>
-      <c r="D11" s="75"/>
+      <c r="D11" s="74"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="14">
         <v>322</v>
       </c>
-      <c r="B12" s="78">
+      <c r="B12" s="77">
         <v>0.13800000000000001</v>
       </c>
-      <c r="C12" s="76">
+      <c r="C12" s="75">
         <v>1.7899999999999999E-3</v>
       </c>
-      <c r="D12" s="75"/>
+      <c r="D12" s="74"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="14">
         <v>332</v>
       </c>
-      <c r="B13" s="78">
+      <c r="B13" s="77">
         <v>0.11600000000000001</v>
       </c>
-      <c r="C13" s="76">
+      <c r="C13" s="75">
         <v>1.8E-3</v>
       </c>
-      <c r="D13" s="75"/>
+      <c r="D13" s="74"/>
     </row>
     <row r="14" spans="1:4" ht="14.65" thickBot="1">
       <c r="A14" s="23">
@@ -1195,10 +1194,10 @@
       <c r="B14" s="18">
         <v>0.10199999999999999</v>
       </c>
-      <c r="C14" s="77">
+      <c r="C14" s="76">
         <v>1.81E-3</v>
       </c>
-      <c r="D14" s="75"/>
+      <c r="D14" s="74"/>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" s="29"/>
@@ -2180,7 +2179,7 @@
       <c r="G3" s="20">
         <v>3</v>
       </c>
-      <c r="H3" s="74" t="s">
+      <c r="H3" s="73" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2286,7 +2285,7 @@
       <c r="B8" s="71">
         <v>1155.4000000000001</v>
       </c>
-      <c r="C8" s="73">
+      <c r="C8" s="72">
         <v>2</v>
       </c>
       <c r="D8" s="23">
@@ -2326,12 +2325,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
       <c r="E1" s="52" t="s">
         <v>25</v>
       </c>
@@ -2373,7 +2372,7 @@
         <v>111.5</v>
       </c>
       <c r="C3" s="68">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D3" s="49">
         <v>1.46</v>
@@ -2381,17 +2380,17 @@
       <c r="E3" s="13">
         <v>1</v>
       </c>
-      <c r="F3" s="80">
+      <c r="F3" s="79">
         <v>93.5</v>
       </c>
       <c r="G3" s="20">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H3" s="17">
         <v>1.454</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" ht="14.65" thickBot="1">
       <c r="A4" s="34">
         <v>2</v>
       </c>
@@ -2399,25 +2398,25 @@
         <v>225.3</v>
       </c>
       <c r="C4" s="68">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="81">
+      <c r="E4" s="80">
         <v>2</v>
       </c>
       <c r="F4" s="14">
         <v>188.3</v>
       </c>
-      <c r="G4" s="17">
-        <v>2</v>
+      <c r="G4" s="20">
+        <v>5</v>
       </c>
       <c r="H4" s="33" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" ht="14.65" thickBot="1">
       <c r="A5" s="34">
         <v>3</v>
       </c>
@@ -2425,25 +2424,25 @@
         <v>338.4</v>
       </c>
       <c r="C5" s="68">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D5" s="6">
         <v>295.64999999999998</v>
       </c>
-      <c r="E5" s="81">
+      <c r="E5" s="80">
         <v>3</v>
       </c>
       <c r="F5" s="67">
         <v>281.89999999999998</v>
       </c>
-      <c r="G5" s="17">
-        <v>2</v>
+      <c r="G5" s="20">
+        <v>5</v>
       </c>
       <c r="H5" s="17">
         <v>295.14999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" ht="14.65" thickBot="1">
       <c r="A6" s="34">
         <v>4</v>
       </c>
@@ -2451,21 +2450,21 @@
         <v>449.8</v>
       </c>
       <c r="C6" s="68">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="81">
+      <c r="E6" s="80">
         <v>4</v>
       </c>
       <c r="F6" s="67">
         <v>374.9</v>
       </c>
-      <c r="G6" s="17">
-        <v>2</v>
-      </c>
-      <c r="H6" s="74" t="s">
+      <c r="G6" s="20">
+        <v>5</v>
+      </c>
+      <c r="H6" s="73" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2477,19 +2476,19 @@
         <v>561.9</v>
       </c>
       <c r="C7" s="68">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D7" s="6">
         <v>0.5</v>
       </c>
-      <c r="E7" s="81">
+      <c r="E7" s="80">
         <v>5</v>
       </c>
       <c r="F7" s="14">
         <v>469.1</v>
       </c>
-      <c r="G7" s="17">
-        <v>2</v>
+      <c r="G7" s="20">
+        <v>5</v>
       </c>
       <c r="H7" s="17">
         <v>0.5</v>
@@ -2502,20 +2501,20 @@
       <c r="B8" s="35">
         <v>676.4</v>
       </c>
-      <c r="C8" s="35">
-        <v>3</v>
+      <c r="C8" s="68">
+        <v>5</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="83">
+      <c r="E8" s="82">
         <v>6</v>
       </c>
       <c r="F8" s="71">
         <v>560</v>
       </c>
-      <c r="G8" s="72">
-        <v>3</v>
+      <c r="G8" s="20">
+        <v>5</v>
       </c>
       <c r="H8" s="33" t="s">
         <v>28</v>
@@ -2546,7 +2545,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="14.65" thickBot="1">
-      <c r="D12" s="84" t="s">
+      <c r="D12" s="83" t="s">
         <v>16</v>
       </c>
       <c r="H12" s="7" t="s">

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1263" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32A883AD-2AE6-41D2-B9B0-7DC9288A562F}"/>
+  <xr:revisionPtr revIDLastSave="1272" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8320E91C-5232-426A-BE97-64A83A8D1D2F}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="4" activeTab="7" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
@@ -417,7 +417,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -524,6 +524,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -536,6 +537,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1050,10 +1053,10 @@
       <c r="B2" s="70">
         <v>0.05</v>
       </c>
-      <c r="C2" s="78">
+      <c r="C2" s="79">
         <v>6.4000000000000005E-4</v>
       </c>
-      <c r="D2" s="74"/>
+      <c r="D2" s="75"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="14">
@@ -1062,130 +1065,130 @@
       <c r="B3" s="68">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="C3" s="75">
+      <c r="C3" s="76">
         <v>5.2999999999999998E-4</v>
       </c>
-      <c r="D3" s="74"/>
+      <c r="D3" s="75"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="67">
         <v>242</v>
       </c>
-      <c r="B4" s="77">
+      <c r="B4" s="78">
         <v>0.09</v>
       </c>
-      <c r="C4" s="75">
+      <c r="C4" s="76">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="D4" s="74"/>
+      <c r="D4" s="75"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="14">
         <v>252</v>
       </c>
-      <c r="B5" s="77">
+      <c r="B5" s="78">
         <v>0.16400000000000001</v>
       </c>
-      <c r="C5" s="75">
+      <c r="C5" s="76">
         <v>4.2999999999999999E-4</v>
       </c>
-      <c r="D5" s="74"/>
+      <c r="D5" s="75"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="14">
         <v>262</v>
       </c>
-      <c r="B6" s="77">
+      <c r="B6" s="78">
         <v>0.20599999999999999</v>
       </c>
-      <c r="C6" s="75">
+      <c r="C6" s="76">
         <v>5.5000000000000003E-4</v>
       </c>
-      <c r="D6" s="74"/>
+      <c r="D6" s="75"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="14">
         <v>272</v>
       </c>
-      <c r="B7" s="77">
+      <c r="B7" s="78">
         <v>0.27</v>
       </c>
-      <c r="C7" s="75">
+      <c r="C7" s="76">
         <v>5.8E-4</v>
       </c>
-      <c r="D7" s="74"/>
+      <c r="D7" s="75"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="34">
         <v>282</v>
       </c>
-      <c r="B8" s="77">
+      <c r="B8" s="78">
         <v>0.32200000000000001</v>
       </c>
-      <c r="C8" s="75">
+      <c r="C8" s="76">
         <v>6.8999999999999997E-4</v>
       </c>
-      <c r="D8" s="74"/>
+      <c r="D8" s="75"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="14">
         <v>292</v>
       </c>
-      <c r="B9" s="77">
+      <c r="B9" s="78">
         <v>0.27800000000000002</v>
       </c>
-      <c r="C9" s="75">
+      <c r="C9" s="76">
         <v>9.5E-4</v>
       </c>
-      <c r="D9" s="74"/>
+      <c r="D9" s="75"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="14">
         <v>302</v>
       </c>
-      <c r="B10" s="77">
+      <c r="B10" s="78">
         <v>0.21</v>
       </c>
-      <c r="C10" s="75">
+      <c r="C10" s="76">
         <v>1.4400000000000001E-3</v>
       </c>
-      <c r="D10" s="74"/>
+      <c r="D10" s="75"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="14">
         <v>312</v>
       </c>
-      <c r="B11" s="77">
+      <c r="B11" s="78">
         <v>0.16600000000000001</v>
       </c>
-      <c r="C11" s="75">
+      <c r="C11" s="76">
         <v>1.7099999999999999E-3</v>
       </c>
-      <c r="D11" s="74"/>
+      <c r="D11" s="75"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="14">
         <v>322</v>
       </c>
-      <c r="B12" s="77">
+      <c r="B12" s="78">
         <v>0.13800000000000001</v>
       </c>
-      <c r="C12" s="75">
+      <c r="C12" s="76">
         <v>1.7899999999999999E-3</v>
       </c>
-      <c r="D12" s="74"/>
+      <c r="D12" s="75"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="14">
         <v>332</v>
       </c>
-      <c r="B13" s="77">
+      <c r="B13" s="78">
         <v>0.11600000000000001</v>
       </c>
-      <c r="C13" s="75">
+      <c r="C13" s="76">
         <v>1.8E-3</v>
       </c>
-      <c r="D13" s="74"/>
+      <c r="D13" s="75"/>
     </row>
     <row r="14" spans="1:4" ht="14.65" thickBot="1">
       <c r="A14" s="23">
@@ -1194,10 +1197,10 @@
       <c r="B14" s="18">
         <v>0.10199999999999999</v>
       </c>
-      <c r="C14" s="76">
+      <c r="C14" s="77">
         <v>1.81E-3</v>
       </c>
-      <c r="D14" s="74"/>
+      <c r="D14" s="75"/>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" s="29"/>
@@ -2325,12 +2328,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="82" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
       <c r="E1" s="52" t="s">
         <v>25</v>
       </c>
@@ -2368,7 +2371,7 @@
       <c r="A3" s="34">
         <v>1</v>
       </c>
-      <c r="B3" s="68">
+      <c r="B3" s="85">
         <v>111.5</v>
       </c>
       <c r="C3" s="68">
@@ -2380,7 +2383,7 @@
       <c r="E3" s="13">
         <v>1</v>
       </c>
-      <c r="F3" s="79">
+      <c r="F3" s="80">
         <v>93.5</v>
       </c>
       <c r="G3" s="20">
@@ -2394,7 +2397,7 @@
       <c r="A4" s="34">
         <v>2</v>
       </c>
-      <c r="B4" s="68">
+      <c r="B4" s="85">
         <v>225.3</v>
       </c>
       <c r="C4" s="68">
@@ -2403,7 +2406,7 @@
       <c r="D4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="80">
+      <c r="E4" s="81">
         <v>2</v>
       </c>
       <c r="F4" s="14">
@@ -2420,7 +2423,7 @@
       <c r="A5" s="34">
         <v>3</v>
       </c>
-      <c r="B5" s="68">
+      <c r="B5" s="85">
         <v>338.4</v>
       </c>
       <c r="C5" s="68">
@@ -2429,7 +2432,7 @@
       <c r="D5" s="6">
         <v>295.64999999999998</v>
       </c>
-      <c r="E5" s="80">
+      <c r="E5" s="81">
         <v>3</v>
       </c>
       <c r="F5" s="67">
@@ -2446,7 +2449,7 @@
       <c r="A6" s="34">
         <v>4</v>
       </c>
-      <c r="B6" s="69">
+      <c r="B6" s="86">
         <v>449.8</v>
       </c>
       <c r="C6" s="68">
@@ -2455,7 +2458,7 @@
       <c r="D6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="80">
+      <c r="E6" s="81">
         <v>4</v>
       </c>
       <c r="F6" s="67">
@@ -2472,7 +2475,7 @@
       <c r="A7" s="34">
         <v>5</v>
       </c>
-      <c r="B7" s="69">
+      <c r="B7" s="86">
         <v>561.9</v>
       </c>
       <c r="C7" s="68">
@@ -2481,7 +2484,7 @@
       <c r="D7" s="6">
         <v>0.5</v>
       </c>
-      <c r="E7" s="80">
+      <c r="E7" s="81">
         <v>5</v>
       </c>
       <c r="F7" s="14">
@@ -2498,7 +2501,7 @@
       <c r="A8" s="50">
         <v>6</v>
       </c>
-      <c r="B8" s="35">
+      <c r="B8" s="74">
         <v>676.4</v>
       </c>
       <c r="C8" s="68">
@@ -2507,7 +2510,7 @@
       <c r="D8" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="82">
+      <c r="E8" s="83">
         <v>6</v>
       </c>
       <c r="F8" s="71">
@@ -2545,7 +2548,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="14.65" thickBot="1">
-      <c r="D12" s="83" t="s">
+      <c r="D12" s="84" t="s">
         <v>16</v>
       </c>
       <c r="H12" s="7" t="s">

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1272" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8320E91C-5232-426A-BE97-64A83A8D1D2F}"/>
+  <xr:revisionPtr revIDLastSave="1284" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7A41E75-E39D-45A8-A66D-6484C1A1FC2E}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="4" activeTab="7" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
@@ -417,7 +417,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -530,7 +530,6 @@
     <xf numFmtId="170" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -539,6 +538,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -2328,12 +2331,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
       <c r="E1" s="52" t="s">
         <v>25</v>
       </c>
@@ -2371,8 +2374,8 @@
       <c r="A3" s="34">
         <v>1</v>
       </c>
-      <c r="B3" s="85">
-        <v>111.5</v>
+      <c r="B3" s="84">
+        <v>112</v>
       </c>
       <c r="C3" s="68">
         <v>5</v>
@@ -2383,8 +2386,8 @@
       <c r="E3" s="13">
         <v>1</v>
       </c>
-      <c r="F3" s="80">
-        <v>93.5</v>
+      <c r="F3" s="86">
+        <v>94</v>
       </c>
       <c r="G3" s="20">
         <v>5</v>
@@ -2397,8 +2400,8 @@
       <c r="A4" s="34">
         <v>2</v>
       </c>
-      <c r="B4" s="85">
-        <v>225.3</v>
+      <c r="B4" s="84">
+        <v>225</v>
       </c>
       <c r="C4" s="68">
         <v>5</v>
@@ -2406,11 +2409,11 @@
       <c r="D4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="81">
+      <c r="E4" s="80">
         <v>2</v>
       </c>
-      <c r="F4" s="14">
-        <v>188.3</v>
+      <c r="F4" s="87">
+        <v>188</v>
       </c>
       <c r="G4" s="20">
         <v>5</v>
@@ -2423,8 +2426,8 @@
       <c r="A5" s="34">
         <v>3</v>
       </c>
-      <c r="B5" s="85">
-        <v>338.4</v>
+      <c r="B5" s="84">
+        <v>338</v>
       </c>
       <c r="C5" s="68">
         <v>5</v>
@@ -2432,11 +2435,11 @@
       <c r="D5" s="6">
         <v>295.64999999999998</v>
       </c>
-      <c r="E5" s="81">
+      <c r="E5" s="80">
         <v>3</v>
       </c>
-      <c r="F5" s="67">
-        <v>281.89999999999998</v>
+      <c r="F5" s="88">
+        <v>282</v>
       </c>
       <c r="G5" s="20">
         <v>5</v>
@@ -2449,8 +2452,8 @@
       <c r="A6" s="34">
         <v>4</v>
       </c>
-      <c r="B6" s="86">
-        <v>449.8</v>
+      <c r="B6" s="85">
+        <v>450</v>
       </c>
       <c r="C6" s="68">
         <v>5</v>
@@ -2458,11 +2461,11 @@
       <c r="D6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="81">
+      <c r="E6" s="80">
         <v>4</v>
       </c>
-      <c r="F6" s="67">
-        <v>374.9</v>
+      <c r="F6" s="88">
+        <v>375</v>
       </c>
       <c r="G6" s="20">
         <v>5</v>
@@ -2475,8 +2478,8 @@
       <c r="A7" s="34">
         <v>5</v>
       </c>
-      <c r="B7" s="86">
-        <v>561.9</v>
+      <c r="B7" s="85">
+        <v>562</v>
       </c>
       <c r="C7" s="68">
         <v>5</v>
@@ -2484,11 +2487,11 @@
       <c r="D7" s="6">
         <v>0.5</v>
       </c>
-      <c r="E7" s="81">
+      <c r="E7" s="80">
         <v>5</v>
       </c>
-      <c r="F7" s="14">
-        <v>469.1</v>
+      <c r="F7" s="87">
+        <v>469</v>
       </c>
       <c r="G7" s="20">
         <v>5</v>
@@ -2502,7 +2505,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="74">
-        <v>676.4</v>
+        <v>676</v>
       </c>
       <c r="C8" s="68">
         <v>5</v>
@@ -2510,10 +2513,10 @@
       <c r="D8" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="83">
+      <c r="E8" s="82">
         <v>6</v>
       </c>
-      <c r="F8" s="71">
+      <c r="F8" s="89">
         <v>560</v>
       </c>
       <c r="G8" s="20">
@@ -2548,7 +2551,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="14.65" thickBot="1">
-      <c r="D12" s="84" t="s">
+      <c r="D12" s="83" t="s">
         <v>16</v>
       </c>
       <c r="H12" s="7" t="s">

--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1284" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7A41E75-E39D-45A8-A66D-6484C1A1FC2E}"/>
+  <xr:revisionPtr revIDLastSave="1367" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56AF5256-C1C6-4A2F-830C-638FD30A084F}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="4" activeTab="7" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="8" activeTab="8" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Aria (tubo aperto)" sheetId="1" r:id="rId1"/>
@@ -21,12 +21,10 @@
     <sheet name="Ampiezza e fase" sheetId="5" r:id="rId6"/>
     <sheet name="Aria 2 (tubo chiuso)" sheetId="7" r:id="rId7"/>
     <sheet name="Argon e kripton 2" sheetId="8" r:id="rId8"/>
-    <sheet name="Onde quadre (Argon e Kripton)" sheetId="9" r:id="rId9"/>
-    <sheet name="Ampiezza e fase 2" sheetId="10" r:id="rId10"/>
-    <sheet name="Foglio1" sheetId="11" r:id="rId11"/>
+    <sheet name="Ampiezza e fase 2" sheetId="10" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Ampiezza e fase 2'!$A$1:$C$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ampiezza e fase 2'!$A$1:$C$11</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -49,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="39">
   <si>
     <t>n</t>
   </si>
@@ -160,9 +158,6 @@
   </si>
   <si>
     <t>Δt (s)</t>
-  </si>
-  <si>
-    <t>Errore sulla media</t>
   </si>
   <si>
     <t xml:space="preserve">Distanza dal tubo </t>
@@ -175,12 +170,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.000000000"/>
     <numFmt numFmtId="166" formatCode="#,##0.00000"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
-    <numFmt numFmtId="170" formatCode="0.00000"/>
+    <numFmt numFmtId="168" formatCode="0.00000"/>
+    <numFmt numFmtId="171" formatCode="0.0000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -417,7 +413,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -471,7 +467,21 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -498,50 +508,25 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -906,16 +891,16 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="15">
+      <c r="B2" s="62">
         <v>190.1</v>
       </c>
       <c r="C2" s="20">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D2" s="14">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="77">
         <v>296.14999999999998</v>
       </c>
     </row>
@@ -923,11 +908,11 @@
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="63">
         <v>381</v>
       </c>
       <c r="C3" s="17">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D3" s="22" t="s">
         <v>13</v>
@@ -940,7 +925,7 @@
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="63">
         <v>561</v>
       </c>
       <c r="C4" s="17">
@@ -957,7 +942,7 @@
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="63">
         <v>760.2</v>
       </c>
       <c r="C5" s="17">
@@ -974,16 +959,16 @@
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="23">
+      <c r="B6" s="64">
         <v>935.6</v>
       </c>
       <c r="C6" s="11">
         <v>4</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="85">
         <v>0.9</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="86">
         <v>2.8964699999999999E-2</v>
       </c>
     </row>
@@ -1024,208 +1009,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9FBD33A-E969-4B4D-8F9E-2B427EE50E6E}">
-  <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.06640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.265625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="14.65" thickBot="1">
-      <c r="A1" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="33" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="15">
-        <v>222</v>
-      </c>
-      <c r="B2" s="70">
-        <v>0.05</v>
-      </c>
-      <c r="C2" s="79">
-        <v>6.4000000000000005E-4</v>
-      </c>
-      <c r="D2" s="75"/>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="14">
-        <v>232</v>
-      </c>
-      <c r="B3" s="68">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="C3" s="76">
-        <v>5.2999999999999998E-4</v>
-      </c>
-      <c r="D3" s="75"/>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="67">
-        <v>242</v>
-      </c>
-      <c r="B4" s="78">
-        <v>0.09</v>
-      </c>
-      <c r="C4" s="76">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="D4" s="75"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="14">
-        <v>252</v>
-      </c>
-      <c r="B5" s="78">
-        <v>0.16400000000000001</v>
-      </c>
-      <c r="C5" s="76">
-        <v>4.2999999999999999E-4</v>
-      </c>
-      <c r="D5" s="75"/>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="14">
-        <v>262</v>
-      </c>
-      <c r="B6" s="78">
-        <v>0.20599999999999999</v>
-      </c>
-      <c r="C6" s="76">
-        <v>5.5000000000000003E-4</v>
-      </c>
-      <c r="D6" s="75"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="14">
-        <v>272</v>
-      </c>
-      <c r="B7" s="78">
-        <v>0.27</v>
-      </c>
-      <c r="C7" s="76">
-        <v>5.8E-4</v>
-      </c>
-      <c r="D7" s="75"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="34">
-        <v>282</v>
-      </c>
-      <c r="B8" s="78">
-        <v>0.32200000000000001</v>
-      </c>
-      <c r="C8" s="76">
-        <v>6.8999999999999997E-4</v>
-      </c>
-      <c r="D8" s="75"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="14">
-        <v>292</v>
-      </c>
-      <c r="B9" s="78">
-        <v>0.27800000000000002</v>
-      </c>
-      <c r="C9" s="76">
-        <v>9.5E-4</v>
-      </c>
-      <c r="D9" s="75"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="14">
-        <v>302</v>
-      </c>
-      <c r="B10" s="78">
-        <v>0.21</v>
-      </c>
-      <c r="C10" s="76">
-        <v>1.4400000000000001E-3</v>
-      </c>
-      <c r="D10" s="75"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="14">
-        <v>312</v>
-      </c>
-      <c r="B11" s="78">
-        <v>0.16600000000000001</v>
-      </c>
-      <c r="C11" s="76">
-        <v>1.7099999999999999E-3</v>
-      </c>
-      <c r="D11" s="75"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="14">
-        <v>322</v>
-      </c>
-      <c r="B12" s="78">
-        <v>0.13800000000000001</v>
-      </c>
-      <c r="C12" s="76">
-        <v>1.7899999999999999E-3</v>
-      </c>
-      <c r="D12" s="75"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="14">
-        <v>332</v>
-      </c>
-      <c r="B13" s="78">
-        <v>0.11600000000000001</v>
-      </c>
-      <c r="C13" s="76">
-        <v>1.8E-3</v>
-      </c>
-      <c r="D13" s="75"/>
-    </row>
-    <row r="14" spans="1:4" ht="14.65" thickBot="1">
-      <c r="A14" s="23">
-        <v>342</v>
-      </c>
-      <c r="B14" s="18">
-        <v>0.10199999999999999</v>
-      </c>
-      <c r="C14" s="77">
-        <v>1.81E-3</v>
-      </c>
-      <c r="D14" s="75"/>
-    </row>
-    <row r="18" spans="2:2">
-      <c r="B18" s="29"/>
-    </row>
-    <row r="19" spans="2:2">
-      <c r="B19" s="29"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:C9" xr:uid="{D9FBD33A-E969-4B4D-8F9E-2B427EE50E6E}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C12">
-      <sortCondition ref="A1:A9"/>
-    </sortState>
-  </autoFilter>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{945BF175-338D-4DE0-99AC-C2E7E5FFDF3D}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1270,7 +1053,7 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="54" t="s">
+      <c r="A2" s="68" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="30">
@@ -1280,9 +1063,9 @@
         <v>0.34499999999999997</v>
       </c>
       <c r="D2" s="20">
-        <v>0.05</v>
-      </c>
-      <c r="E2">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="E2" s="29">
         <f>G2/G4</f>
         <v>0.45381056300973421</v>
       </c>
@@ -1295,7 +1078,7 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="55"/>
+      <c r="A3" s="69"/>
       <c r="B3" s="24">
         <v>2.5</v>
       </c>
@@ -1303,7 +1086,7 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="D3" s="17">
-        <v>0.05</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="F3" s="26">
         <f>C7-C6</f>
@@ -1314,7 +1097,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A4" s="56"/>
+      <c r="A4" s="70"/>
       <c r="B4" s="25">
         <v>3.5</v>
       </c>
@@ -1322,7 +1105,7 @@
         <v>0.78800000000000003</v>
       </c>
       <c r="D4" s="11">
-        <v>0.05</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="F4" s="26">
         <f>C6-C5</f>
@@ -1333,7 +1116,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="68" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="24">
@@ -1343,7 +1126,7 @@
         <v>0.23</v>
       </c>
       <c r="D5" s="17">
-        <v>0.05</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E5" s="14"/>
       <c r="F5" s="26">
@@ -1352,7 +1135,7 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="55"/>
+      <c r="A6" s="69"/>
       <c r="B6" s="24">
         <v>2</v>
       </c>
@@ -1360,7 +1143,7 @@
         <v>0.45</v>
       </c>
       <c r="D6" s="17">
-        <v>0.05</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>20</v>
@@ -1371,7 +1154,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A7" s="56"/>
+      <c r="A7" s="70"/>
       <c r="B7" s="25">
         <v>3</v>
       </c>
@@ -1379,7 +1162,7 @@
         <v>0.67500000000000004</v>
       </c>
       <c r="D7" s="11">
-        <v>0.05</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>21</v>
@@ -1417,19 +1200,19 @@
   <sheetData>
     <row r="1" spans="1:8" ht="14.65" thickBot="1">
       <c r="A1" s="15"/>
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="58"/>
-      <c r="D1" s="59" t="s">
+      <c r="C1" s="72"/>
+      <c r="D1" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="58"/>
+      <c r="E1" s="72"/>
       <c r="F1" s="15"/>
-      <c r="G1" s="59" t="s">
+      <c r="G1" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="58"/>
+      <c r="H1" s="72"/>
     </row>
     <row r="2" spans="1:8" ht="14.65" thickBot="1">
       <c r="A2" s="39" t="s">
@@ -1461,13 +1244,13 @@
       <c r="A3" s="40">
         <v>3</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="61">
         <v>319.2</v>
       </c>
       <c r="C3" s="17">
         <v>5</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="63">
         <v>377</v>
       </c>
       <c r="E3" s="17">
@@ -1487,13 +1270,13 @@
       <c r="A4" s="40">
         <v>5</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="61">
         <v>534.29999999999995</v>
       </c>
       <c r="C4" s="17">
         <v>5</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="63">
         <v>632</v>
       </c>
       <c r="E4" s="17">
@@ -1513,13 +1296,13 @@
       <c r="A5" s="40">
         <v>7</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="61">
         <v>741.2</v>
       </c>
       <c r="C5" s="17">
         <v>6</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="63">
         <v>884</v>
       </c>
       <c r="E5" s="17">
@@ -1539,13 +1322,13 @@
       <c r="A6" s="40">
         <v>9</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="61">
         <v>954.1</v>
       </c>
       <c r="C6" s="17">
         <v>6</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="63">
         <v>1146</v>
       </c>
       <c r="E6" s="17">
@@ -1565,13 +1348,13 @@
       <c r="A7" s="41">
         <v>11</v>
       </c>
-      <c r="B7" s="35">
+      <c r="B7" s="53">
         <v>1155.0999999999999</v>
       </c>
       <c r="C7" s="11">
         <v>6</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="64">
         <v>1404.5</v>
       </c>
       <c r="E7" s="11">
@@ -1612,18 +1395,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="51" t="s">
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="74" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="53"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="67"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="9" t="s">
@@ -1655,7 +1438,7 @@
       <c r="A3" s="34">
         <v>4</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="61">
         <v>440.2</v>
       </c>
       <c r="C3">
@@ -1667,7 +1450,7 @@
       <c r="E3" s="34">
         <v>3</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="61">
         <v>314.5</v>
       </c>
       <c r="G3">
@@ -1681,7 +1464,7 @@
       <c r="A4" s="34">
         <v>5</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="61">
         <v>549.5</v>
       </c>
       <c r="C4">
@@ -1693,7 +1476,7 @@
       <c r="E4" s="34">
         <v>4</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="61">
         <v>400</v>
       </c>
       <c r="G4">
@@ -1707,7 +1490,7 @@
       <c r="A5" s="34">
         <v>6</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="61">
         <v>659.5</v>
       </c>
       <c r="C5">
@@ -1719,7 +1502,7 @@
       <c r="E5" s="34">
         <v>5</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="61">
         <v>500</v>
       </c>
       <c r="G5">
@@ -1733,7 +1516,7 @@
       <c r="A6" s="34">
         <v>7</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="61">
         <v>769.5</v>
       </c>
       <c r="C6">
@@ -1745,7 +1528,7 @@
       <c r="E6" s="34">
         <v>6</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="61">
         <v>600</v>
       </c>
       <c r="G6">
@@ -1759,7 +1542,7 @@
       <c r="A7" s="34">
         <v>8</v>
       </c>
-      <c r="B7" s="35">
+      <c r="B7" s="53">
         <v>882</v>
       </c>
       <c r="C7" s="11">
@@ -1771,7 +1554,7 @@
       <c r="E7" s="34">
         <v>7</v>
       </c>
-      <c r="F7" s="35">
+      <c r="F7" s="53">
         <v>700</v>
       </c>
       <c r="G7" s="35">
@@ -1868,7 +1651,7 @@
       <c r="A2" s="14">
         <v>1.57</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="81">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="C2">
@@ -1877,7 +1660,7 @@
       <c r="D2">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="E2" s="17">
+      <c r="E2" s="83">
         <f>AVERAGE(C2:D2)</f>
         <v>4.4999999999999997E-3</v>
       </c>
@@ -1886,7 +1669,7 @@
       <c r="A3" s="14">
         <v>1.37</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="81">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="C3">
@@ -1895,7 +1678,7 @@
       <c r="D3">
         <v>3.9199999999999999E-3</v>
       </c>
-      <c r="E3" s="17">
+      <c r="E3" s="83">
         <f t="shared" ref="E3:E8" si="0">AVERAGE(C3:D3)</f>
         <v>3.9199999999999999E-3</v>
       </c>
@@ -1904,7 +1687,7 @@
       <c r="A4" s="14">
         <v>1.17</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="81">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="C4">
@@ -1913,7 +1696,7 @@
       <c r="D4">
         <v>3.3500000000000001E-3</v>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="83">
         <f t="shared" si="0"/>
         <v>3.3550000000000003E-3</v>
       </c>
@@ -1922,7 +1705,7 @@
       <c r="A5" s="14">
         <v>0.97</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="81">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="C5">
@@ -1931,7 +1714,7 @@
       <c r="D5">
         <v>2.7699999999999999E-3</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="83">
         <f t="shared" si="0"/>
         <v>2.7799999999999999E-3</v>
       </c>
@@ -1940,7 +1723,7 @@
       <c r="A6" s="14">
         <v>0.77</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="81">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="C6">
@@ -1949,7 +1732,7 @@
       <c r="D6">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="83">
         <f t="shared" si="0"/>
         <v>2.2000000000000001E-3</v>
       </c>
@@ -1958,7 +1741,7 @@
       <c r="A7" s="14">
         <v>0.56999999999999995</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="81">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="C7">
@@ -1967,7 +1750,7 @@
       <c r="D7">
         <v>1.6199999999999999E-3</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="83">
         <f t="shared" si="0"/>
         <v>1.6199999999999999E-3</v>
       </c>
@@ -1976,7 +1759,7 @@
       <c r="A8" s="23">
         <v>0.37</v>
       </c>
-      <c r="B8" s="35">
+      <c r="B8" s="82">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="C8" s="35">
@@ -1985,7 +1768,7 @@
       <c r="D8" s="35">
         <v>1.0399999999999999E-3</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="84">
         <f t="shared" si="0"/>
         <v>1.0449999999999999E-3</v>
       </c>
@@ -2115,23 +1898,23 @@
   <sheetData>
     <row r="1" spans="1:9" ht="14.65" thickBot="1">
       <c r="A1" s="15"/>
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="58"/>
-      <c r="D1" s="59" t="s">
+      <c r="C1" s="72"/>
+      <c r="D1" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="58"/>
-      <c r="F1" s="60" t="s">
+      <c r="E1" s="72"/>
+      <c r="F1" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="61"/>
+      <c r="G1" s="76"/>
       <c r="H1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="66" t="s">
-        <v>38</v>
+      <c r="I1" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="14.65" thickBot="1">
@@ -2156,36 +1939,36 @@
       <c r="G2" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="77">
         <v>294.64999999999998</v>
       </c>
-      <c r="I2" s="69" t="s">
-        <v>39</v>
+      <c r="I2" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="48">
         <v>1</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="62">
         <v>105</v>
       </c>
-      <c r="C3" s="70">
+      <c r="C3" s="51">
         <v>1</v>
       </c>
-      <c r="D3" s="15">
+      <c r="D3" s="62">
         <v>129.30000000000001</v>
       </c>
       <c r="E3" s="20">
         <v>2</v>
       </c>
-      <c r="F3" s="70">
+      <c r="F3" s="79">
         <v>151</v>
       </c>
       <c r="G3" s="20">
         <v>3</v>
       </c>
-      <c r="H3" s="73" t="s">
+      <c r="H3" s="52" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2193,19 +1976,19 @@
       <c r="A4" s="40">
         <v>3</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="63">
         <v>315.60000000000002</v>
       </c>
-      <c r="C4" s="68">
+      <c r="C4">
         <v>1</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="63">
         <v>386.6</v>
       </c>
       <c r="E4" s="17">
         <v>2</v>
       </c>
-      <c r="F4" s="69">
+      <c r="F4" s="61">
         <v>456.5</v>
       </c>
       <c r="G4" s="17">
@@ -2219,19 +2002,19 @@
       <c r="A5" s="40">
         <v>5</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="63">
         <v>525.70000000000005</v>
       </c>
-      <c r="C5" s="68">
+      <c r="C5">
         <v>1</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="63">
         <v>645.70000000000005</v>
       </c>
       <c r="E5" s="17">
         <v>2</v>
       </c>
-      <c r="F5" s="69">
+      <c r="F5" s="61">
         <v>760</v>
       </c>
       <c r="G5" s="17">
@@ -2242,19 +2025,19 @@
       <c r="A6" s="40">
         <v>7</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="63">
         <v>737.4</v>
       </c>
-      <c r="C6" s="68">
+      <c r="C6">
         <v>1</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="63">
         <v>903.5</v>
       </c>
       <c r="E6" s="17">
         <v>2</v>
       </c>
-      <c r="F6" s="69">
+      <c r="F6" s="61">
         <v>1063</v>
       </c>
       <c r="G6" s="17">
@@ -2265,19 +2048,19 @@
       <c r="A7" s="40">
         <v>9</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="63">
         <v>949.3</v>
       </c>
-      <c r="C7" s="68">
+      <c r="C7">
         <v>1</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="63">
         <v>1162.7</v>
       </c>
       <c r="E7" s="17">
         <v>2</v>
       </c>
-      <c r="F7" s="69">
+      <c r="F7" s="61">
         <v>1380</v>
       </c>
       <c r="G7" s="17">
@@ -2288,19 +2071,19 @@
       <c r="A8" s="41">
         <v>11</v>
       </c>
-      <c r="B8" s="71">
+      <c r="B8" s="64">
         <v>1155.4000000000001</v>
       </c>
-      <c r="C8" s="72">
+      <c r="C8" s="35">
         <v>2</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="64">
         <v>1430</v>
       </c>
       <c r="E8" s="11">
         <v>3</v>
       </c>
-      <c r="F8" s="35">
+      <c r="F8" s="53">
         <v>1680</v>
       </c>
       <c r="G8" s="11">
@@ -2331,18 +2114,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="52" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="53"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="67"/>
     </row>
     <row r="2" spans="1:8" ht="14.65" thickBot="1">
       <c r="A2" s="36" t="s">
@@ -2374,10 +2157,10 @@
       <c r="A3" s="34">
         <v>1</v>
       </c>
-      <c r="B3" s="84">
+      <c r="B3" s="61">
         <v>112</v>
       </c>
-      <c r="C3" s="68">
+      <c r="C3" s="20">
         <v>5</v>
       </c>
       <c r="D3" s="49">
@@ -2386,7 +2169,7 @@
       <c r="E3" s="13">
         <v>1</v>
       </c>
-      <c r="F3" s="86">
+      <c r="F3" s="62">
         <v>94</v>
       </c>
       <c r="G3" s="20">
@@ -2396,81 +2179,81 @@
         <v>1.454</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="14.65" thickBot="1">
+    <row r="4" spans="1:8">
       <c r="A4" s="34">
         <v>2</v>
       </c>
-      <c r="B4" s="84">
+      <c r="B4" s="61">
         <v>225</v>
       </c>
-      <c r="C4" s="68">
+      <c r="C4" s="17">
         <v>5</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="80">
+      <c r="E4" s="58">
         <v>2</v>
       </c>
-      <c r="F4" s="87">
+      <c r="F4" s="63">
         <v>188</v>
       </c>
-      <c r="G4" s="20">
+      <c r="G4" s="17">
         <v>5</v>
       </c>
       <c r="H4" s="33" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="14.65" thickBot="1">
+    <row r="5" spans="1:8">
       <c r="A5" s="34">
         <v>3</v>
       </c>
-      <c r="B5" s="84">
+      <c r="B5" s="61">
         <v>338</v>
       </c>
-      <c r="C5" s="68">
-        <v>5</v>
-      </c>
-      <c r="D5" s="6">
+      <c r="C5" s="17">
+        <v>5</v>
+      </c>
+      <c r="D5" s="77">
         <v>295.64999999999998</v>
       </c>
-      <c r="E5" s="80">
+      <c r="E5" s="58">
         <v>3</v>
       </c>
-      <c r="F5" s="88">
+      <c r="F5" s="63">
         <v>282</v>
       </c>
-      <c r="G5" s="20">
-        <v>5</v>
-      </c>
-      <c r="H5" s="17">
+      <c r="G5" s="17">
+        <v>5</v>
+      </c>
+      <c r="H5" s="80">
         <v>295.14999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="14.65" thickBot="1">
+    <row r="6" spans="1:8">
       <c r="A6" s="34">
         <v>4</v>
       </c>
-      <c r="B6" s="85">
+      <c r="B6" s="61">
         <v>450</v>
       </c>
-      <c r="C6" s="68">
+      <c r="C6" s="17">
         <v>5</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="80">
+      <c r="E6" s="58">
         <v>4</v>
       </c>
-      <c r="F6" s="88">
+      <c r="F6" s="63">
         <v>375</v>
       </c>
-      <c r="G6" s="20">
-        <v>5</v>
-      </c>
-      <c r="H6" s="73" t="s">
+      <c r="G6" s="17">
+        <v>5</v>
+      </c>
+      <c r="H6" s="52" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2478,22 +2261,22 @@
       <c r="A7" s="34">
         <v>5</v>
       </c>
-      <c r="B7" s="85">
+      <c r="B7" s="61">
         <v>562</v>
       </c>
-      <c r="C7" s="68">
+      <c r="C7" s="17">
         <v>5</v>
       </c>
       <c r="D7" s="6">
         <v>0.5</v>
       </c>
-      <c r="E7" s="80">
-        <v>5</v>
-      </c>
-      <c r="F7" s="87">
+      <c r="E7" s="58">
+        <v>5</v>
+      </c>
+      <c r="F7" s="63">
         <v>469</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="17">
         <v>5</v>
       </c>
       <c r="H7" s="17">
@@ -2504,22 +2287,22 @@
       <c r="A8" s="50">
         <v>6</v>
       </c>
-      <c r="B8" s="74">
+      <c r="B8" s="53">
         <v>676</v>
       </c>
-      <c r="C8" s="68">
+      <c r="C8" s="11">
         <v>5</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="82">
+      <c r="E8" s="59">
         <v>6</v>
       </c>
-      <c r="F8" s="89">
+      <c r="F8" s="64">
         <v>560</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="11">
         <v>5</v>
       </c>
       <c r="H8" s="33" t="s">
@@ -2527,10 +2310,10 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="14.65" thickBot="1">
-      <c r="D9" s="8">
+      <c r="D9" s="78">
         <v>3.9947999999999997E-2</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="78">
         <v>8.3797999999999997E-2</v>
       </c>
     </row>
@@ -2551,7 +2334,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="14.65" thickBot="1">
-      <c r="D12" s="83" t="s">
+      <c r="D12" s="60" t="s">
         <v>16</v>
       </c>
       <c r="H12" s="7" t="s">
@@ -2576,122 +2359,194 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73ADE9FB-B547-41CD-8278-951487520755}">
-  <dimension ref="A1:D11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9FBD33A-E969-4B4D-8F9E-2B427EE50E6E}">
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.06640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.9296875" customWidth="1"/>
-    <col min="5" max="5" width="10.06640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.73046875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="7.86328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.06640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="14.65" thickBot="1">
-      <c r="A1" s="62" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="64" t="s">
-        <v>25</v>
-      </c>
-      <c r="D1" s="65"/>
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" s="48" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="14.65" thickBot="1">
-      <c r="A3" s="23">
-        <v>1.45</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="23">
-        <v>1.45</v>
-      </c>
-      <c r="D3" s="6"/>
+      <c r="A2" s="15">
+        <v>222</v>
+      </c>
+      <c r="B2" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="C2" s="57">
+        <v>6.4000000000000005E-4</v>
+      </c>
+      <c r="D2" s="54"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="14">
+        <v>232</v>
+      </c>
+      <c r="B3">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="C3" s="55">
+        <v>5.2999999999999998E-4</v>
+      </c>
+      <c r="D3" s="54"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="14"/>
-      <c r="B4" s="6"/>
-      <c r="D4" s="6"/>
+      <c r="A4" s="14">
+        <v>242</v>
+      </c>
+      <c r="B4" s="29">
+        <v>0.09</v>
+      </c>
+      <c r="C4" s="55">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="D4" s="54"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="14"/>
-      <c r="B5" s="6"/>
-      <c r="D5" s="6"/>
+      <c r="A5" s="14">
+        <v>252</v>
+      </c>
+      <c r="B5" s="29">
+        <v>0.16400000000000001</v>
+      </c>
+      <c r="C5" s="55">
+        <v>4.2999999999999999E-4</v>
+      </c>
+      <c r="D5" s="54"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="14"/>
-      <c r="B6" s="6"/>
-      <c r="D6" s="6"/>
+      <c r="A6" s="14">
+        <v>262</v>
+      </c>
+      <c r="B6" s="29">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="C6" s="55">
+        <v>5.5000000000000003E-4</v>
+      </c>
+      <c r="D6" s="54"/>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="14"/>
-      <c r="B7" s="6"/>
-      <c r="D7" s="6"/>
+      <c r="A7" s="14">
+        <v>272</v>
+      </c>
+      <c r="B7" s="29">
+        <v>0.27</v>
+      </c>
+      <c r="C7" s="55">
+        <v>5.8E-4</v>
+      </c>
+      <c r="D7" s="54"/>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="14"/>
-      <c r="B8" s="6"/>
-      <c r="D8" s="6"/>
-    </row>
-    <row r="9" spans="1:4" ht="14.65" thickBot="1">
-      <c r="A9" s="14"/>
-      <c r="B9" s="6"/>
-      <c r="D9" s="6"/>
+      <c r="A8" s="34">
+        <v>282</v>
+      </c>
+      <c r="B8" s="29">
+        <v>0.32200000000000001</v>
+      </c>
+      <c r="C8" s="55">
+        <v>6.8999999999999997E-4</v>
+      </c>
+      <c r="D8" s="54"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="14">
+        <v>292</v>
+      </c>
+      <c r="B9" s="29">
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="C9" s="55">
+        <v>9.5E-4</v>
+      </c>
+      <c r="D9" s="54"/>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="49" t="e">
-        <f>AVERAGE(B3:B9)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="49" t="e">
-        <f>AVERAGE(D3:D9)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="14.65" thickBot="1">
-      <c r="A11" s="50" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="8" t="e">
-        <f>_xlfn.STDEV.S(B3:B9)/COUNT(B3:B9)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C11" s="50" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="8" t="e">
-        <f>_xlfn.STDEV.S(D3:D9)/COUNT(D3:D9)</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="A10" s="14">
+        <v>302</v>
+      </c>
+      <c r="B10" s="29">
+        <v>0.21</v>
+      </c>
+      <c r="C10" s="55">
+        <v>1.4400000000000001E-3</v>
+      </c>
+      <c r="D10" s="54"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="14">
+        <v>312</v>
+      </c>
+      <c r="B11" s="29">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="C11" s="55">
+        <v>1.7099999999999999E-3</v>
+      </c>
+      <c r="D11" s="54"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="14">
+        <v>322</v>
+      </c>
+      <c r="B12" s="29">
+        <v>0.13800000000000001</v>
+      </c>
+      <c r="C12" s="55">
+        <v>1.7899999999999999E-3</v>
+      </c>
+      <c r="D12" s="54"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="14">
+        <v>332</v>
+      </c>
+      <c r="B13" s="29">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="C13" s="55">
+        <v>1.8E-3</v>
+      </c>
+      <c r="D13" s="54"/>
+    </row>
+    <row r="14" spans="1:4" ht="14.65" thickBot="1">
+      <c r="A14" s="23">
+        <v>342</v>
+      </c>
+      <c r="B14" s="18">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="C14" s="56">
+        <v>1.81E-3</v>
+      </c>
+      <c r="D14" s="54"/>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" s="29"/>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" s="29"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-  </mergeCells>
+  <autoFilter ref="A1:C9" xr:uid="{D9FBD33A-E969-4B4D-8F9E-2B427EE50E6E}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C12">
+      <sortCondition ref="A1:A9"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Tubo risonanza.xlsx
+++ b/Tubo risonanza.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1367" documentId="8_{34F8618C-3BC8-4D1E-A580-8499E5AA5FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56AF5256-C1C6-4A2F-830C-638FD30A084F}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="8" activeTab="8" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{84DCF574-2E35-45F1-915E-7E47BD9768D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Aria (tubo aperto)" sheetId="1" r:id="rId1"/>
@@ -176,7 +176,7 @@
     <numFmt numFmtId="166" formatCode="#,##0.00000"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
     <numFmt numFmtId="168" formatCode="0.00000"/>
-    <numFmt numFmtId="171" formatCode="0.0000"/>
+    <numFmt numFmtId="169" formatCode="0.0000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -481,15 +481,16 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -511,22 +512,21 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -900,7 +900,7 @@
       <c r="D2" s="14">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="E2" s="77">
+      <c r="E2" s="65">
         <v>296.14999999999998</v>
       </c>
     </row>
@@ -965,10 +965,10 @@
       <c r="C6" s="11">
         <v>4</v>
       </c>
-      <c r="D6" s="85">
+      <c r="D6" s="73">
         <v>0.9</v>
       </c>
-      <c r="E6" s="86">
+      <c r="E6" s="74">
         <v>2.8964699999999999E-2</v>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="68" t="s">
+      <c r="A2" s="75" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="30">
@@ -1078,7 +1078,7 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="69"/>
+      <c r="A3" s="76"/>
       <c r="B3" s="24">
         <v>2.5</v>
       </c>
@@ -1097,7 +1097,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A4" s="70"/>
+      <c r="A4" s="77"/>
       <c r="B4" s="25">
         <v>3.5</v>
       </c>
@@ -1116,7 +1116,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A5" s="68" t="s">
+      <c r="A5" s="75" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="24">
@@ -1135,7 +1135,7 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="69"/>
+      <c r="A6" s="76"/>
       <c r="B6" s="24">
         <v>2</v>
       </c>
@@ -1154,7 +1154,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A7" s="70"/>
+      <c r="A7" s="77"/>
       <c r="B7" s="25">
         <v>3</v>
       </c>
@@ -1200,19 +1200,19 @@
   <sheetData>
     <row r="1" spans="1:8" ht="14.65" thickBot="1">
       <c r="A1" s="15"/>
-      <c r="B1" s="71" t="s">
+      <c r="B1" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="72"/>
-      <c r="D1" s="73" t="s">
+      <c r="C1" s="79"/>
+      <c r="D1" s="80" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="72"/>
+      <c r="E1" s="79"/>
       <c r="F1" s="15"/>
-      <c r="G1" s="73" t="s">
+      <c r="G1" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="72"/>
+      <c r="H1" s="79"/>
     </row>
     <row r="2" spans="1:8" ht="14.65" thickBot="1">
       <c r="A2" s="39" t="s">
@@ -1395,18 +1395,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="74" t="s">
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="81" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="67"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="83"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="9" t="s">
@@ -1651,7 +1651,7 @@
       <c r="A2" s="14">
         <v>1.57</v>
       </c>
-      <c r="B2" s="81">
+      <c r="B2" s="69">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="C2">
@@ -1660,7 +1660,7 @@
       <c r="D2">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="E2" s="83">
+      <c r="E2" s="71">
         <f>AVERAGE(C2:D2)</f>
         <v>4.4999999999999997E-3</v>
       </c>
@@ -1669,7 +1669,7 @@
       <c r="A3" s="14">
         <v>1.37</v>
       </c>
-      <c r="B3" s="81">
+      <c r="B3" s="69">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="C3">
@@ -1678,7 +1678,7 @@
       <c r="D3">
         <v>3.9199999999999999E-3</v>
       </c>
-      <c r="E3" s="83">
+      <c r="E3" s="71">
         <f t="shared" ref="E3:E8" si="0">AVERAGE(C3:D3)</f>
         <v>3.9199999999999999E-3</v>
       </c>
@@ -1687,7 +1687,7 @@
       <c r="A4" s="14">
         <v>1.17</v>
       </c>
-      <c r="B4" s="81">
+      <c r="B4" s="69">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="C4">
@@ -1696,7 +1696,7 @@
       <c r="D4">
         <v>3.3500000000000001E-3</v>
       </c>
-      <c r="E4" s="83">
+      <c r="E4" s="71">
         <f t="shared" si="0"/>
         <v>3.3550000000000003E-3</v>
       </c>
@@ -1705,7 +1705,7 @@
       <c r="A5" s="14">
         <v>0.97</v>
       </c>
-      <c r="B5" s="81">
+      <c r="B5" s="69">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="C5">
@@ -1714,7 +1714,7 @@
       <c r="D5">
         <v>2.7699999999999999E-3</v>
       </c>
-      <c r="E5" s="83">
+      <c r="E5" s="71">
         <f t="shared" si="0"/>
         <v>2.7799999999999999E-3</v>
       </c>
@@ -1723,7 +1723,7 @@
       <c r="A6" s="14">
         <v>0.77</v>
       </c>
-      <c r="B6" s="81">
+      <c r="B6" s="69">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="C6">
@@ -1732,7 +1732,7 @@
       <c r="D6">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="E6" s="83">
+      <c r="E6" s="71">
         <f t="shared" si="0"/>
         <v>2.2000000000000001E-3</v>
       </c>
@@ -1741,7 +1741,7 @@
       <c r="A7" s="14">
         <v>0.56999999999999995</v>
       </c>
-      <c r="B7" s="81">
+      <c r="B7" s="69">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="C7">
@@ -1750,7 +1750,7 @@
       <c r="D7">
         <v>1.6199999999999999E-3</v>
       </c>
-      <c r="E7" s="83">
+      <c r="E7" s="71">
         <f t="shared" si="0"/>
         <v>1.6199999999999999E-3</v>
       </c>
@@ -1759,7 +1759,7 @@
       <c r="A8" s="23">
         <v>0.37</v>
       </c>
-      <c r="B8" s="82">
+      <c r="B8" s="70">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="C8" s="35">
@@ -1768,7 +1768,7 @@
       <c r="D8" s="35">
         <v>1.0399999999999999E-3</v>
       </c>
-      <c r="E8" s="84">
+      <c r="E8" s="72">
         <f t="shared" si="0"/>
         <v>1.0449999999999999E-3</v>
       </c>
@@ -1898,18 +1898,18 @@
   <sheetData>
     <row r="1" spans="1:9" ht="14.65" thickBot="1">
       <c r="A1" s="15"/>
-      <c r="B1" s="71" t="s">
+      <c r="B1" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="72"/>
-      <c r="D1" s="73" t="s">
+      <c r="C1" s="79"/>
+      <c r="D1" s="80" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="72"/>
-      <c r="F1" s="75" t="s">
+      <c r="E1" s="79"/>
+      <c r="F1" s="84" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="76"/>
+      <c r="G1" s="85"/>
       <c r="H1" s="5" t="s">
         <v>15</v>
       </c>
@@ -1939,7 +1939,7 @@
       <c r="G2" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="77">
+      <c r="H2" s="65">
         <v>294.64999999999998</v>
       </c>
       <c r="I2" t="s">
@@ -1962,7 +1962,7 @@
       <c r="E3" s="20">
         <v>2</v>
       </c>
-      <c r="F3" s="79">
+      <c r="F3" s="67">
         <v>151</v>
       </c>
       <c r="G3" s="20">
@@ -2114,18 +2114,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.65" thickBot="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="86" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="66" t="s">
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="67"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="83"/>
     </row>
     <row r="2" spans="1:8" ht="14.65" thickBot="1">
       <c r="A2" s="36" t="s">
@@ -2215,7 +2215,7 @@
       <c r="C5" s="17">
         <v>5</v>
       </c>
-      <c r="D5" s="77">
+      <c r="D5" s="65">
         <v>295.64999999999998</v>
       </c>
       <c r="E5" s="58">
@@ -2227,7 +2227,7 @@
       <c r="G5" s="17">
         <v>5</v>
       </c>
-      <c r="H5" s="80">
+      <c r="H5" s="68">
         <v>295.14999999999998</v>
       </c>
     </row>
@@ -2310,10 +2310,10 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="14.65" thickBot="1">
-      <c r="D9" s="78">
+      <c r="D9" s="66">
         <v>3.9947999999999997E-2</v>
       </c>
-      <c r="H9" s="78">
+      <c r="H9" s="66">
         <v>8.3797999999999997E-2</v>
       </c>
     </row>
